--- a/InputData/trans/BCDTRtSY/BAU Cargo Dist Transported Relative to Start Yr.xlsx
+++ b/InputData/trans/BCDTRtSY/BAU Cargo Dist Transported Relative to Start Yr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28409"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/skorpius/Library/CloudStorage/GoogleDrive-ferolea@gmail.com/.shortcut-targets-by-id/1HGdhm3a4YN2IE0FhA2aqI2jKTxxSmLoI/EI.ICM/Material de apoyo/Transporte/BCDTRtSY/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\eps-mexico\InputData\trans\BCDTRtSY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B9EDD0-2B24-4A42-939B-40DEA43ED1F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345E1DF7-738B-47A7-959F-1ADECE585CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="29040" windowHeight="19820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="95">
   <si>
     <t>BCDTRtSY BAU Cargo Dist Transported Relative to Start Year</t>
   </si>
@@ -14571,6 +14571,142 @@
       <c r="BU40" t="s">
         <v>63</v>
       </c>
+      <c r="BV40">
+        <f t="shared" ref="BV40:DC40" si="33">BV6</f>
+        <v>2017</v>
+      </c>
+      <c r="BW40">
+        <f t="shared" si="33"/>
+        <v>2018</v>
+      </c>
+      <c r="BX40">
+        <f t="shared" si="33"/>
+        <v>2019</v>
+      </c>
+      <c r="BY40">
+        <f t="shared" si="33"/>
+        <v>2020</v>
+      </c>
+      <c r="BZ40">
+        <f t="shared" si="33"/>
+        <v>2021</v>
+      </c>
+      <c r="CA40">
+        <f>CA6</f>
+        <v>2022</v>
+      </c>
+      <c r="CB40">
+        <f t="shared" si="33"/>
+        <v>2023</v>
+      </c>
+      <c r="CC40">
+        <f t="shared" si="33"/>
+        <v>2024</v>
+      </c>
+      <c r="CD40">
+        <f t="shared" si="33"/>
+        <v>2025</v>
+      </c>
+      <c r="CE40">
+        <f t="shared" si="33"/>
+        <v>2026</v>
+      </c>
+      <c r="CF40">
+        <f t="shared" si="33"/>
+        <v>2027</v>
+      </c>
+      <c r="CG40">
+        <f t="shared" si="33"/>
+        <v>2028</v>
+      </c>
+      <c r="CH40">
+        <f t="shared" si="33"/>
+        <v>2029</v>
+      </c>
+      <c r="CI40">
+        <f t="shared" si="33"/>
+        <v>2030</v>
+      </c>
+      <c r="CJ40">
+        <f t="shared" si="33"/>
+        <v>2031</v>
+      </c>
+      <c r="CK40">
+        <f t="shared" si="33"/>
+        <v>2032</v>
+      </c>
+      <c r="CL40">
+        <f t="shared" si="33"/>
+        <v>2033</v>
+      </c>
+      <c r="CM40">
+        <f t="shared" si="33"/>
+        <v>2034</v>
+      </c>
+      <c r="CN40">
+        <f t="shared" si="33"/>
+        <v>2035</v>
+      </c>
+      <c r="CO40">
+        <f t="shared" si="33"/>
+        <v>2036</v>
+      </c>
+      <c r="CP40">
+        <f t="shared" si="33"/>
+        <v>2037</v>
+      </c>
+      <c r="CQ40">
+        <f t="shared" si="33"/>
+        <v>2038</v>
+      </c>
+      <c r="CR40">
+        <f t="shared" si="33"/>
+        <v>2039</v>
+      </c>
+      <c r="CS40">
+        <f t="shared" si="33"/>
+        <v>2040</v>
+      </c>
+      <c r="CT40">
+        <f t="shared" si="33"/>
+        <v>2041</v>
+      </c>
+      <c r="CU40">
+        <f t="shared" si="33"/>
+        <v>2042</v>
+      </c>
+      <c r="CV40">
+        <f t="shared" si="33"/>
+        <v>2043</v>
+      </c>
+      <c r="CW40">
+        <f t="shared" si="33"/>
+        <v>2044</v>
+      </c>
+      <c r="CX40">
+        <f t="shared" si="33"/>
+        <v>2045</v>
+      </c>
+      <c r="CY40">
+        <f t="shared" si="33"/>
+        <v>2046</v>
+      </c>
+      <c r="CZ40">
+        <f t="shared" si="33"/>
+        <v>2047</v>
+      </c>
+      <c r="DA40">
+        <f t="shared" si="33"/>
+        <v>2048</v>
+      </c>
+      <c r="DB40">
+        <f t="shared" si="33"/>
+        <v>2049</v>
+      </c>
+      <c r="DC40">
+        <f t="shared" si="33"/>
+        <v>2050</v>
+      </c>
     </row>
     <row r="41" spans="2:107">
       <c r="B41" t="s">
@@ -14594,139 +14730,139 @@
         <v>279361.98342830798</v>
       </c>
       <c r="BV41" s="37">
-        <f t="shared" ref="BV41:DC41" si="33">BV7+BV12+BV28+BV30+BV33</f>
+        <f t="shared" ref="BV41:DC41" si="34">BV7+BV12+BV28+BV30+BV33</f>
         <v>287706.06220015557</v>
       </c>
       <c r="BW41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>295942.50701369793</v>
       </c>
       <c r="BX41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>304095.44007988111</v>
       </c>
       <c r="BY41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>312359.09518968011</v>
       </c>
       <c r="BZ41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>320960.38387676375</v>
       </c>
       <c r="CA41" s="37">
-        <f t="shared" si="33"/>
+        <f>CA7+CA12+CA28+CA30+CA33</f>
         <v>329609.9164185538</v>
       </c>
       <c r="CB41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>338491.41872723802</v>
       </c>
       <c r="CC41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>347717.54395971453</v>
       </c>
       <c r="CD41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>357460.7694629507</v>
       </c>
       <c r="CE41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>367945.62554579409</v>
       </c>
       <c r="CF41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>378836.11103348382</v>
       </c>
       <c r="CG41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>391193.66342530464</v>
       </c>
       <c r="CH41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>405135.77844961517</v>
       </c>
       <c r="CI41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>419153.48822661955</v>
       </c>
       <c r="CJ41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>433577.542444847</v>
       </c>
       <c r="CK41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>448448.58346936561</v>
       </c>
       <c r="CL41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>463801.53626499535</v>
       </c>
       <c r="CM41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>479679.23531577562</v>
       </c>
       <c r="CN41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>486703.53668920597</v>
       </c>
       <c r="CO41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>493948.29443099099</v>
       </c>
       <c r="CP41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>501426.40225408657</v>
       </c>
       <c r="CQ41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>509151.65106013254</v>
       </c>
       <c r="CR41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>517138.79322953901</v>
       </c>
       <c r="CS41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>525403.6115392464</v>
       </c>
       <c r="CT41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>533962.99304150511</v>
       </c>
       <c r="CU41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>542835.00826103892</v>
       </c>
       <c r="CV41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>552038.99609370506</v>
       </c>
       <c r="CW41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>561595.65481735941</v>
       </c>
       <c r="CX41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>571527.13965523045</v>
       </c>
       <c r="CY41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>581857.16736382456</v>
       </c>
       <c r="CZ41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>592611.12835139257</v>
       </c>
       <c r="DA41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>603816.20686944714</v>
       </c>
       <c r="DB41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>615501.50985890056</v>
       </c>
       <c r="DC41" s="37">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>627698.20507429854</v>
       </c>
     </row>
@@ -14752,139 +14888,139 @@
         <v>327116.9920531268</v>
       </c>
       <c r="BV42" s="37">
-        <f t="shared" ref="BV42:DC42" si="34">BV26+BV27</f>
+        <f t="shared" ref="BV42:DC42" si="35">BV26+BV27</f>
         <v>321756.39738196286</v>
       </c>
       <c r="BW42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>318633.53945038799</v>
       </c>
       <c r="BX42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>315395.12813876983</v>
       </c>
       <c r="BY42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>311582.45052803191</v>
       </c>
       <c r="BZ42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>306877.25423118961</v>
       </c>
       <c r="CA42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>302391.93787426583</v>
       </c>
       <c r="CB42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>302443.61648804648</v>
       </c>
       <c r="CC42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>305178.33063114551</v>
       </c>
       <c r="CD42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>307588.31878076779</v>
       </c>
       <c r="CE42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>310331.96777644224</v>
       </c>
       <c r="CF42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>315823.41368198156</v>
       </c>
       <c r="CG42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>321971.79110242537</v>
       </c>
       <c r="CH42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>328683.48202329769</v>
       </c>
       <c r="CI42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>335673.77896237472</v>
       </c>
       <c r="CJ42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>342253.01281595766</v>
       </c>
       <c r="CK42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>348536.35521011066</v>
       </c>
       <c r="CL42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>354577.31949300418</v>
       </c>
       <c r="CM42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>360798.3949003059</v>
       </c>
       <c r="CN42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>364210.0202065488</v>
       </c>
       <c r="CO42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>367654.03839946387</v>
       </c>
       <c r="CP42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>371130.75852051459</v>
       </c>
       <c r="CQ42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>374640.49257580983</v>
       </c>
       <c r="CR42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>378183.5555647228</v>
       </c>
       <c r="CS42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>381760.26550878712</v>
       </c>
       <c r="CT42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>385370.94348087435</v>
       </c>
       <c r="CU42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>389015.91363465524</v>
       </c>
       <c r="CV42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>392695.50323434733</v>
       </c>
       <c r="CW42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>396410.04268475174</v>
       </c>
       <c r="CX42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>400159.86556158197</v>
       </c>
       <c r="CY42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>403945.30864208838</v>
       </c>
       <c r="CZ42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>407766.71193597931</v>
       </c>
       <c r="DA42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>411624.41871664423</v>
       </c>
       <c r="DB42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>415518.77555267961</v>
       </c>
       <c r="DC42" s="37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>419450.13233972219</v>
       </c>
     </row>
@@ -14910,139 +15046,139 @@
         <v>17320.036799862188</v>
       </c>
       <c r="BV43" s="37">
-        <f t="shared" ref="BV43:DC43" si="35">BV24</f>
+        <f t="shared" ref="BV43:DC43" si="36">BV24</f>
         <v>18501.796972281769</v>
       </c>
       <c r="BW43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>19628.309706638152</v>
       </c>
       <c r="BX43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>20701.862939993684</v>
       </c>
       <c r="BY43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>21724.859471252887</v>
       </c>
       <c r="BZ43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>22711.41335186869</v>
       </c>
       <c r="CA43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>23665.994299172664</v>
       </c>
       <c r="CB43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>24591.387761664872</v>
       </c>
       <c r="CC43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>25493.213894705612</v>
       </c>
       <c r="CD43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>26375.115874543248</v>
       </c>
       <c r="CE43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>27243.244195320713</v>
       </c>
       <c r="CF43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>28102.491116154411</v>
       </c>
       <c r="CG43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>28954.460579953215</v>
       </c>
       <c r="CH43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>29804.172187830813</v>
       </c>
       <c r="CI43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>30655.734507998259</v>
       </c>
       <c r="CJ43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>31480.643844294889</v>
       </c>
       <c r="CK43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>32285.483098806555</v>
       </c>
       <c r="CL43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>33071.80987208763</v>
       </c>
       <c r="CM43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>33842.992747623903</v>
       </c>
       <c r="CN43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>34294.860305512921</v>
       </c>
       <c r="CO43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>34752.761144542157</v>
       </c>
       <c r="CP43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>35216.775820353811</v>
       </c>
       <c r="CQ43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>35686.985964159299</v>
       </c>
       <c r="CR43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>36163.474297100147</v>
       </c>
       <c r="CS43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>36646.324644800567</v>
       </c>
       <c r="CT43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>37135.621952114408</v>
       </c>
       <c r="CU43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>37631.452298068965</v>
       </c>
       <c r="CV43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>38133.902911008314</v>
       </c>
       <c r="CW43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>38643.06218393887</v>
       </c>
       <c r="CX43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>39159.019690079811</v>
       </c>
       <c r="CY43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>39681.866198621137</v>
       </c>
       <c r="CZ43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>40211.693690692111</v>
       </c>
       <c r="DA43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>40748.595375542965</v>
       </c>
       <c r="DB43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>41292.665706942578</v>
       </c>
       <c r="DC43" s="37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>41844.000399795172</v>
       </c>
     </row>
@@ -15068,139 +15204,139 @@
         <v>133078.67843419794</v>
       </c>
       <c r="BV44" s="37">
-        <f t="shared" ref="BV44:DC44" si="36">BV13+BV14+BV15+BV17+BV18+BV19+BV31</f>
+        <f t="shared" ref="BV44:DC44" si="37">BV13+BV14+BV15+BV17+BV18+BV19+BV31</f>
         <v>137831.42690337566</v>
       </c>
       <c r="BW44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>142703.60668052826</v>
       </c>
       <c r="BX44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>148318.81708444876</v>
       </c>
       <c r="BY44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>154100.47415183665</v>
       </c>
       <c r="BZ44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>160047.71423499245</v>
       </c>
       <c r="CA44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>166188.33860095323</v>
       </c>
       <c r="CB44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>172626.34957429851</v>
       </c>
       <c r="CC44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>179325.40869729398</v>
       </c>
       <c r="CD44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>186214.91528089345</v>
       </c>
       <c r="CE44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>193288.25661287189</v>
       </c>
       <c r="CF44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>200615.72798563208</v>
       </c>
       <c r="CG44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>208154.62840555713</v>
       </c>
       <c r="CH44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>215918.93298858404</v>
       </c>
       <c r="CI44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>223899.00961825458</v>
       </c>
       <c r="CJ44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>232056.68257611326</v>
       </c>
       <c r="CK44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>240378.30111743027</v>
       </c>
       <c r="CL44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>248839.93889114424</v>
       </c>
       <c r="CM44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>257449.70328362737</v>
       </c>
       <c r="CN44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>261537.26341840619</v>
       </c>
       <c r="CO44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>265695.0953946212</v>
       </c>
       <c r="CP44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>269924.46228737442</v>
       </c>
       <c r="CQ44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>274226.65042942378</v>
       </c>
       <c r="CR44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>278602.96984488785</v>
       </c>
       <c r="CS44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>283054.75469109172</v>
       </c>
       <c r="CT44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>287583.36370870552</v>
       </c>
       <c r="CU44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>292190.18068033346</v>
       </c>
       <c r="CV44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>296876.61489771114</v>
       </c>
       <c r="CW44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>301644.10163767403</v>
       </c>
       <c r="CX44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>306494.10264706251</v>
       </c>
       <c r="CY44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>311428.10663673043</v>
       </c>
       <c r="CZ44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>316447.62978483096</v>
       </c>
       <c r="DA44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>321554.21624955162</v>
       </c>
       <c r="DB44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>326749.43869147927</v>
       </c>
       <c r="DC44" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>332034.89880577434</v>
       </c>
     </row>
@@ -15226,145 +15362,151 @@
         <v>731331.35051324428</v>
       </c>
       <c r="BV45" s="37">
-        <f t="shared" ref="BV45:DC45" si="37">BV20+BV22+BV32</f>
+        <f t="shared" ref="BV45:DC45" si="38">BV20+BV22+BV32</f>
         <v>766094.66934096883</v>
       </c>
       <c r="BW45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>800652.36538417765</v>
       </c>
       <c r="BX45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>834863.96530559671</v>
       </c>
       <c r="BY45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>868646.8371896469</v>
       </c>
       <c r="BZ45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>902116.15628301934</v>
       </c>
       <c r="CA45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>935342.86574395827</v>
       </c>
       <c r="CB45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>969663.26173659158</v>
       </c>
       <c r="CC45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1005255.7441791665</v>
       </c>
       <c r="CD45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1041009.8375782928</v>
       </c>
       <c r="CE45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1076476.5268221381</v>
       </c>
       <c r="CF45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1112730.8350358657</v>
       </c>
       <c r="CG45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1149462.3297953801</v>
       </c>
       <c r="CH45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1186555.4509650399</v>
       </c>
       <c r="CI45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1223832.3466483087</v>
       </c>
       <c r="CJ45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1260471.8320155602</v>
       </c>
       <c r="CK45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1296135.8144071174</v>
       </c>
       <c r="CL45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1331368.8610624759</v>
       </c>
       <c r="CM45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1366899.2832650638</v>
       </c>
       <c r="CN45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1382366.8943322077</v>
       </c>
       <c r="CO45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1398011.1238428848</v>
       </c>
       <c r="CP45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1413834.0068595051</v>
       </c>
       <c r="CQ45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1429837.6021075239</v>
       </c>
       <c r="CR45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1446023.992253117</v>
       </c>
       <c r="CS45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1462395.2841841439</v>
       </c>
       <c r="CT45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1478953.6092944401</v>
       </c>
       <c r="CU45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1495701.1237714752</v>
       </c>
       <c r="CV45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1512640.008887419</v>
       </c>
       <c r="CW45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1529772.471293658</v>
       </c>
       <c r="CX45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1547100.743318799</v>
       </c>
       <c r="CY45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1564627.0832702052</v>
       </c>
       <c r="CZ45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1582353.7757391075</v>
       </c>
       <c r="DA45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1600283.1319093276</v>
       </c>
       <c r="DB45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1618417.4898696668</v>
       </c>
       <c r="DC45" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1636759.2149299937</v>
       </c>
     </row>
     <row r="47" spans="2:107">
       <c r="D47" s="37"/>
       <c r="BU47" s="37"/>
+      <c r="BY47">
+        <v>2020</v>
+      </c>
+      <c r="BZ47">
+        <v>2021</v>
+      </c>
       <c r="CA47" s="1">
         <v>2022</v>
       </c>
@@ -15392,127 +15534,129 @@
       <c r="BX48" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="BY48" s="51" t="s">
-        <v>70</v>
-      </c>
-      <c r="BZ48" s="51" t="s">
-        <v>70</v>
+      <c r="BY48">
+        <f>BY41/$BY41</f>
+        <v>1</v>
+      </c>
+      <c r="BZ48">
+        <f t="shared" ref="BZ48:DC48" si="39">BZ41/$BY41</f>
+        <v>1.0275365398976473</v>
       </c>
       <c r="CA48">
-        <f t="shared" ref="CA48:DC48" si="38">CA41/$CA41</f>
-        <v>1</v>
+        <f t="shared" si="39"/>
+        <v>1.0552275297711378</v>
       </c>
       <c r="CB48">
-        <f t="shared" si="38"/>
-        <v>1.02694549486007</v>
+        <f t="shared" si="39"/>
+        <v>1.0836611577507902</v>
       </c>
       <c r="CC48">
-        <f t="shared" si="38"/>
-        <v>1.0549365375226358</v>
+        <f t="shared" si="39"/>
+        <v>1.113198076555328</v>
       </c>
       <c r="CD48">
-        <f t="shared" si="38"/>
-        <v>1.084496405165889</v>
+        <f t="shared" si="39"/>
+        <v>1.1443904626688799</v>
       </c>
       <c r="CE48">
-        <f t="shared" si="38"/>
-        <v>1.1163062978923239</v>
+        <f t="shared" si="39"/>
+        <v>1.1779571371928808</v>
       </c>
       <c r="CF48">
-        <f t="shared" si="38"/>
-        <v>1.1493468253316153</v>
+        <f t="shared" si="39"/>
+        <v>1.2128224113449795</v>
       </c>
       <c r="CG48">
-        <f t="shared" si="38"/>
-        <v>1.1868382713599823</v>
+        <f t="shared" si="39"/>
+        <v>1.2523844173250414</v>
       </c>
       <c r="CH48">
-        <f t="shared" si="38"/>
-        <v>1.2291371050109887</v>
+        <f t="shared" si="39"/>
+        <v>1.297019311070793</v>
       </c>
       <c r="CI48">
-        <f t="shared" si="38"/>
-        <v>1.2716652847736512</v>
+        <f t="shared" si="39"/>
+        <v>1.3418962171474103</v>
       </c>
       <c r="CJ48">
-        <f t="shared" si="38"/>
-        <v>1.3154262685903853</v>
+        <f t="shared" si="39"/>
+        <v>1.3880740120006974</v>
       </c>
       <c r="CK48">
-        <f t="shared" si="38"/>
-        <v>1.3605433608978712</v>
+        <f t="shared" si="39"/>
+        <v>1.4356828098667822</v>
       </c>
       <c r="CL48">
-        <f t="shared" si="38"/>
-        <v>1.4071225201733277</v>
+        <f t="shared" si="39"/>
+        <v>1.4848344210478386</v>
       </c>
       <c r="CM48">
-        <f t="shared" si="38"/>
-        <v>1.4552937014997356</v>
+        <f t="shared" si="39"/>
+        <v>1.5356659777250614</v>
       </c>
       <c r="CN48">
-        <f t="shared" si="38"/>
-        <v>1.4766046543064788</v>
+        <f t="shared" si="39"/>
+        <v>1.5581538818123901</v>
       </c>
       <c r="CO48">
-        <f t="shared" si="38"/>
-        <v>1.4985844473312289</v>
+        <f t="shared" si="39"/>
+        <v>1.5813475645107782</v>
       </c>
       <c r="CP48">
-        <f t="shared" si="38"/>
-        <v>1.5212721986718152</v>
+        <f t="shared" si="39"/>
+        <v>1.605288304313967</v>
       </c>
       <c r="CQ48">
-        <f t="shared" si="38"/>
-        <v>1.5447097483972188</v>
+        <f t="shared" si="39"/>
+        <v>1.6300202520145928</v>
       </c>
       <c r="CR48">
-        <f t="shared" si="38"/>
-        <v>1.5689418535965782</v>
+        <f t="shared" si="39"/>
+        <v>1.6555906365252671</v>
       </c>
       <c r="CS48">
-        <f t="shared" si="38"/>
-        <v>1.5940163974680446</v>
+        <f t="shared" si="39"/>
+        <v>1.6820499855148927</v>
       </c>
       <c r="CT48">
-        <f t="shared" si="38"/>
-        <v>1.6199846134588207</v>
+        <f t="shared" si="39"/>
+        <v>1.7094523619274027</v>
       </c>
       <c r="CU48">
-        <f t="shared" si="38"/>
-        <v>1.6469013255405889</v>
+        <f t="shared" si="39"/>
+        <v>1.7378556175270077</v>
       </c>
       <c r="CV48">
-        <f t="shared" si="38"/>
-        <v>1.6748252057826458</v>
+        <f t="shared" si="39"/>
+        <v>1.7673216646964587</v>
       </c>
       <c r="CW48">
-        <f t="shared" si="38"/>
-        <v>1.7038190504687956</v>
+        <f t="shared" si="39"/>
+        <v>1.7979167678031924</v>
       </c>
       <c r="CX48">
-        <f t="shared" si="38"/>
-        <v>1.7339500760938245</v>
+        <f t="shared" si="39"/>
+        <v>1.8297118555429626</v>
       </c>
       <c r="CY48">
-        <f t="shared" si="38"/>
-        <v>1.7652902366716285</v>
+        <f t="shared" si="39"/>
+        <v>1.8627828557721096</v>
       </c>
       <c r="CZ48">
-        <f t="shared" si="38"/>
-        <v>1.7979165638902312</v>
+        <f t="shared" si="39"/>
+        <v>1.8972110544485006</v>
       </c>
       <c r="DA48">
-        <f t="shared" si="38"/>
-        <v>1.8319115317595409</v>
+        <f t="shared" si="39"/>
+        <v>1.9330834804178814</v>
       </c>
       <c r="DB48">
-        <f t="shared" si="38"/>
-        <v>1.867363447516271</v>
+        <f t="shared" si="39"/>
+        <v>1.9704933179075101</v>
       </c>
       <c r="DC48">
-        <f t="shared" si="38"/>
-        <v>1.9043668706775756</v>
+        <f t="shared" si="39"/>
+        <v>2.0095403487230898</v>
       </c>
     </row>
     <row r="49" spans="2:107">
@@ -15540,127 +15684,129 @@
       <c r="BX49" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="BY49" s="51" t="s">
-        <v>70</v>
-      </c>
-      <c r="BZ49" s="51" t="s">
-        <v>70</v>
+      <c r="BY49">
+        <f>BY42/$BY42</f>
+        <v>1</v>
+      </c>
+      <c r="BZ49">
+        <f t="shared" ref="BZ49:DC49" si="40">BZ42/$BY42</f>
+        <v>0.98489903302041404</v>
       </c>
       <c r="CA49">
-        <f t="shared" ref="CA49:DC49" si="39">CA42/$CA42</f>
-        <v>1</v>
+        <f t="shared" si="40"/>
+        <v>0.97050375385972121</v>
       </c>
       <c r="CB49">
-        <f t="shared" si="39"/>
-        <v>1.0001708994431</v>
+        <f t="shared" si="40"/>
+        <v>0.97066961241078231</v>
       </c>
       <c r="CC49">
-        <f t="shared" si="39"/>
-        <v>1.009214507425255</v>
+        <f t="shared" si="40"/>
+        <v>0.9794464679058994</v>
       </c>
       <c r="CD49">
-        <f t="shared" si="39"/>
-        <v>1.0171842574343455</v>
+        <f t="shared" si="40"/>
+        <v>0.98718114020704517</v>
       </c>
       <c r="CE49">
-        <f t="shared" si="39"/>
-        <v>1.0262574126744008</v>
+        <f t="shared" si="40"/>
+        <v>0.99598667142687114</v>
       </c>
       <c r="CF49">
-        <f t="shared" si="39"/>
-        <v>1.0444174401676691</v>
+        <f t="shared" si="40"/>
+        <v>1.0136110462792836</v>
       </c>
       <c r="CG49">
-        <f t="shared" si="39"/>
-        <v>1.064749918155228</v>
+        <f t="shared" si="40"/>
+        <v>1.0333437924914797</v>
       </c>
       <c r="CH49">
-        <f t="shared" si="39"/>
-        <v>1.0869452550020162</v>
+        <f t="shared" si="40"/>
+        <v>1.0548844502194685</v>
       </c>
       <c r="CI49">
-        <f t="shared" si="39"/>
-        <v>1.1100619326099475</v>
+        <f t="shared" si="40"/>
+        <v>1.0773192726147309</v>
       </c>
       <c r="CJ49">
-        <f t="shared" si="39"/>
-        <v>1.1318192383762096</v>
+        <f t="shared" si="40"/>
+        <v>1.098434819534762</v>
       </c>
       <c r="CK49">
-        <f t="shared" si="39"/>
-        <v>1.1525980410067402</v>
+        <f t="shared" si="40"/>
+        <v>1.1186007254884021</v>
       </c>
       <c r="CL49">
-        <f t="shared" si="39"/>
-        <v>1.1725753073497514</v>
+        <f t="shared" si="40"/>
+        <v>1.1379887374661499</v>
       </c>
       <c r="CM49">
-        <f t="shared" si="39"/>
-        <v>1.1931481951424425</v>
+        <f t="shared" si="40"/>
+        <v>1.1579548022966917</v>
       </c>
       <c r="CN49">
-        <f t="shared" si="39"/>
-        <v>1.2044303256457414</v>
+        <f t="shared" si="40"/>
+        <v>1.1689041523016783</v>
       </c>
       <c r="CO49">
-        <f t="shared" si="39"/>
-        <v>1.2158195783392014</v>
+        <f t="shared" si="40"/>
+        <v>1.1799574647943383</v>
       </c>
       <c r="CP49">
-        <f t="shared" si="39"/>
-        <v>1.2273169752125808</v>
+        <f t="shared" si="40"/>
+        <v>1.191115731619568</v>
       </c>
       <c r="CQ49">
-        <f t="shared" si="39"/>
-        <v>1.2389235480596208</v>
+        <f t="shared" si="40"/>
+        <v>1.2023799541370666</v>
       </c>
       <c r="CR49">
-        <f t="shared" si="39"/>
-        <v>1.2506403385726872</v>
+        <f t="shared" si="40"/>
+        <v>1.2137511433131856</v>
       </c>
       <c r="CS49">
-        <f t="shared" si="39"/>
-        <v>1.2624683984383291</v>
+        <f t="shared" si="40"/>
+        <v>1.2252303198136687</v>
       </c>
       <c r="CT49">
-        <f t="shared" si="39"/>
-        <v>1.2744087894337681</v>
+        <f t="shared" si="40"/>
+        <v>1.2368185140972949</v>
       </c>
       <c r="CU49">
-        <f t="shared" si="39"/>
-        <v>1.2864625835243251</v>
+        <f t="shared" si="40"/>
+        <v>1.2485167665104326</v>
       </c>
       <c r="CV49">
-        <f t="shared" si="39"/>
-        <v>1.2986308629617951</v>
+        <f t="shared" si="40"/>
+        <v>1.260326127382511</v>
       </c>
       <c r="CW49">
-        <f t="shared" si="39"/>
-        <v>1.3109147203837772</v>
+        <f t="shared" si="40"/>
+        <v>1.2722476571224226</v>
       </c>
       <c r="CX49">
-        <f t="shared" si="39"/>
-        <v>1.3233152589139725</v>
+        <f t="shared" si="40"/>
+        <v>1.2842824263158592</v>
       </c>
       <c r="CY49">
-        <f t="shared" si="39"/>
-        <v>1.3358335922634561</v>
+        <f t="shared" si="40"/>
+        <v>1.2964315158236004</v>
       </c>
       <c r="CZ49">
-        <f t="shared" si="39"/>
-        <v>1.3484708448329339</v>
+        <f t="shared" si="40"/>
+        <v>1.308696016880752</v>
       </c>
       <c r="DA49">
-        <f t="shared" si="39"/>
-        <v>1.3612281518159957</v>
+        <f t="shared" si="40"/>
+        <v>1.3210770311969542</v>
       </c>
       <c r="DB49">
-        <f t="shared" si="39"/>
-        <v>1.3741066593033699</v>
+        <f t="shared" si="40"/>
+        <v>1.3335756710575615</v>
       </c>
       <c r="DC49">
-        <f t="shared" si="39"/>
-        <v>1.3871075243881965</v>
+        <f t="shared" si="40"/>
+        <v>1.3461930594258094</v>
       </c>
     </row>
     <row r="50" spans="2:107">
@@ -15688,127 +15834,129 @@
       <c r="BX50" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="BY50" s="51" t="s">
-        <v>70</v>
-      </c>
-      <c r="BZ50" s="51" t="s">
-        <v>70</v>
+      <c r="BY50">
+        <f>BY43/$BY43</f>
+        <v>1</v>
+      </c>
+      <c r="BZ50">
+        <f t="shared" ref="BZ50:DC50" si="41">BZ43/$BY43</f>
+        <v>1.0454112893996506</v>
       </c>
       <c r="CA50">
-        <f t="shared" ref="CA50:DC50" si="40">CA43/$CA43</f>
-        <v>1</v>
+        <f t="shared" si="41"/>
+        <v>1.0893508577345854</v>
       </c>
       <c r="CB50">
-        <f t="shared" si="40"/>
-        <v>1.0391022431085668</v>
+        <f t="shared" si="41"/>
+        <v>1.1319469198042491</v>
       </c>
       <c r="CC50">
-        <f t="shared" si="40"/>
-        <v>1.0772086552728033</v>
+        <f t="shared" si="41"/>
+        <v>1.1734581725805475</v>
       </c>
       <c r="CD50">
-        <f t="shared" si="40"/>
-        <v>1.1144731778907464</v>
+        <f t="shared" si="41"/>
+        <v>1.2140523122574738</v>
       </c>
       <c r="CE50">
-        <f t="shared" si="40"/>
-        <v>1.1511556983799791</v>
+        <f t="shared" si="41"/>
+        <v>1.2540124474162859</v>
       </c>
       <c r="CF50">
-        <f t="shared" si="40"/>
-        <v>1.1874629377873569</v>
+        <f t="shared" si="41"/>
+        <v>1.2935637698066877</v>
       </c>
       <c r="CG50">
-        <f t="shared" si="40"/>
-        <v>1.2234626702739224</v>
+        <f t="shared" si="41"/>
+        <v>1.3327801092691438</v>
       </c>
       <c r="CH50">
-        <f t="shared" si="40"/>
-        <v>1.2593669976871722</v>
+        <f t="shared" si="41"/>
+        <v>1.3718925191331508</v>
       </c>
       <c r="CI50">
-        <f t="shared" si="40"/>
-        <v>1.2953495264329522</v>
+        <f t="shared" si="41"/>
+        <v>1.4110901176858257</v>
       </c>
       <c r="CJ50">
-        <f t="shared" si="40"/>
-        <v>1.3302058407660233</v>
+        <f t="shared" si="41"/>
+        <v>1.449060873602023</v>
       </c>
       <c r="CK50">
-        <f t="shared" si="40"/>
-        <v>1.3642140993812044</v>
+        <f t="shared" si="41"/>
+        <v>1.48610779929453</v>
       </c>
       <c r="CL50">
-        <f t="shared" si="40"/>
-        <v>1.3974401182562519</v>
+        <f t="shared" si="41"/>
+        <v>1.5223025914551684</v>
       </c>
       <c r="CM50">
-        <f t="shared" si="40"/>
-        <v>1.430026235948473</v>
+        <f t="shared" si="41"/>
+        <v>1.5578003067134296</v>
       </c>
       <c r="CN50">
-        <f t="shared" si="40"/>
-        <v>1.4491197737976227</v>
+        <f t="shared" si="41"/>
+        <v>1.5785998685465887</v>
       </c>
       <c r="CO50">
-        <f t="shared" si="40"/>
-        <v>1.4684682462615599</v>
+        <f t="shared" si="41"/>
+        <v>1.5996771436210326</v>
       </c>
       <c r="CP50">
-        <f t="shared" si="40"/>
-        <v>1.4880750571965171</v>
+        <f t="shared" si="41"/>
+        <v>1.6210358399304683</v>
       </c>
       <c r="CQ50">
-        <f t="shared" si="40"/>
-        <v>1.5079436559066051</v>
+        <f t="shared" si="41"/>
+        <v>1.6426797149772867</v>
       </c>
       <c r="CR50">
-        <f t="shared" si="40"/>
-        <v>1.5280775377506273</v>
+        <f t="shared" si="41"/>
+        <v>1.6646125764335993</v>
       </c>
       <c r="CS50">
-        <f t="shared" si="40"/>
-        <v>1.5484802447569963</v>
+        <f t="shared" si="41"/>
+        <v>1.6868382828110948</v>
       </c>
       <c r="CT50">
-        <f t="shared" si="40"/>
-        <v>1.5691553662468611</v>
+        <f t="shared" si="41"/>
+        <v>1.7093607441398457</v>
       </c>
       <c r="CU50">
-        <f t="shared" si="40"/>
-        <v>1.5901065394655536</v>
+        <f t="shared" si="41"/>
+        <v>1.7321839226561744</v>
       </c>
       <c r="CV50">
-        <f t="shared" si="40"/>
-        <v>1.6113374502224667</v>
+        <f t="shared" si="41"/>
+        <v>1.755311833499704</v>
       </c>
       <c r="CW50">
-        <f t="shared" si="40"/>
-        <v>1.6328518335394759</v>
+        <f t="shared" si="41"/>
+        <v>1.7787485454197187</v>
       </c>
       <c r="CX50">
-        <f t="shared" si="40"/>
-        <v>1.6546534743080186</v>
+        <f t="shared" si="41"/>
+        <v>1.802498181490952</v>
       </c>
       <c r="CY50">
-        <f t="shared" si="40"/>
-        <v>1.6767462079549462</v>
+        <f t="shared" si="41"/>
+        <v>1.8265649198389342</v>
       </c>
       <c r="CZ50">
-        <f t="shared" si="40"/>
-        <v>1.699133921117266</v>
+        <f t="shared" si="41"/>
+        <v>1.8509529943750231</v>
       </c>
       <c r="DA50">
-        <f t="shared" si="40"/>
-        <v>1.7218205523258954</v>
+        <f t="shared" si="41"/>
+        <v>1.8756666955412518</v>
       </c>
       <c r="DB50">
-        <f t="shared" si="40"/>
-        <v>1.7448100926985401</v>
+        <f t="shared" si="41"/>
+        <v>1.9007103710651163</v>
       </c>
       <c r="DC50">
-        <f t="shared" si="40"/>
-        <v>1.7681065866418293</v>
+        <f t="shared" si="41"/>
+        <v>1.9260884267244469</v>
       </c>
     </row>
     <row r="51" spans="2:107">
@@ -15830,127 +15978,129 @@
       <c r="BX51" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="BY51" s="51" t="s">
-        <v>70</v>
-      </c>
-      <c r="BZ51" s="51" t="s">
-        <v>70</v>
+      <c r="BY51">
+        <f>BY44/$BY44</f>
+        <v>1</v>
+      </c>
+      <c r="BZ51">
+        <f t="shared" ref="BZ51:DC51" si="42">BZ44/$BY44</f>
+        <v>1.0385932627131045</v>
       </c>
       <c r="CA51">
-        <f t="shared" ref="CA51:DC51" si="41">CA44/$CA44</f>
-        <v>1</v>
+        <f t="shared" si="42"/>
+        <v>1.0784414487732614</v>
       </c>
       <c r="CB51">
-        <f t="shared" si="41"/>
-        <v>1.0387392462524345</v>
+        <f t="shared" si="42"/>
+        <v>1.1202194576261209</v>
       </c>
       <c r="CC51">
-        <f t="shared" si="41"/>
-        <v>1.0790492895406165</v>
+        <f t="shared" si="42"/>
+        <v>1.1636914791099409</v>
       </c>
       <c r="CD51">
-        <f t="shared" si="41"/>
-        <v>1.1205053065006412</v>
+        <f t="shared" si="42"/>
+        <v>1.2083993661006789</v>
       </c>
       <c r="CE51">
-        <f t="shared" si="41"/>
-        <v>1.1630675066617655</v>
+        <f t="shared" si="42"/>
+        <v>1.254300206905419</v>
       </c>
       <c r="CF51">
-        <f t="shared" si="41"/>
-        <v>1.2071588757340246</v>
+        <f t="shared" si="42"/>
+        <v>1.3018501668461027</v>
       </c>
       <c r="CG51">
-        <f t="shared" si="41"/>
-        <v>1.2525224703363345</v>
+        <f t="shared" si="42"/>
+        <v>1.3507721475305807</v>
       </c>
       <c r="CH51">
-        <f t="shared" si="41"/>
-        <v>1.2992423825058057</v>
+        <f t="shared" si="42"/>
+        <v>1.401156837297185</v>
       </c>
       <c r="CI51">
-        <f t="shared" si="41"/>
-        <v>1.3472606532030782</v>
+        <f t="shared" si="42"/>
+        <v>1.4529417307155381</v>
       </c>
       <c r="CJ51">
-        <f t="shared" si="41"/>
-        <v>1.3963475688467002</v>
+        <f t="shared" si="42"/>
+        <v>1.5058790951380567</v>
       </c>
       <c r="CK51">
-        <f t="shared" si="41"/>
-        <v>1.4464209892284916</v>
+        <f t="shared" si="42"/>
+        <v>1.5598803471596283</v>
       </c>
       <c r="CL51">
-        <f t="shared" si="41"/>
-        <v>1.4973369430490049</v>
+        <f t="shared" si="42"/>
+        <v>1.6147902221634951</v>
       </c>
       <c r="CM51">
-        <f t="shared" si="41"/>
-        <v>1.5491442146359522</v>
+        <f t="shared" si="42"/>
+        <v>1.6706613311907124</v>
       </c>
       <c r="CN51">
-        <f t="shared" si="41"/>
-        <v>1.5737401650449261</v>
+        <f t="shared" si="42"/>
+        <v>1.6971866235837214</v>
       </c>
       <c r="CO51">
-        <f t="shared" si="41"/>
-        <v>1.5987589600531527</v>
+        <f t="shared" si="42"/>
+        <v>1.7241679291189547</v>
       </c>
       <c r="CP51">
-        <f t="shared" si="41"/>
-        <v>1.6242081999237592</v>
+        <f t="shared" si="42"/>
+        <v>1.7516134442351898</v>
       </c>
       <c r="CQ51">
-        <f t="shared" si="41"/>
-        <v>1.650095624867453</v>
+        <f t="shared" si="42"/>
+        <v>1.779531516296476</v>
       </c>
       <c r="CR51">
-        <f t="shared" si="41"/>
-        <v>1.6764291176522408</v>
+        <f t="shared" si="42"/>
+        <v>1.8079306464065628</v>
       </c>
       <c r="CS51">
-        <f t="shared" si="41"/>
-        <v>1.7032167062621333</v>
+        <f t="shared" si="42"/>
+        <v>1.8368194922761574</v>
       </c>
       <c r="CT51">
-        <f t="shared" si="41"/>
-        <v>1.730466566605751</v>
+        <f t="shared" si="42"/>
+        <v>1.8662068711439974</v>
       </c>
       <c r="CU51">
-        <f t="shared" si="41"/>
-        <v>1.7581870252757765</v>
+        <f t="shared" si="42"/>
+        <v>1.8961017627527592</v>
       </c>
       <c r="CV51">
-        <f t="shared" si="41"/>
-        <v>1.7863865623602082</v>
+        <f t="shared" si="42"/>
+        <v>1.9265133123808289</v>
       </c>
       <c r="CW51">
-        <f t="shared" si="41"/>
-        <v>1.81507381430639</v>
+        <f t="shared" si="42"/>
+        <v>1.9574508339309926</v>
       </c>
       <c r="CX51">
-        <f t="shared" si="41"/>
-        <v>1.844257576838815</v>
+        <f t="shared" si="42"/>
+        <v>1.9889238130771161</v>
       </c>
       <c r="CY51">
-        <f t="shared" si="41"/>
-        <v>1.8739468079317096</v>
+        <f t="shared" si="42"/>
+        <v>2.0209419104699013</v>
       </c>
       <c r="CZ51">
-        <f t="shared" si="41"/>
-        <v>1.9041506308374387</v>
+        <f t="shared" si="42"/>
+        <v>2.0535149650028468</v>
       </c>
       <c r="DA51">
-        <f t="shared" si="41"/>
-        <v>1.934878337171771</v>
+        <f t="shared" si="42"/>
+        <v>2.0866529971395233</v>
       </c>
       <c r="DB51">
-        <f t="shared" si="41"/>
-        <v>1.9661393900570896</v>
+        <f t="shared" si="42"/>
+        <v>2.120366212303344</v>
       </c>
       <c r="DC51">
-        <f t="shared" si="41"/>
-        <v>1.9979434273246284</v>
+        <f t="shared" si="42"/>
+        <v>2.1546650043309876</v>
       </c>
     </row>
     <row r="52" spans="2:107">
@@ -15972,127 +16122,129 @@
       <c r="BX52" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="BY52" s="51" t="s">
-        <v>70</v>
-      </c>
-      <c r="BZ52" s="51" t="s">
-        <v>70</v>
+      <c r="BY52">
+        <f>BY45/$BY45</f>
+        <v>1</v>
+      </c>
+      <c r="BZ52">
+        <f t="shared" ref="BZ52:DC52" si="43">BZ45/$BY45</f>
+        <v>1.0385304103583184</v>
       </c>
       <c r="CA52">
-        <f t="shared" ref="CA52:DC52" si="42">CA45/$CA45</f>
-        <v>1</v>
+        <f t="shared" si="43"/>
+        <v>1.0767815246643786</v>
       </c>
       <c r="CB52">
-        <f t="shared" si="42"/>
-        <v>1.0366928505573572</v>
+        <f t="shared" si="43"/>
+        <v>1.116291708231812</v>
       </c>
       <c r="CC52">
-        <f t="shared" si="42"/>
-        <v>1.0747457226603214</v>
+        <f t="shared" si="43"/>
+        <v>1.1572663378727004</v>
       </c>
       <c r="CD52">
-        <f t="shared" si="42"/>
-        <v>1.1129713773465184</v>
+        <f t="shared" si="43"/>
+        <v>1.1984270166069975</v>
       </c>
       <c r="CE52">
-        <f t="shared" si="42"/>
-        <v>1.1508897605862682</v>
+        <f t="shared" si="43"/>
+        <v>1.2392568311247036</v>
       </c>
       <c r="CF52">
-        <f t="shared" si="42"/>
-        <v>1.1896502082696867</v>
+        <f t="shared" si="43"/>
+        <v>1.280993365077929</v>
       </c>
       <c r="CG52">
-        <f t="shared" si="42"/>
-        <v>1.2289208288140567</v>
+        <f t="shared" si="43"/>
+        <v>1.3232792437422118</v>
       </c>
       <c r="CH52">
-        <f t="shared" si="42"/>
-        <v>1.2685780737967898</v>
+        <f t="shared" si="43"/>
+        <v>1.3659814324587078</v>
       </c>
       <c r="CI52">
-        <f t="shared" si="42"/>
-        <v>1.308431797012628</v>
+        <f t="shared" si="43"/>
+        <v>1.4088951853066105</v>
       </c>
       <c r="CJ52">
-        <f t="shared" si="42"/>
-        <v>1.3476040478621698</v>
+        <f t="shared" si="43"/>
+        <v>1.4510751413009155</v>
       </c>
       <c r="CK52">
-        <f t="shared" si="42"/>
-        <v>1.3857333624672377</v>
+        <f t="shared" si="43"/>
+        <v>1.4921320828157683</v>
       </c>
       <c r="CL52">
-        <f t="shared" si="42"/>
-        <v>1.4234019521852281</v>
+        <f t="shared" si="43"/>
+        <v>1.5326929242842628</v>
       </c>
       <c r="CM52">
-        <f t="shared" si="42"/>
-        <v>1.4613884740306986</v>
+        <f t="shared" si="43"/>
+        <v>1.5735961091937254</v>
       </c>
       <c r="CN52">
-        <f t="shared" si="42"/>
-        <v>1.4779253094881875</v>
+        <f t="shared" si="43"/>
+        <v>1.5914026680907642</v>
       </c>
       <c r="CO52">
-        <f t="shared" si="42"/>
-        <v>1.4946509724334369</v>
+        <f t="shared" si="43"/>
+        <v>1.6094125529379724</v>
       </c>
       <c r="CP52">
-        <f t="shared" si="42"/>
-        <v>1.5115676386059371</v>
+        <f t="shared" si="43"/>
+        <v>1.6276281065314355</v>
       </c>
       <c r="CQ52">
-        <f t="shared" si="42"/>
-        <v>1.5286775090439715</v>
+        <f t="shared" si="43"/>
+        <v>1.6460516989085121</v>
       </c>
       <c r="CR52">
-        <f t="shared" si="42"/>
-        <v>1.5459828103814854</v>
+        <f t="shared" si="43"/>
+        <v>1.6646857276674969</v>
       </c>
       <c r="CS52">
-        <f t="shared" si="42"/>
-        <v>1.5634857951484729</v>
+        <f t="shared" si="43"/>
+        <v>1.683532618291071</v>
       </c>
       <c r="CT52">
-        <f t="shared" si="42"/>
-        <v>1.58118874207492</v>
+        <f t="shared" si="43"/>
+        <v>1.7025948244735833</v>
       </c>
       <c r="CU52">
-        <f t="shared" si="42"/>
-        <v>1.5990939563983482</v>
+        <f t="shared" si="43"/>
+        <v>1.7218748284522067</v>
       </c>
       <c r="CV52">
-        <f t="shared" si="42"/>
-        <v>1.6172037701750008</v>
+        <f t="shared" si="43"/>
+        <v>1.7413751413420189</v>
       </c>
       <c r="CW52">
-        <f t="shared" si="42"/>
-        <v>1.635520542594719</v>
+        <f t="shared" si="43"/>
+        <v>1.7610983034750534</v>
       </c>
       <c r="CX52">
-        <f t="shared" si="42"/>
-        <v>1.6540466602995441</v>
+        <f t="shared" si="43"/>
+        <v>1.7810468847433665</v>
       </c>
       <c r="CY52">
-        <f t="shared" si="42"/>
-        <v>1.672784537706099</v>
+        <f t="shared" si="43"/>
+        <v>1.8012234849461712</v>
       </c>
       <c r="CZ52">
-        <f t="shared" si="42"/>
-        <v>1.6917366173317909</v>
+        <f t="shared" si="43"/>
+        <v>1.8216307341410845</v>
       </c>
       <c r="DA52">
-        <f t="shared" si="42"/>
-        <v>1.7109053701248744</v>
+        <f t="shared" si="43"/>
+        <v>1.8422712929995353</v>
       </c>
       <c r="DB52">
-        <f t="shared" si="42"/>
-        <v>1.7302932957984352</v>
+        <f t="shared" si="43"/>
+        <v>1.8631478531663916</v>
       </c>
       <c r="DC52">
-        <f t="shared" si="42"/>
-        <v>1.7499029231683283</v>
+        <f t="shared" si="43"/>
+        <v>1.8842631376238455</v>
       </c>
     </row>
     <row r="53" spans="2:107">
@@ -17025,8 +17177,12 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
+      <c r="F12" s="1">
+        <v>2020</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2021</v>
+      </c>
       <c r="H12" s="1">
         <v>2022</v>
       </c>
@@ -17182,121 +17338,129 @@
       <c r="D13" t="s">
         <v>64</v>
       </c>
+      <c r="F13">
+        <f>F3/$F3</f>
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <f t="shared" ref="G13:AJ13" si="2">G3/$F3</f>
+        <v>1.0086705202312138</v>
+      </c>
       <c r="H13">
-        <f t="shared" ref="H13:AJ13" si="2">H3/$H3</f>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>1.0144508670520231</v>
       </c>
       <c r="I13">
         <f t="shared" si="2"/>
-        <v>1.0199430199430197</v>
+        <v>1.0346820809248554</v>
       </c>
       <c r="J13">
         <f t="shared" si="2"/>
-        <v>1.0256410256410255</v>
+        <v>1.0404624277456647</v>
       </c>
       <c r="K13">
         <f t="shared" si="2"/>
-        <v>1.0427350427350428</v>
+        <v>1.0578034682080926</v>
       </c>
       <c r="L13">
         <f t="shared" si="2"/>
-        <v>1.0512820512820511</v>
+        <v>1.0664739884393062</v>
       </c>
       <c r="M13">
         <f t="shared" si="2"/>
-        <v>1.0569800569800569</v>
+        <v>1.0722543352601157</v>
       </c>
       <c r="N13">
         <f t="shared" si="2"/>
-        <v>1.054131054131054</v>
+        <v>1.0693641618497109</v>
       </c>
       <c r="O13">
         <f t="shared" si="2"/>
-        <v>1.054131054131054</v>
+        <v>1.0693641618497109</v>
       </c>
       <c r="P13">
         <f t="shared" si="2"/>
-        <v>1.054131054131054</v>
+        <v>1.0693641618497109</v>
       </c>
       <c r="Q13">
         <f t="shared" si="2"/>
-        <v>1.0484330484330484</v>
+        <v>1.0635838150289016</v>
       </c>
       <c r="R13">
         <f t="shared" si="2"/>
-        <v>1.048433048433048</v>
+        <v>1.0635838150289012</v>
       </c>
       <c r="S13">
         <f t="shared" si="2"/>
-        <v>1.0467236467236458</v>
+        <v>1.0618497109826579</v>
       </c>
       <c r="T13">
         <f t="shared" si="2"/>
-        <v>1.0442165242165238</v>
+        <v>1.0593063583815026</v>
       </c>
       <c r="U13">
         <f t="shared" si="2"/>
-        <v>1.0419259259259255</v>
+        <v>1.0569826589595372</v>
       </c>
       <c r="V13">
         <f t="shared" si="2"/>
-        <v>1.0407772079772073</v>
+        <v>1.0558173410404619</v>
       </c>
       <c r="W13">
         <f t="shared" si="2"/>
-        <v>1.0383824501424503</v>
+        <v>1.0533879768786127</v>
       </c>
       <c r="X13">
         <f t="shared" si="2"/>
-        <v>1.0363686381766388</v>
+        <v>1.0513450635838157</v>
       </c>
       <c r="Y13">
         <f t="shared" si="2"/>
-        <v>1.034562374928776</v>
+        <v>1.0495126982658969</v>
       </c>
       <c r="Z13">
         <f t="shared" si="2"/>
-        <v>1.0326626178917397</v>
+        <v>1.0475854880924873</v>
       </c>
       <c r="AA13">
         <f t="shared" si="2"/>
-        <v>1.0305358812079797</v>
+        <v>1.0454280182196556</v>
       </c>
       <c r="AB13">
         <f t="shared" si="2"/>
-        <v>1.0286826450233648</v>
+        <v>1.0435480011653209</v>
       </c>
       <c r="AC13">
         <f t="shared" si="2"/>
-        <v>1.0267428874374971</v>
+        <v>1.0415802124004667</v>
       </c>
       <c r="AD13">
         <f t="shared" si="2"/>
-        <v>1.0247515969425922</v>
+        <v>1.0395601460313579</v>
       </c>
       <c r="AE13">
         <f t="shared" si="2"/>
-        <v>1.0227906150000019</v>
+        <v>1.0375708261994239</v>
       </c>
       <c r="AF13">
         <f t="shared" si="2"/>
-        <v>1.0208742509732691</v>
+        <v>1.0356267690509176</v>
       </c>
       <c r="AG13">
         <f t="shared" si="2"/>
-        <v>1.0188976809140393</v>
+        <v>1.0336216358405428</v>
       </c>
       <c r="AH13">
         <f t="shared" si="2"/>
-        <v>1.016941078548609</v>
+        <v>1.0316367588744559</v>
       </c>
       <c r="AI13">
         <f t="shared" si="2"/>
-        <v>1.0149968532135234</v>
+        <v>1.0296644377975339</v>
       </c>
       <c r="AJ13">
         <f t="shared" si="2"/>
-        <v>1.0130438869306038</v>
+        <v>1.0276832494585026</v>
       </c>
     </row>
     <row r="14" spans="1:56">
@@ -17306,121 +17470,129 @@
       <c r="D14" t="s">
         <v>66</v>
       </c>
+      <c r="F14">
+        <f>F4/$F4</f>
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <f t="shared" ref="G14:AJ14" si="3">G4/$F4</f>
+        <v>1</v>
+      </c>
       <c r="H14">
-        <f t="shared" ref="H14:AJ14" si="3">H4/$H4</f>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>1.1111111111111112</v>
       </c>
       <c r="I14">
         <f t="shared" si="3"/>
-        <v>1.1000000000000001</v>
+        <v>1.2222222222222223</v>
       </c>
       <c r="J14">
         <f t="shared" si="3"/>
-        <v>1.1000000000000001</v>
+        <v>1.2222222222222223</v>
       </c>
       <c r="K14">
         <f t="shared" si="3"/>
-        <v>1.2</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="L14">
         <f t="shared" si="3"/>
-        <v>1.3</v>
+        <v>1.4444444444444444</v>
       </c>
       <c r="M14">
         <f t="shared" si="3"/>
-        <v>1.3</v>
+        <v>1.4444444444444444</v>
       </c>
       <c r="N14">
         <f t="shared" si="3"/>
-        <v>1.4</v>
+        <v>1.5555555555555554</v>
       </c>
       <c r="O14">
         <f t="shared" si="3"/>
-        <v>1.4</v>
+        <v>1.5555555555555554</v>
       </c>
       <c r="P14">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>1.6666666666666665</v>
       </c>
       <c r="Q14">
         <f t="shared" si="3"/>
-        <v>1.6</v>
+        <v>1.7777777777777779</v>
       </c>
       <c r="R14">
         <f t="shared" si="3"/>
-        <v>1.6500000000000057</v>
+        <v>1.8333333333333397</v>
       </c>
       <c r="S14">
         <f t="shared" si="3"/>
-        <v>1.7199999999999989</v>
+        <v>1.9111111111111099</v>
       </c>
       <c r="T14">
         <f t="shared" si="3"/>
-        <v>1.8110000000000355</v>
+        <v>2.0122222222222614</v>
       </c>
       <c r="U14">
         <f t="shared" si="3"/>
-        <v>1.8788000000000125</v>
+        <v>2.0875555555555692</v>
       </c>
       <c r="V14">
         <f t="shared" si="3"/>
-        <v>1.947540000000032</v>
+        <v>2.163933333333369</v>
       </c>
       <c r="W14">
         <f t="shared" si="3"/>
-        <v>2.0276320000000396</v>
+        <v>2.2529244444444885</v>
       </c>
       <c r="X14">
         <f t="shared" si="3"/>
-        <v>2.1025356000000386</v>
+        <v>2.3361506666667093</v>
       </c>
       <c r="Y14">
         <f t="shared" si="3"/>
-        <v>2.1730724800000587</v>
+        <v>2.4145249777778428</v>
       </c>
       <c r="Z14">
         <f t="shared" si="3"/>
-        <v>2.2489781840000376</v>
+        <v>2.4988646488889308</v>
       </c>
       <c r="AA14">
         <f t="shared" si="3"/>
-        <v>2.3244467072000532</v>
+        <v>2.5827185635556145</v>
       </c>
       <c r="AB14">
         <f t="shared" si="3"/>
-        <v>2.3973545937600704</v>
+        <v>2.6637273264000783</v>
       </c>
       <c r="AC14">
         <f t="shared" si="3"/>
-        <v>2.4715811774080692</v>
+        <v>2.7462013082311878</v>
       </c>
       <c r="AD14">
         <f t="shared" si="3"/>
-        <v>2.5467047698464569</v>
+        <v>2.829671966496063</v>
       </c>
       <c r="AE14">
         <f t="shared" si="3"/>
-        <v>2.6205893790132109</v>
+        <v>2.9117659766813455</v>
       </c>
       <c r="AF14">
         <f t="shared" si="3"/>
-        <v>2.694625981359394</v>
+        <v>2.9940288681771046</v>
       </c>
       <c r="AG14">
         <f t="shared" si="3"/>
-        <v>2.7692364733185855</v>
+        <v>3.0769294147984283</v>
       </c>
       <c r="AH14">
         <f t="shared" si="3"/>
-        <v>2.8435170971893342</v>
+        <v>3.1594634413214822</v>
       </c>
       <c r="AI14">
         <f t="shared" si="3"/>
-        <v>2.9176162648427066</v>
+        <v>3.2417958498252295</v>
       </c>
       <c r="AJ14">
         <f t="shared" si="3"/>
-        <v>2.9920005053913314</v>
+        <v>3.3244450059903681</v>
       </c>
     </row>
     <row r="15" spans="1:56">
@@ -17433,121 +17605,129 @@
       <c r="D15" t="s">
         <v>85</v>
       </c>
+      <c r="F15">
+        <f>F5/$F5</f>
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <f t="shared" ref="G15:AJ15" si="4">G5/$F5</f>
+        <v>1.0286054827175208</v>
+      </c>
       <c r="H15">
-        <f t="shared" ref="H15:AJ15" si="4">H5/$H5</f>
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>1.0584028605482716</v>
       </c>
       <c r="I15">
         <f t="shared" si="4"/>
-        <v>1.0292792792792793</v>
+        <v>1.0893921334922527</v>
       </c>
       <c r="J15">
         <f t="shared" si="4"/>
-        <v>1.0585585585585586</v>
+        <v>1.1203814064362336</v>
       </c>
       <c r="K15">
         <f t="shared" si="4"/>
-        <v>1.0889639639639641</v>
+        <v>1.1525625744934445</v>
       </c>
       <c r="L15">
         <f t="shared" si="4"/>
-        <v>1.1204954954954955</v>
+        <v>1.1859356376638854</v>
       </c>
       <c r="M15">
         <f t="shared" si="4"/>
-        <v>1.1542792792792793</v>
+        <v>1.2216924910607865</v>
       </c>
       <c r="N15">
         <f t="shared" si="4"/>
-        <v>1.1880630630630631</v>
+        <v>1.2574493444576877</v>
       </c>
       <c r="O15">
         <f t="shared" si="4"/>
-        <v>1.222972972972973</v>
+        <v>1.2943980929678187</v>
       </c>
       <c r="P15">
         <f t="shared" si="4"/>
-        <v>1.2601351351351353</v>
+        <v>1.33373063170441</v>
       </c>
       <c r="Q15">
         <f t="shared" si="4"/>
-        <v>1.2972972972972974</v>
+        <v>1.3730631704410012</v>
       </c>
       <c r="R15">
         <f t="shared" si="4"/>
-        <v>1.3319819819819791</v>
+        <v>1.4097735399284832</v>
       </c>
       <c r="S15">
         <f t="shared" si="4"/>
-        <v>1.3687387387387373</v>
+        <v>1.4486769964243129</v>
       </c>
       <c r="T15">
         <f t="shared" si="4"/>
-        <v>1.4052387387387315</v>
+        <v>1.4873087008343187</v>
       </c>
       <c r="U15">
         <f t="shared" si="4"/>
-        <v>1.4411729729729748</v>
+        <v>1.5253415971394535</v>
       </c>
       <c r="V15">
         <f t="shared" si="4"/>
-        <v>1.4771883783783688</v>
+        <v>1.5634604052443282</v>
       </c>
       <c r="W15">
         <f t="shared" si="4"/>
-        <v>1.5137182702702676</v>
+        <v>1.6021237473182328</v>
       </c>
       <c r="X15">
         <f t="shared" si="4"/>
-        <v>1.5497840306306283</v>
+        <v>1.6402958512514874</v>
       </c>
       <c r="Y15">
         <f t="shared" si="4"/>
-        <v>1.585911242522515</v>
+        <v>1.6785329956614938</v>
       </c>
       <c r="Z15">
         <f t="shared" si="4"/>
-        <v>1.6221766363603489</v>
+        <v>1.7169163922383666</v>
       </c>
       <c r="AA15">
         <f t="shared" si="4"/>
-        <v>1.6584065580972849</v>
+        <v>1.7552622450421798</v>
       </c>
       <c r="AB15">
         <f t="shared" si="4"/>
-        <v>1.6945301019913346</v>
+        <v>1.7934955072327829</v>
       </c>
       <c r="AC15">
         <f t="shared" si="4"/>
-        <v>1.7307579514092779</v>
+        <v>1.8318391666882463</v>
       </c>
       <c r="AD15">
         <f t="shared" si="4"/>
-        <v>1.7669705630974966</v>
+        <v>1.8701666984869807</v>
       </c>
       <c r="AE15">
         <f t="shared" si="4"/>
-        <v>1.8031501362270319</v>
+        <v>1.9084592621806964</v>
       </c>
       <c r="AF15">
         <f t="shared" si="4"/>
-        <v>1.839341347374178</v>
+        <v>1.9467641435855421</v>
       </c>
       <c r="AG15">
         <f t="shared" si="4"/>
-        <v>1.8755544226949061</v>
+        <v>1.9850921660942509</v>
       </c>
       <c r="AH15">
         <f t="shared" si="4"/>
-        <v>1.9117440022149585</v>
+        <v>2.0233953205803132</v>
       </c>
       <c r="AI15">
         <f t="shared" si="4"/>
-        <v>1.9479374437325638</v>
+        <v>2.0617025626156336</v>
       </c>
       <c r="AJ15">
         <f t="shared" si="4"/>
-        <v>1.984138651404278</v>
+        <v>2.1000180243706779</v>
       </c>
     </row>
     <row r="16" spans="1:56">
@@ -17560,121 +17740,129 @@
       <c r="D16" t="s">
         <v>78</v>
       </c>
+      <c r="F16">
+        <f>F6/$F6</f>
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <f t="shared" ref="G16:AJ16" si="5">G6/$F6</f>
+        <v>1.0335570469798658</v>
+      </c>
       <c r="H16">
-        <f t="shared" ref="H16:AJ16" si="5">H6/$H6</f>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>1.0671140939597314</v>
       </c>
       <c r="I16">
         <f t="shared" si="5"/>
-        <v>1.0314465408805031</v>
+        <v>1.1006711409395973</v>
       </c>
       <c r="J16">
         <f t="shared" si="5"/>
-        <v>1.0628930817610063</v>
+        <v>1.1342281879194629</v>
       </c>
       <c r="K16">
         <f t="shared" si="5"/>
-        <v>1.0943396226415094</v>
+        <v>1.1677852348993287</v>
       </c>
       <c r="L16">
         <f t="shared" si="5"/>
-        <v>1.1257861635220126</v>
+        <v>1.2013422818791946</v>
       </c>
       <c r="M16">
         <f t="shared" si="5"/>
-        <v>1.1635220125786163</v>
+        <v>1.2416107382550334</v>
       </c>
       <c r="N16">
         <f t="shared" si="5"/>
-        <v>1.1949685534591195</v>
+        <v>1.2751677852348993</v>
       </c>
       <c r="O16">
         <f t="shared" si="5"/>
-        <v>1.2327044025157234</v>
+        <v>1.3154362416107384</v>
       </c>
       <c r="P16">
         <f t="shared" si="5"/>
-        <v>1.270440251572327</v>
+        <v>1.355704697986577</v>
       </c>
       <c r="Q16">
         <f t="shared" si="5"/>
-        <v>1.3081761006289307</v>
+        <v>1.3959731543624161</v>
       </c>
       <c r="R16">
         <f t="shared" si="5"/>
-        <v>1.343396226415088</v>
+        <v>1.4335570469798591</v>
       </c>
       <c r="S16">
         <f t="shared" si="5"/>
-        <v>1.3816352201257909</v>
+        <v>1.4743624161073876</v>
       </c>
       <c r="T16">
         <f t="shared" si="5"/>
-        <v>1.4185157232704393</v>
+        <v>1.5137181208053683</v>
       </c>
       <c r="U16">
         <f t="shared" si="5"/>
-        <v>1.455315723270437</v>
+        <v>1.5529879194630838</v>
       </c>
       <c r="V16">
         <f t="shared" si="5"/>
-        <v>1.4922274213836459</v>
+        <v>1.592376912751676</v>
       </c>
       <c r="W16">
         <f t="shared" si="5"/>
-        <v>1.5296209308176061</v>
+        <v>1.6322800536912707</v>
       </c>
       <c r="X16">
         <f t="shared" si="5"/>
-        <v>1.5663679396226406</v>
+        <v>1.6714933046979856</v>
       </c>
       <c r="Y16">
         <f t="shared" si="5"/>
-        <v>1.6034124397484195</v>
+        <v>1.7110240128858973</v>
       </c>
       <c r="Z16">
         <f t="shared" si="5"/>
-        <v>1.640489076327035</v>
+        <v>1.7505890143355607</v>
       </c>
       <c r="AA16">
         <f t="shared" si="5"/>
-        <v>1.6775180072251468</v>
+        <v>1.7901031083811969</v>
       </c>
       <c r="AB16">
         <f t="shared" si="5"/>
-        <v>1.7144562656039994</v>
+        <v>1.8295204445035969</v>
       </c>
       <c r="AC16">
         <f t="shared" si="5"/>
-        <v>1.7515334115372718</v>
+        <v>1.8690859894927934</v>
       </c>
       <c r="AD16">
         <f t="shared" si="5"/>
-        <v>1.7885445799447695</v>
+        <v>1.9085811289343513</v>
       </c>
       <c r="AE16">
         <f t="shared" si="5"/>
-        <v>1.8255461915919113</v>
+        <v>1.948066070222241</v>
       </c>
       <c r="AF16">
         <f t="shared" si="5"/>
-        <v>1.8625630961028981</v>
+        <v>1.9875673307406765</v>
       </c>
       <c r="AG16">
         <f t="shared" si="5"/>
-        <v>1.8995966412718996</v>
+        <v>2.0270863487398123</v>
       </c>
       <c r="AH16">
         <f t="shared" si="5"/>
-        <v>1.9366002767779609</v>
+        <v>2.066573449716079</v>
       </c>
       <c r="AI16">
         <f t="shared" si="5"/>
-        <v>1.973618710141805</v>
+        <v>2.1060763416949464</v>
       </c>
       <c r="AJ16">
         <f t="shared" si="5"/>
-        <v>2.0106396485097457</v>
+        <v>2.1455819067989905</v>
       </c>
     </row>
     <row r="17" spans="1:36">
@@ -17687,12 +17875,20 @@
       <c r="D17" t="s">
         <v>88</v>
       </c>
+      <c r="F17">
+        <f>MAX(1,F7/$F7)</f>
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <f t="shared" ref="G17:AJ17" si="6">MAX(1,G7/$F7)</f>
+        <v>1</v>
+      </c>
       <c r="H17">
-        <f>MAX(1,H7/$H7)</f>
+        <f>MAX(1,H7/$F7)</f>
         <v>1</v>
       </c>
       <c r="I17">
-        <f t="shared" ref="H17:AJ17" si="6">MAX(1,I7/$H7)</f>
+        <f t="shared" si="6"/>
         <v>1.0075187969924813</v>
       </c>
       <c r="J17">
@@ -17815,14 +18011,14 @@
   <sheetPr>
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="B2:BB44"/>
+  <dimension ref="B2:BD44"/>
   <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:54" ht="29.25" customHeight="1">
+    <row r="2" spans="2:56" ht="29.25" customHeight="1">
       <c r="B2" s="44" t="s">
         <v>90</v>
       </c>
@@ -17832,13 +18028,13 @@
       <c r="D2" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="F2" s="46" t="s">
+      <c r="H2" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="48"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="48"/>
     </row>
-    <row r="3" spans="2:54">
+    <row r="3" spans="2:56">
       <c r="B3" s="49">
         <v>2009</v>
       </c>
@@ -17847,154 +18043,160 @@
       </c>
       <c r="D3" s="49"/>
       <c r="F3">
+        <v>2020</v>
+      </c>
+      <c r="G3">
+        <v>2021</v>
+      </c>
+      <c r="H3">
         <v>2022</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>2023</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>2024</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>2025</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>2026</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>2027</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>2028</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>2029</v>
       </c>
-      <c r="N3">
+      <c r="P3">
         <v>2030</v>
       </c>
-      <c r="O3">
+      <c r="Q3">
         <v>2031</v>
       </c>
-      <c r="P3">
+      <c r="R3">
         <v>2032</v>
       </c>
-      <c r="Q3">
+      <c r="S3">
         <v>2033</v>
       </c>
-      <c r="R3">
+      <c r="T3">
         <v>2034</v>
       </c>
-      <c r="S3">
+      <c r="U3">
         <v>2035</v>
       </c>
-      <c r="T3">
+      <c r="V3">
         <v>2036</v>
       </c>
-      <c r="U3">
+      <c r="W3">
         <v>2037</v>
       </c>
-      <c r="V3">
+      <c r="X3">
         <v>2038</v>
       </c>
-      <c r="W3">
+      <c r="Y3">
         <v>2039</v>
       </c>
-      <c r="X3">
+      <c r="Z3">
         <v>2040</v>
       </c>
-      <c r="Y3">
+      <c r="AA3">
         <v>2041</v>
       </c>
-      <c r="Z3">
+      <c r="AB3">
         <v>2042</v>
       </c>
-      <c r="AA3">
+      <c r="AC3">
         <v>2043</v>
       </c>
-      <c r="AB3">
+      <c r="AD3">
         <v>2044</v>
       </c>
-      <c r="AC3">
+      <c r="AE3">
         <v>2045</v>
       </c>
-      <c r="AD3">
+      <c r="AF3">
         <v>2046</v>
       </c>
-      <c r="AE3">
+      <c r="AG3">
         <v>2047</v>
       </c>
-      <c r="AF3">
+      <c r="AH3">
         <v>2048</v>
       </c>
-      <c r="AG3">
+      <c r="AI3">
         <v>2049</v>
       </c>
-      <c r="AH3">
+      <c r="AJ3">
         <v>2050</v>
       </c>
-      <c r="AI3" s="1">
+      <c r="AK3" s="1">
         <v>2051</v>
       </c>
-      <c r="AJ3" s="1">
+      <c r="AL3" s="1">
         <v>2052</v>
       </c>
-      <c r="AK3" s="1">
+      <c r="AM3" s="1">
         <v>2053</v>
       </c>
-      <c r="AL3" s="1">
+      <c r="AN3" s="1">
         <v>2054</v>
       </c>
-      <c r="AM3" s="1">
+      <c r="AO3" s="1">
         <v>2055</v>
       </c>
-      <c r="AN3" s="1">
+      <c r="AP3" s="1">
         <v>2056</v>
       </c>
-      <c r="AO3" s="1">
+      <c r="AQ3" s="1">
         <v>2057</v>
       </c>
-      <c r="AP3" s="1">
+      <c r="AR3" s="1">
         <v>2058</v>
       </c>
-      <c r="AQ3" s="1">
+      <c r="AS3" s="1">
         <v>2059</v>
       </c>
-      <c r="AR3" s="1">
+      <c r="AT3" s="1">
         <v>2060</v>
       </c>
-      <c r="AS3" s="1">
+      <c r="AU3" s="1">
         <v>2061</v>
       </c>
-      <c r="AT3" s="1">
+      <c r="AV3" s="1">
         <v>2062</v>
       </c>
-      <c r="AU3" s="1">
+      <c r="AW3" s="1">
         <v>2063</v>
       </c>
-      <c r="AV3" s="1">
+      <c r="AX3" s="1">
         <v>2064</v>
       </c>
-      <c r="AW3" s="1">
+      <c r="AY3" s="1">
         <v>2065</v>
       </c>
-      <c r="AX3" s="1">
+      <c r="AZ3" s="1">
         <v>2066</v>
       </c>
-      <c r="AY3" s="1">
+      <c r="BA3" s="1">
         <v>2067</v>
       </c>
-      <c r="AZ3" s="1">
+      <c r="BB3" s="1">
         <v>2068</v>
       </c>
-      <c r="BA3" s="1">
+      <c r="BC3" s="1">
         <v>2069</v>
       </c>
-      <c r="BB3" s="1">
+      <c r="BD3" s="1">
         <v>2070</v>
       </c>
     </row>
-    <row r="4" spans="2:54">
+    <row r="4" spans="2:56">
       <c r="B4" s="49">
         <v>2010</v>
       </c>
@@ -18002,204 +18204,182 @@
         <v>1154145</v>
       </c>
       <c r="D4" s="49"/>
-      <c r="F4">
-        <f>D16</f>
+      <c r="F4" cm="1">
+        <f t="array" ref="F4:AJ4">TRANSPOSE(D14:D44)</f>
         <v>1</v>
       </c>
       <c r="G4">
-        <f>D17</f>
-        <v>1.0590871647245823</v>
+        <v>1.0670054940538001</v>
       </c>
       <c r="H4">
-        <f>D18</f>
-        <v>1.1181743294491644</v>
+        <v>1.1340109881076001</v>
       </c>
       <c r="I4">
-        <f>D19</f>
-        <v>1.1772614941737467</v>
+        <v>1.2010164821614002</v>
       </c>
       <c r="J4">
-        <f>D20</f>
-        <v>1.236348658898329</v>
+        <v>1.2680219762152003</v>
       </c>
       <c r="K4">
-        <f>D21</f>
-        <v>1.2954358236229113</v>
+        <v>1.3350274702690004</v>
       </c>
       <c r="L4">
-        <f>D22</f>
-        <v>1.3545229883474934</v>
+        <v>1.4020329643228002</v>
       </c>
       <c r="M4">
-        <f>D23</f>
-        <v>1.4136101530720757</v>
+        <v>1.4690384583766003</v>
       </c>
       <c r="N4">
-        <f>D24</f>
-        <v>1.472697317796658</v>
+        <v>1.5360439524304004</v>
       </c>
       <c r="O4">
-        <f>D25</f>
-        <v>1.5317844825212403</v>
+        <v>1.6030494464842004</v>
       </c>
       <c r="P4">
-        <f>D26</f>
-        <v>1.5908716472458224</v>
+        <v>1.6700549405380005</v>
       </c>
       <c r="Q4">
-        <f>D27</f>
-        <v>1.6499588119704047</v>
+        <v>1.7370604345918006</v>
       </c>
       <c r="R4">
-        <f>D28</f>
-        <v>1.709045976694987</v>
+        <v>1.8040659286456007</v>
       </c>
       <c r="S4">
-        <f>D29</f>
-        <v>1.7681331414195693</v>
+        <v>1.8710714226994007</v>
       </c>
       <c r="T4">
-        <f>D30</f>
-        <v>1.8272203061441514</v>
+        <v>1.9380769167532008</v>
       </c>
       <c r="U4">
-        <f>D31</f>
-        <v>1.8863074708687337</v>
+        <v>2.0050824108070007</v>
       </c>
       <c r="V4">
-        <f>D32</f>
-        <v>1.945394635593316</v>
+        <v>2.0720879048608007</v>
       </c>
       <c r="W4">
-        <f>D33</f>
-        <v>2.0044818003178984</v>
+        <v>2.1390933989146008</v>
       </c>
       <c r="X4">
-        <f>D34</f>
-        <v>2.0635689650424807</v>
+        <v>2.2060988929684009</v>
       </c>
       <c r="Y4">
-        <f>D35</f>
-        <v>2.122656129767063</v>
+        <v>2.273104387022201</v>
       </c>
       <c r="Z4">
-        <f>D36</f>
-        <v>2.1817432944916448</v>
+        <v>2.340109881076001</v>
       </c>
       <c r="AA4">
-        <f>D37</f>
-        <v>2.2408304592162271</v>
+        <v>2.4071153751298011</v>
       </c>
       <c r="AB4">
-        <f>D38</f>
-        <v>2.2999176239408095</v>
+        <v>2.4741208691836012</v>
       </c>
       <c r="AC4">
-        <f>D39</f>
-        <v>2.3590047886653918</v>
+        <v>2.5411263632374013</v>
       </c>
       <c r="AD4">
-        <f>D40</f>
-        <v>2.4180919533899741</v>
+        <v>2.6081318572912013</v>
       </c>
       <c r="AE4">
-        <f>D41</f>
-        <v>2.4771791181145564</v>
+        <v>2.6751373513450014</v>
       </c>
       <c r="AF4">
-        <f>D42</f>
-        <v>2.5362662828391387</v>
+        <v>2.7421428453988015</v>
       </c>
       <c r="AG4">
-        <f>D43</f>
-        <v>2.595353447563721</v>
+        <v>2.8091483394526016</v>
       </c>
       <c r="AH4">
-        <f>D44</f>
-        <v>2.6544406122883029</v>
-      </c>
-      <c r="AI4" s="5">
-        <f t="shared" ref="AI4:BB4" si="0">AH4+(AH4-AC4)/5</f>
-        <v>2.7135277770128852</v>
-      </c>
-      <c r="AJ4" s="5">
-        <f t="shared" si="0"/>
-        <v>2.7726149417374675</v>
+        <v>2.8761538335064016</v>
+      </c>
+      <c r="AI4">
+        <v>2.9431593275602017</v>
+      </c>
+      <c r="AJ4">
+        <v>3.0101648216140018</v>
       </c>
       <c r="AK4" s="5">
-        <f t="shared" si="0"/>
-        <v>2.8317021064620498</v>
+        <f t="shared" ref="AK4:BD4" si="0">AJ4+(AJ4-AE4)/5</f>
+        <v>3.0771703156678019</v>
       </c>
       <c r="AL4" s="5">
         <f t="shared" si="0"/>
-        <v>2.8907892711866321</v>
+        <v>3.1441758097216019</v>
       </c>
       <c r="AM4" s="5">
         <f t="shared" si="0"/>
-        <v>2.9498764359112144</v>
+        <v>3.211181303775402</v>
       </c>
       <c r="AN4" s="5">
         <f t="shared" si="0"/>
-        <v>3.0089636006357967</v>
+        <v>3.2781867978292021</v>
       </c>
       <c r="AO4" s="5">
         <f t="shared" si="0"/>
-        <v>3.068050765360379</v>
+        <v>3.3451922918830022</v>
       </c>
       <c r="AP4" s="5">
         <f t="shared" si="0"/>
-        <v>3.1271379300849613</v>
+        <v>3.4121977859368022</v>
       </c>
       <c r="AQ4" s="5">
         <f t="shared" si="0"/>
-        <v>3.1862250948095436</v>
+        <v>3.4792032799906023</v>
       </c>
       <c r="AR4" s="5">
         <f t="shared" si="0"/>
-        <v>3.2453122595341259</v>
+        <v>3.5462087740444024</v>
       </c>
       <c r="AS4" s="5">
         <f t="shared" si="0"/>
-        <v>3.3043994242587083</v>
+        <v>3.6132142680982025</v>
       </c>
       <c r="AT4" s="5">
         <f t="shared" si="0"/>
-        <v>3.3634865889832906</v>
+        <v>3.6802197621520025</v>
       </c>
       <c r="AU4" s="5">
         <f t="shared" si="0"/>
-        <v>3.4225737537078729</v>
+        <v>3.7472252562058026</v>
       </c>
       <c r="AV4" s="5">
         <f t="shared" si="0"/>
-        <v>3.4816609184324552</v>
+        <v>3.8142307502596027</v>
       </c>
       <c r="AW4" s="5">
         <f t="shared" si="0"/>
-        <v>3.5407480831570375</v>
+        <v>3.8812362443134028</v>
       </c>
       <c r="AX4" s="5">
         <f t="shared" si="0"/>
-        <v>3.5998352478816198</v>
+        <v>3.9482417383672028</v>
       </c>
       <c r="AY4" s="5">
         <f t="shared" si="0"/>
-        <v>3.6589224126062021</v>
+        <v>4.0152472324210029</v>
       </c>
       <c r="AZ4" s="5">
         <f t="shared" si="0"/>
-        <v>3.7180095773307844</v>
+        <v>4.0822527264748025</v>
       </c>
       <c r="BA4" s="5">
         <f t="shared" si="0"/>
-        <v>3.7770967420553667</v>
+        <v>4.1492582205286022</v>
       </c>
       <c r="BB4" s="5">
         <f t="shared" si="0"/>
-        <v>3.836183906779949</v>
+        <v>4.2162637145824018</v>
+      </c>
+      <c r="BC4" s="5">
+        <f t="shared" si="0"/>
+        <v>4.2832692086362014</v>
+      </c>
+      <c r="BD4" s="5">
+        <f t="shared" si="0"/>
+        <v>4.350274702690001</v>
       </c>
     </row>
-    <row r="5" spans="2:54">
+    <row r="5" spans="2:56">
       <c r="B5" s="49">
         <v>2011</v>
       </c>
@@ -18208,7 +18388,7 @@
       </c>
       <c r="D5" s="49"/>
     </row>
-    <row r="6" spans="2:54">
+    <row r="6" spans="2:56">
       <c r="B6" s="49">
         <v>2012</v>
       </c>
@@ -18217,7 +18397,7 @@
       </c>
       <c r="D6" s="49"/>
     </row>
-    <row r="7" spans="2:54">
+    <row r="7" spans="2:56">
       <c r="B7" s="49">
         <v>2013</v>
       </c>
@@ -18226,7 +18406,7 @@
       </c>
       <c r="D7" s="49"/>
     </row>
-    <row r="8" spans="2:54">
+    <row r="8" spans="2:56">
       <c r="B8" s="49">
         <v>2014</v>
       </c>
@@ -18235,7 +18415,7 @@
       </c>
       <c r="D8" s="49"/>
     </row>
-    <row r="9" spans="2:54">
+    <row r="9" spans="2:56">
       <c r="B9" s="49">
         <v>2015</v>
       </c>
@@ -18244,7 +18424,7 @@
       </c>
       <c r="D9" s="49"/>
     </row>
-    <row r="10" spans="2:54">
+    <row r="10" spans="2:56">
       <c r="B10" s="49">
         <v>2016</v>
       </c>
@@ -18253,7 +18433,7 @@
       </c>
       <c r="D10" s="49"/>
     </row>
-    <row r="11" spans="2:54">
+    <row r="11" spans="2:56">
       <c r="B11" s="49">
         <v>2017</v>
       </c>
@@ -18262,7 +18442,7 @@
       </c>
       <c r="D11" s="49"/>
     </row>
-    <row r="12" spans="2:54">
+    <row r="12" spans="2:56">
       <c r="B12" s="49">
         <v>2018</v>
       </c>
@@ -18271,7 +18451,7 @@
       </c>
       <c r="D12" s="49"/>
     </row>
-    <row r="13" spans="2:54">
+    <row r="13" spans="2:56">
       <c r="B13" s="49">
         <v>2019</v>
       </c>
@@ -18280,25 +18460,31 @@
       </c>
       <c r="D13" s="49"/>
     </row>
-    <row r="14" spans="2:54">
+    <row r="14" spans="2:56">
       <c r="B14" s="49">
         <v>2020</v>
       </c>
       <c r="C14" s="50">
         <v>4080801.4761904757</v>
       </c>
-      <c r="D14" s="49"/>
+      <c r="D14" s="49">
+        <f>C14/C$14</f>
+        <v>1</v>
+      </c>
     </row>
-    <row r="15" spans="2:54">
+    <row r="15" spans="2:56">
       <c r="B15" s="49">
         <v>2021</v>
       </c>
       <c r="C15" s="50">
         <v>4354237.5952380951</v>
       </c>
-      <c r="D15" s="49"/>
+      <c r="D15" s="49">
+        <f t="shared" ref="D15:D44" si="1">C15/C$14</f>
+        <v>1.0670054940538001</v>
+      </c>
     </row>
-    <row r="16" spans="2:54">
+    <row r="16" spans="2:56">
       <c r="B16" s="49">
         <v>2022</v>
       </c>
@@ -18306,8 +18492,8 @@
         <v>4627673.7142857146</v>
       </c>
       <c r="D16" s="49">
-        <f t="shared" ref="D16:D44" si="1">C16/C$16</f>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>1.1340109881076001</v>
       </c>
     </row>
     <row r="17" spans="2:4">
@@ -18319,7 +18505,7 @@
       </c>
       <c r="D17" s="49">
         <f t="shared" si="1"/>
-        <v>1.0590871647245823</v>
+        <v>1.2010164821614002</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -18331,7 +18517,7 @@
       </c>
       <c r="D18" s="49">
         <f t="shared" si="1"/>
-        <v>1.1181743294491644</v>
+        <v>1.2680219762152003</v>
       </c>
     </row>
     <row r="19" spans="2:4">
@@ -18343,7 +18529,7 @@
       </c>
       <c r="D19" s="49">
         <f t="shared" si="1"/>
-        <v>1.1772614941737467</v>
+        <v>1.3350274702690004</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -18355,7 +18541,7 @@
       </c>
       <c r="D20" s="49">
         <f t="shared" si="1"/>
-        <v>1.236348658898329</v>
+        <v>1.4020329643228002</v>
       </c>
     </row>
     <row r="21" spans="2:4">
@@ -18367,7 +18553,7 @@
       </c>
       <c r="D21" s="49">
         <f t="shared" si="1"/>
-        <v>1.2954358236229113</v>
+        <v>1.4690384583766003</v>
       </c>
     </row>
     <row r="22" spans="2:4">
@@ -18379,7 +18565,7 @@
       </c>
       <c r="D22" s="49">
         <f t="shared" si="1"/>
-        <v>1.3545229883474934</v>
+        <v>1.5360439524304004</v>
       </c>
     </row>
     <row r="23" spans="2:4">
@@ -18391,7 +18577,7 @@
       </c>
       <c r="D23" s="49">
         <f t="shared" si="1"/>
-        <v>1.4136101530720757</v>
+        <v>1.6030494464842004</v>
       </c>
     </row>
     <row r="24" spans="2:4">
@@ -18403,7 +18589,7 @@
       </c>
       <c r="D24" s="49">
         <f t="shared" si="1"/>
-        <v>1.472697317796658</v>
+        <v>1.6700549405380005</v>
       </c>
     </row>
     <row r="25" spans="2:4">
@@ -18415,7 +18601,7 @@
       </c>
       <c r="D25" s="49">
         <f t="shared" si="1"/>
-        <v>1.5317844825212403</v>
+        <v>1.7370604345918006</v>
       </c>
     </row>
     <row r="26" spans="2:4">
@@ -18427,7 +18613,7 @@
       </c>
       <c r="D26" s="49">
         <f t="shared" si="1"/>
-        <v>1.5908716472458224</v>
+        <v>1.8040659286456007</v>
       </c>
     </row>
     <row r="27" spans="2:4">
@@ -18439,7 +18625,7 @@
       </c>
       <c r="D27" s="49">
         <f t="shared" si="1"/>
-        <v>1.6499588119704047</v>
+        <v>1.8710714226994007</v>
       </c>
     </row>
     <row r="28" spans="2:4">
@@ -18451,7 +18637,7 @@
       </c>
       <c r="D28" s="49">
         <f t="shared" si="1"/>
-        <v>1.709045976694987</v>
+        <v>1.9380769167532008</v>
       </c>
     </row>
     <row r="29" spans="2:4">
@@ -18463,7 +18649,7 @@
       </c>
       <c r="D29" s="49">
         <f t="shared" si="1"/>
-        <v>1.7681331414195693</v>
+        <v>2.0050824108070007</v>
       </c>
     </row>
     <row r="30" spans="2:4">
@@ -18475,7 +18661,7 @@
       </c>
       <c r="D30" s="49">
         <f t="shared" si="1"/>
-        <v>1.8272203061441514</v>
+        <v>2.0720879048608007</v>
       </c>
     </row>
     <row r="31" spans="2:4">
@@ -18487,7 +18673,7 @@
       </c>
       <c r="D31" s="49">
         <f t="shared" si="1"/>
-        <v>1.8863074708687337</v>
+        <v>2.1390933989146008</v>
       </c>
     </row>
     <row r="32" spans="2:4">
@@ -18499,7 +18685,7 @@
       </c>
       <c r="D32" s="49">
         <f t="shared" si="1"/>
-        <v>1.945394635593316</v>
+        <v>2.2060988929684009</v>
       </c>
     </row>
     <row r="33" spans="2:4">
@@ -18511,7 +18697,7 @@
       </c>
       <c r="D33" s="49">
         <f t="shared" si="1"/>
-        <v>2.0044818003178984</v>
+        <v>2.273104387022201</v>
       </c>
     </row>
     <row r="34" spans="2:4">
@@ -18523,7 +18709,7 @@
       </c>
       <c r="D34" s="49">
         <f t="shared" si="1"/>
-        <v>2.0635689650424807</v>
+        <v>2.340109881076001</v>
       </c>
     </row>
     <row r="35" spans="2:4">
@@ -18535,7 +18721,7 @@
       </c>
       <c r="D35" s="49">
         <f t="shared" si="1"/>
-        <v>2.122656129767063</v>
+        <v>2.4071153751298011</v>
       </c>
     </row>
     <row r="36" spans="2:4">
@@ -18547,7 +18733,7 @@
       </c>
       <c r="D36" s="49">
         <f t="shared" si="1"/>
-        <v>2.1817432944916448</v>
+        <v>2.4741208691836012</v>
       </c>
     </row>
     <row r="37" spans="2:4">
@@ -18559,7 +18745,7 @@
       </c>
       <c r="D37" s="49">
         <f t="shared" si="1"/>
-        <v>2.2408304592162271</v>
+        <v>2.5411263632374013</v>
       </c>
     </row>
     <row r="38" spans="2:4">
@@ -18571,7 +18757,7 @@
       </c>
       <c r="D38" s="49">
         <f t="shared" si="1"/>
-        <v>2.2999176239408095</v>
+        <v>2.6081318572912013</v>
       </c>
     </row>
     <row r="39" spans="2:4">
@@ -18583,7 +18769,7 @@
       </c>
       <c r="D39" s="49">
         <f t="shared" si="1"/>
-        <v>2.3590047886653918</v>
+        <v>2.6751373513450014</v>
       </c>
     </row>
     <row r="40" spans="2:4">
@@ -18595,7 +18781,7 @@
       </c>
       <c r="D40" s="49">
         <f t="shared" si="1"/>
-        <v>2.4180919533899741</v>
+        <v>2.7421428453988015</v>
       </c>
     </row>
     <row r="41" spans="2:4">
@@ -18607,7 +18793,7 @@
       </c>
       <c r="D41" s="49">
         <f t="shared" si="1"/>
-        <v>2.4771791181145564</v>
+        <v>2.8091483394526016</v>
       </c>
     </row>
     <row r="42" spans="2:4">
@@ -18619,7 +18805,7 @@
       </c>
       <c r="D42" s="49">
         <f t="shared" si="1"/>
-        <v>2.5362662828391387</v>
+        <v>2.8761538335064016</v>
       </c>
     </row>
     <row r="43" spans="2:4">
@@ -18631,7 +18817,7 @@
       </c>
       <c r="D43" s="49">
         <f t="shared" si="1"/>
-        <v>2.595353447563721</v>
+        <v>2.9431593275602017</v>
       </c>
     </row>
     <row r="44" spans="2:4">
@@ -18643,7 +18829,7 @@
       </c>
       <c r="D44" s="49">
         <f t="shared" si="1"/>
-        <v>2.6544406122883029</v>
+        <v>3.0101648216140018</v>
       </c>
     </row>
   </sheetData>
@@ -18656,1172 +18842,1217 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AX7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.42578125" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="52" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" ht="80.099999999999994">
+    <row r="1" spans="1:52" ht="75">
       <c r="A1" s="4" t="s">
         <v>94</v>
       </c>
       <c r="B1">
+        <v>2020</v>
+      </c>
+      <c r="C1">
+        <v>2021</v>
+      </c>
+      <c r="D1">
         <v>2022</v>
       </c>
-      <c r="C1">
+      <c r="E1">
         <v>2023</v>
       </c>
-      <c r="D1">
+      <c r="F1">
         <v>2024</v>
       </c>
-      <c r="E1">
+      <c r="G1">
         <v>2025</v>
       </c>
-      <c r="F1">
+      <c r="H1">
         <v>2026</v>
       </c>
-      <c r="G1">
+      <c r="I1">
         <v>2027</v>
       </c>
-      <c r="H1">
+      <c r="J1">
         <v>2028</v>
       </c>
-      <c r="I1">
+      <c r="K1">
         <v>2029</v>
       </c>
-      <c r="J1">
+      <c r="L1">
         <v>2030</v>
       </c>
-      <c r="K1">
+      <c r="M1">
         <v>2031</v>
       </c>
-      <c r="L1">
+      <c r="N1">
         <v>2032</v>
       </c>
-      <c r="M1">
+      <c r="O1">
         <v>2033</v>
       </c>
-      <c r="N1">
+      <c r="P1">
         <v>2034</v>
       </c>
-      <c r="O1">
+      <c r="Q1">
         <v>2035</v>
       </c>
-      <c r="P1">
+      <c r="R1">
         <v>2036</v>
       </c>
-      <c r="Q1">
+      <c r="S1">
         <v>2037</v>
       </c>
-      <c r="R1">
+      <c r="T1">
         <v>2038</v>
       </c>
-      <c r="S1">
+      <c r="U1">
         <v>2039</v>
       </c>
-      <c r="T1">
+      <c r="V1">
         <v>2040</v>
       </c>
-      <c r="U1">
+      <c r="W1">
         <v>2041</v>
       </c>
-      <c r="V1">
+      <c r="X1">
         <v>2042</v>
       </c>
-      <c r="W1">
+      <c r="Y1">
         <v>2043</v>
       </c>
-      <c r="X1">
+      <c r="Z1">
         <v>2044</v>
       </c>
-      <c r="Y1">
+      <c r="AA1">
         <v>2045</v>
       </c>
-      <c r="Z1">
+      <c r="AB1">
         <v>2046</v>
       </c>
-      <c r="AA1">
+      <c r="AC1">
         <v>2047</v>
       </c>
-      <c r="AB1">
+      <c r="AD1">
         <v>2048</v>
       </c>
-      <c r="AC1">
+      <c r="AE1">
         <v>2049</v>
       </c>
-      <c r="AD1">
+      <c r="AF1">
         <v>2050</v>
       </c>
-      <c r="AE1">
+      <c r="AG1">
         <v>2051</v>
       </c>
-      <c r="AF1">
+      <c r="AH1">
         <v>2052</v>
       </c>
-      <c r="AG1">
+      <c r="AI1">
         <v>2053</v>
       </c>
-      <c r="AH1">
+      <c r="AJ1">
         <v>2054</v>
       </c>
-      <c r="AI1">
+      <c r="AK1">
         <v>2055</v>
       </c>
-      <c r="AJ1">
+      <c r="AL1">
         <v>2056</v>
       </c>
-      <c r="AK1">
+      <c r="AM1">
         <v>2057</v>
       </c>
-      <c r="AL1">
+      <c r="AN1">
         <v>2058</v>
       </c>
-      <c r="AM1">
+      <c r="AO1">
         <v>2059</v>
       </c>
-      <c r="AN1">
+      <c r="AP1">
         <v>2060</v>
       </c>
-      <c r="AO1">
+      <c r="AQ1">
         <v>2061</v>
       </c>
-      <c r="AP1">
+      <c r="AR1">
         <v>2062</v>
       </c>
-      <c r="AQ1">
+      <c r="AS1">
         <v>2063</v>
       </c>
-      <c r="AR1">
+      <c r="AT1">
         <v>2064</v>
       </c>
-      <c r="AS1">
+      <c r="AU1">
         <v>2065</v>
       </c>
-      <c r="AT1">
+      <c r="AV1">
         <v>2066</v>
       </c>
-      <c r="AU1">
+      <c r="AW1">
         <v>2067</v>
       </c>
-      <c r="AV1">
+      <c r="AX1">
         <v>2068</v>
       </c>
-      <c r="AW1">
+      <c r="AY1">
         <v>2069</v>
       </c>
-      <c r="AX1">
+      <c r="AZ1">
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:50">
+    <row r="2" spans="1:52">
       <c r="A2" t="s">
         <v>75</v>
       </c>
       <c r="B2">
+        <f>'Mexico-Christopher'!BY48</f>
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <f>'Mexico-Christopher'!BZ48</f>
+        <v>1.0275365398976473</v>
+      </c>
+      <c r="D2">
         <f>'Mexico-Christopher'!CA48</f>
-        <v>1</v>
-      </c>
-      <c r="C2">
+        <v>1.0552275297711378</v>
+      </c>
+      <c r="E2">
         <f>'Mexico-Christopher'!CB48</f>
-        <v>1.02694549486007</v>
-      </c>
-      <c r="D2">
+        <v>1.0836611577507902</v>
+      </c>
+      <c r="F2">
         <f>'Mexico-Christopher'!CC48</f>
-        <v>1.0549365375226358</v>
-      </c>
-      <c r="E2">
+        <v>1.113198076555328</v>
+      </c>
+      <c r="G2">
         <f>'Mexico-Christopher'!CD48</f>
-        <v>1.084496405165889</v>
-      </c>
-      <c r="F2">
+        <v>1.1443904626688799</v>
+      </c>
+      <c r="H2">
         <f>'Mexico-Christopher'!CE48</f>
-        <v>1.1163062978923239</v>
-      </c>
-      <c r="G2">
+        <v>1.1779571371928808</v>
+      </c>
+      <c r="I2">
         <f>'Mexico-Christopher'!CF48</f>
-        <v>1.1493468253316153</v>
-      </c>
-      <c r="H2">
+        <v>1.2128224113449795</v>
+      </c>
+      <c r="J2">
         <f>'Mexico-Christopher'!CG48</f>
-        <v>1.1868382713599823</v>
-      </c>
-      <c r="I2">
+        <v>1.2523844173250414</v>
+      </c>
+      <c r="K2">
         <f>'Mexico-Christopher'!CH48</f>
-        <v>1.2291371050109887</v>
-      </c>
-      <c r="J2">
+        <v>1.297019311070793</v>
+      </c>
+      <c r="L2">
         <f>'Mexico-Christopher'!CI48</f>
-        <v>1.2716652847736512</v>
-      </c>
-      <c r="K2">
+        <v>1.3418962171474103</v>
+      </c>
+      <c r="M2">
         <f>'Mexico-Christopher'!CJ48</f>
-        <v>1.3154262685903853</v>
-      </c>
-      <c r="L2">
+        <v>1.3880740120006974</v>
+      </c>
+      <c r="N2">
         <f>'Mexico-Christopher'!CK48</f>
-        <v>1.3605433608978712</v>
-      </c>
-      <c r="M2">
+        <v>1.4356828098667822</v>
+      </c>
+      <c r="O2">
         <f>'Mexico-Christopher'!CL48</f>
-        <v>1.4071225201733277</v>
-      </c>
-      <c r="N2">
+        <v>1.4848344210478386</v>
+      </c>
+      <c r="P2">
         <f>'Mexico-Christopher'!CM48</f>
-        <v>1.4552937014997356</v>
-      </c>
-      <c r="O2">
+        <v>1.5356659777250614</v>
+      </c>
+      <c r="Q2">
         <f>'Mexico-Christopher'!CN48</f>
-        <v>1.4766046543064788</v>
-      </c>
-      <c r="P2">
+        <v>1.5581538818123901</v>
+      </c>
+      <c r="R2">
         <f>'Mexico-Christopher'!CO48</f>
-        <v>1.4985844473312289</v>
-      </c>
-      <c r="Q2">
+        <v>1.5813475645107782</v>
+      </c>
+      <c r="S2">
         <f>'Mexico-Christopher'!CP48</f>
-        <v>1.5212721986718152</v>
-      </c>
-      <c r="R2">
+        <v>1.605288304313967</v>
+      </c>
+      <c r="T2">
         <f>'Mexico-Christopher'!CQ48</f>
-        <v>1.5447097483972188</v>
-      </c>
-      <c r="S2">
+        <v>1.6300202520145928</v>
+      </c>
+      <c r="U2">
         <f>'Mexico-Christopher'!CR48</f>
-        <v>1.5689418535965782</v>
-      </c>
-      <c r="T2">
+        <v>1.6555906365252671</v>
+      </c>
+      <c r="V2">
         <f>'Mexico-Christopher'!CS48</f>
-        <v>1.5940163974680446</v>
-      </c>
-      <c r="U2">
+        <v>1.6820499855148927</v>
+      </c>
+      <c r="W2">
         <f>'Mexico-Christopher'!CT48</f>
-        <v>1.6199846134588207</v>
-      </c>
-      <c r="V2">
+        <v>1.7094523619274027</v>
+      </c>
+      <c r="X2">
         <f>'Mexico-Christopher'!CU48</f>
-        <v>1.6469013255405889</v>
-      </c>
-      <c r="W2">
+        <v>1.7378556175270077</v>
+      </c>
+      <c r="Y2">
         <f>'Mexico-Christopher'!CV48</f>
-        <v>1.6748252057826458</v>
-      </c>
-      <c r="X2">
+        <v>1.7673216646964587</v>
+      </c>
+      <c r="Z2">
         <f>'Mexico-Christopher'!CW48</f>
-        <v>1.7038190504687956</v>
-      </c>
-      <c r="Y2">
+        <v>1.7979167678031924</v>
+      </c>
+      <c r="AA2">
         <f>'Mexico-Christopher'!CX48</f>
-        <v>1.7339500760938245</v>
-      </c>
-      <c r="Z2">
+        <v>1.8297118555429626</v>
+      </c>
+      <c r="AB2">
         <f>'Mexico-Christopher'!CY48</f>
-        <v>1.7652902366716285</v>
-      </c>
-      <c r="AA2">
+        <v>1.8627828557721096</v>
+      </c>
+      <c r="AC2">
         <f>'Mexico-Christopher'!CZ48</f>
-        <v>1.7979165638902312</v>
-      </c>
-      <c r="AB2">
+        <v>1.8972110544485006</v>
+      </c>
+      <c r="AD2">
         <f>'Mexico-Christopher'!DA48</f>
-        <v>1.8319115317595409</v>
-      </c>
-      <c r="AC2">
+        <v>1.9330834804178814</v>
+      </c>
+      <c r="AE2">
         <f>'Mexico-Christopher'!DB48</f>
-        <v>1.867363447516271</v>
-      </c>
-      <c r="AD2">
+        <v>1.9704933179075101</v>
+      </c>
+      <c r="AF2">
         <f>'Mexico-Christopher'!DC48</f>
-        <v>1.9043668706775756</v>
-      </c>
-      <c r="AE2" s="5">
-        <f t="shared" ref="AE2:AN7" si="0">AD2+(AD2-Y2)/5</f>
-        <v>1.9384502295943258</v>
-      </c>
-      <c r="AF2" s="5">
-        <f t="shared" si="0"/>
-        <v>1.9730822281788651</v>
+        <v>2.0095403487230898</v>
       </c>
       <c r="AG2" s="5">
-        <f t="shared" si="0"/>
-        <v>2.0081153610365918</v>
+        <f t="shared" ref="AG2:AP7" si="0">AF2+(AF2-AA2)/5</f>
+        <v>2.0455060473591153</v>
       </c>
       <c r="AH2" s="5">
         <f t="shared" si="0"/>
-        <v>2.043356126892002</v>
+        <v>2.0820506856765166</v>
       </c>
       <c r="AI2" s="5">
         <f t="shared" si="0"/>
-        <v>2.0785546627671483</v>
+        <v>2.1190186119221197</v>
       </c>
       <c r="AJ2" s="5">
         <f t="shared" si="0"/>
-        <v>2.1133922211850629</v>
+        <v>2.1562056382229673</v>
       </c>
       <c r="AK2" s="5">
         <f t="shared" si="0"/>
-        <v>2.1483806195032105</v>
+        <v>2.1933481022860586</v>
       </c>
       <c r="AL2" s="5">
         <f t="shared" si="0"/>
-        <v>2.1834402977680796</v>
+        <v>2.2301096529986522</v>
       </c>
       <c r="AM2" s="5">
         <f t="shared" si="0"/>
-        <v>2.2185052851143769</v>
+        <v>2.2670303741265596</v>
       </c>
       <c r="AN2" s="5">
         <f t="shared" si="0"/>
-        <v>2.2535351167588518</v>
+        <v>2.304026311816568</v>
       </c>
       <c r="AO2" s="5">
-        <f t="shared" ref="AO2:AX7" si="1">AN2+(AN2-AI2)/5</f>
-        <v>2.2885312075571926</v>
+        <f t="shared" si="0"/>
+        <v>2.3410278517954577</v>
       </c>
       <c r="AP2" s="5">
-        <f t="shared" si="1"/>
-        <v>2.3235590048316186</v>
+        <f t="shared" si="0"/>
+        <v>2.3779922945099559</v>
       </c>
       <c r="AQ2" s="5">
-        <f t="shared" si="1"/>
-        <v>2.3585946818973</v>
+        <f t="shared" ref="AQ2:AZ7" si="1">AP2+(AP2-AK2)/5</f>
+        <v>2.4149211329547353</v>
       </c>
       <c r="AR2" s="5">
         <f t="shared" si="1"/>
-        <v>2.3936255587231443</v>
+        <v>2.4518834289459521</v>
       </c>
       <c r="AS2" s="5">
         <f t="shared" si="1"/>
-        <v>2.4286496134448976</v>
+        <v>2.4888540399098305</v>
       </c>
       <c r="AT2" s="5">
         <f t="shared" si="1"/>
-        <v>2.4636725127821069</v>
+        <v>2.5258195855284828</v>
       </c>
       <c r="AU2" s="5">
         <f t="shared" si="1"/>
-        <v>2.4987007738270899</v>
+        <v>2.5627779322750879</v>
       </c>
       <c r="AV2" s="5">
         <f t="shared" si="1"/>
-        <v>2.533729127626184</v>
+        <v>2.5997350598281144</v>
       </c>
       <c r="AW2" s="5">
         <f t="shared" si="1"/>
-        <v>2.5687560167719607</v>
+        <v>2.6366978452027903</v>
       </c>
       <c r="AX2" s="5">
         <f t="shared" si="1"/>
-        <v>2.6037821083817239</v>
+        <v>2.6736607284541578</v>
+      </c>
+      <c r="AY2" s="5">
+        <f t="shared" si="1"/>
+        <v>2.7106220661630234</v>
+      </c>
+      <c r="AZ2" s="5">
+        <f t="shared" si="1"/>
+        <v>2.7475825622899315</v>
       </c>
     </row>
-    <row r="3" spans="1:50">
+    <row r="3" spans="1:52">
       <c r="A3" t="s">
         <v>76</v>
       </c>
       <c r="B3">
+        <f>'Mexico-Christopher'!BY49</f>
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <f>'Mexico-Christopher'!BZ49</f>
+        <v>0.98489903302041404</v>
+      </c>
+      <c r="D3">
         <f>'Mexico-Christopher'!CA49</f>
-        <v>1</v>
-      </c>
-      <c r="C3">
+        <v>0.97050375385972121</v>
+      </c>
+      <c r="E3">
         <f>'Mexico-Christopher'!CB49</f>
-        <v>1.0001708994431</v>
-      </c>
-      <c r="D3">
+        <v>0.97066961241078231</v>
+      </c>
+      <c r="F3">
         <f>'Mexico-Christopher'!CC49</f>
-        <v>1.009214507425255</v>
-      </c>
-      <c r="E3">
+        <v>0.9794464679058994</v>
+      </c>
+      <c r="G3">
         <f>'Mexico-Christopher'!CD49</f>
-        <v>1.0171842574343455</v>
-      </c>
-      <c r="F3">
+        <v>0.98718114020704517</v>
+      </c>
+      <c r="H3">
         <f>'Mexico-Christopher'!CE49</f>
-        <v>1.0262574126744008</v>
-      </c>
-      <c r="G3">
+        <v>0.99598667142687114</v>
+      </c>
+      <c r="I3">
         <f>'Mexico-Christopher'!CF49</f>
-        <v>1.0444174401676691</v>
-      </c>
-      <c r="H3">
+        <v>1.0136110462792836</v>
+      </c>
+      <c r="J3">
         <f>'Mexico-Christopher'!CG49</f>
-        <v>1.064749918155228</v>
-      </c>
-      <c r="I3">
+        <v>1.0333437924914797</v>
+      </c>
+      <c r="K3">
         <f>'Mexico-Christopher'!CH49</f>
-        <v>1.0869452550020162</v>
-      </c>
-      <c r="J3">
+        <v>1.0548844502194685</v>
+      </c>
+      <c r="L3">
         <f>'Mexico-Christopher'!CI49</f>
-        <v>1.1100619326099475</v>
-      </c>
-      <c r="K3">
+        <v>1.0773192726147309</v>
+      </c>
+      <c r="M3">
         <f>'Mexico-Christopher'!CJ49</f>
-        <v>1.1318192383762096</v>
-      </c>
-      <c r="L3">
+        <v>1.098434819534762</v>
+      </c>
+      <c r="N3">
         <f>'Mexico-Christopher'!CK49</f>
-        <v>1.1525980410067402</v>
-      </c>
-      <c r="M3">
+        <v>1.1186007254884021</v>
+      </c>
+      <c r="O3">
         <f>'Mexico-Christopher'!CL49</f>
-        <v>1.1725753073497514</v>
-      </c>
-      <c r="N3">
+        <v>1.1379887374661499</v>
+      </c>
+      <c r="P3">
         <f>'Mexico-Christopher'!CM49</f>
-        <v>1.1931481951424425</v>
-      </c>
-      <c r="O3">
+        <v>1.1579548022966917</v>
+      </c>
+      <c r="Q3">
         <f>'Mexico-Christopher'!CN49</f>
-        <v>1.2044303256457414</v>
-      </c>
-      <c r="P3">
+        <v>1.1689041523016783</v>
+      </c>
+      <c r="R3">
         <f>'Mexico-Christopher'!CO49</f>
-        <v>1.2158195783392014</v>
-      </c>
-      <c r="Q3">
+        <v>1.1799574647943383</v>
+      </c>
+      <c r="S3">
         <f>'Mexico-Christopher'!CP49</f>
-        <v>1.2273169752125808</v>
-      </c>
-      <c r="R3">
+        <v>1.191115731619568</v>
+      </c>
+      <c r="T3">
         <f>'Mexico-Christopher'!CQ49</f>
-        <v>1.2389235480596208</v>
-      </c>
-      <c r="S3">
+        <v>1.2023799541370666</v>
+      </c>
+      <c r="U3">
         <f>'Mexico-Christopher'!CR49</f>
-        <v>1.2506403385726872</v>
-      </c>
-      <c r="T3">
+        <v>1.2137511433131856</v>
+      </c>
+      <c r="V3">
         <f>'Mexico-Christopher'!CS49</f>
-        <v>1.2624683984383291</v>
-      </c>
-      <c r="U3">
+        <v>1.2252303198136687</v>
+      </c>
+      <c r="W3">
         <f>'Mexico-Christopher'!CT49</f>
-        <v>1.2744087894337681</v>
-      </c>
-      <c r="V3">
+        <v>1.2368185140972949</v>
+      </c>
+      <c r="X3">
         <f>'Mexico-Christopher'!CU49</f>
-        <v>1.2864625835243251</v>
-      </c>
-      <c r="W3">
+        <v>1.2485167665104326</v>
+      </c>
+      <c r="Y3">
         <f>'Mexico-Christopher'!CV49</f>
-        <v>1.2986308629617951</v>
-      </c>
-      <c r="X3">
+        <v>1.260326127382511</v>
+      </c>
+      <c r="Z3">
         <f>'Mexico-Christopher'!CW49</f>
-        <v>1.3109147203837772</v>
-      </c>
-      <c r="Y3">
+        <v>1.2722476571224226</v>
+      </c>
+      <c r="AA3">
         <f>'Mexico-Christopher'!CX49</f>
-        <v>1.3233152589139725</v>
-      </c>
-      <c r="Z3">
+        <v>1.2842824263158592</v>
+      </c>
+      <c r="AB3">
         <f>'Mexico-Christopher'!CY49</f>
-        <v>1.3358335922634561</v>
-      </c>
-      <c r="AA3">
+        <v>1.2964315158236004</v>
+      </c>
+      <c r="AC3">
         <f>'Mexico-Christopher'!CZ49</f>
-        <v>1.3484708448329339</v>
-      </c>
-      <c r="AB3">
+        <v>1.308696016880752</v>
+      </c>
+      <c r="AD3">
         <f>'Mexico-Christopher'!DA49</f>
-        <v>1.3612281518159957</v>
-      </c>
-      <c r="AC3">
+        <v>1.3210770311969542</v>
+      </c>
+      <c r="AE3">
         <f>'Mexico-Christopher'!DB49</f>
-        <v>1.3741066593033699</v>
-      </c>
-      <c r="AD3">
+        <v>1.3335756710575615</v>
+      </c>
+      <c r="AF3">
         <f>'Mexico-Christopher'!DC49</f>
-        <v>1.3871075243881965</v>
-      </c>
-      <c r="AE3" s="5">
-        <f t="shared" si="0"/>
-        <v>1.3998659774830413</v>
-      </c>
-      <c r="AF3" s="5">
-        <f t="shared" si="0"/>
-        <v>1.4126724545269584</v>
+        <v>1.3461930594258094</v>
       </c>
       <c r="AG3" s="5">
         <f t="shared" si="0"/>
-        <v>1.4255127764657634</v>
+        <v>1.3585751860477995</v>
       </c>
       <c r="AH3" s="5">
         <f t="shared" si="0"/>
-        <v>1.4383697013957168</v>
+        <v>1.3710039200926394</v>
       </c>
       <c r="AI3" s="5">
         <f t="shared" si="0"/>
-        <v>1.4512223098141863</v>
+        <v>1.383465500735017</v>
       </c>
       <c r="AJ3" s="5">
         <f t="shared" si="0"/>
-        <v>1.4640452668993842</v>
+        <v>1.3959431946426295</v>
       </c>
       <c r="AK3" s="5">
         <f t="shared" si="0"/>
-        <v>1.4768811247826528</v>
+        <v>1.4084166993596432</v>
       </c>
       <c r="AL3" s="5">
         <f t="shared" si="0"/>
-        <v>1.4897228588337916</v>
+        <v>1.42086142734641</v>
       </c>
       <c r="AM3" s="5">
         <f t="shared" si="0"/>
-        <v>1.5025648753073972</v>
+        <v>1.433318675606132</v>
       </c>
       <c r="AN3" s="5">
         <f t="shared" si="0"/>
-        <v>1.5154039100897334</v>
+        <v>1.4457816267088306</v>
       </c>
       <c r="AO3" s="5">
-        <f t="shared" si="1"/>
-        <v>1.5282402301448428</v>
+        <f t="shared" si="0"/>
+        <v>1.4582448519035933</v>
       </c>
       <c r="AP3" s="5">
-        <f t="shared" si="1"/>
-        <v>1.5410792227939345</v>
+        <f t="shared" si="0"/>
+        <v>1.470705183355786</v>
       </c>
       <c r="AQ3" s="5">
         <f t="shared" si="1"/>
-        <v>1.5539188423961909</v>
+        <v>1.4831628801550145</v>
       </c>
       <c r="AR3" s="5">
         <f t="shared" si="1"/>
-        <v>1.5667580391086708</v>
+        <v>1.4956231707167353</v>
       </c>
       <c r="AS3" s="5">
         <f t="shared" si="1"/>
-        <v>1.5795966718689256</v>
+        <v>1.508084069738856</v>
       </c>
       <c r="AT3" s="5">
         <f t="shared" si="1"/>
-        <v>1.5924352242247641</v>
+        <v>1.5205445583448611</v>
       </c>
       <c r="AU3" s="5">
         <f t="shared" si="1"/>
-        <v>1.6052742230407484</v>
+        <v>1.5330044996331147</v>
       </c>
       <c r="AV3" s="5">
         <f t="shared" si="1"/>
-        <v>1.6181132230901112</v>
+        <v>1.5454643628885805</v>
       </c>
       <c r="AW3" s="5">
         <f t="shared" si="1"/>
-        <v>1.6309520992288953</v>
+        <v>1.5579246594352936</v>
       </c>
       <c r="AX3" s="5">
         <f t="shared" si="1"/>
-        <v>1.6437909112529401</v>
+        <v>1.5703849571790052</v>
+      </c>
+      <c r="AY3" s="5">
+        <f t="shared" si="1"/>
+        <v>1.5828451346670349</v>
+      </c>
+      <c r="AZ3" s="5">
+        <f t="shared" si="1"/>
+        <v>1.5953052499314697</v>
       </c>
     </row>
-    <row r="4" spans="1:50">
+    <row r="4" spans="1:52">
       <c r="A4" t="s">
         <v>77</v>
       </c>
       <c r="B4">
+        <f>'Oil Prospective'!F15</f>
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <f>'Oil Prospective'!G15</f>
+        <v>1.0286054827175208</v>
+      </c>
+      <c r="D4">
         <f>'Oil Prospective'!H15</f>
-        <v>1</v>
-      </c>
-      <c r="C4">
+        <v>1.0584028605482716</v>
+      </c>
+      <c r="E4">
         <f>'Oil Prospective'!I15</f>
-        <v>1.0292792792792793</v>
-      </c>
-      <c r="D4">
+        <v>1.0893921334922527</v>
+      </c>
+      <c r="F4">
         <f>'Oil Prospective'!J15</f>
-        <v>1.0585585585585586</v>
-      </c>
-      <c r="E4">
+        <v>1.1203814064362336</v>
+      </c>
+      <c r="G4">
         <f>'Oil Prospective'!K15</f>
-        <v>1.0889639639639641</v>
-      </c>
-      <c r="F4">
+        <v>1.1525625744934445</v>
+      </c>
+      <c r="H4">
         <f>'Oil Prospective'!L15</f>
-        <v>1.1204954954954955</v>
-      </c>
-      <c r="G4">
+        <v>1.1859356376638854</v>
+      </c>
+      <c r="I4">
         <f>'Oil Prospective'!M15</f>
-        <v>1.1542792792792793</v>
-      </c>
-      <c r="H4">
+        <v>1.2216924910607865</v>
+      </c>
+      <c r="J4">
         <f>'Oil Prospective'!N15</f>
-        <v>1.1880630630630631</v>
-      </c>
-      <c r="I4">
+        <v>1.2574493444576877</v>
+      </c>
+      <c r="K4">
         <f>'Oil Prospective'!O15</f>
-        <v>1.222972972972973</v>
-      </c>
-      <c r="J4">
+        <v>1.2943980929678187</v>
+      </c>
+      <c r="L4">
         <f>'Oil Prospective'!P15</f>
-        <v>1.2601351351351353</v>
-      </c>
-      <c r="K4">
+        <v>1.33373063170441</v>
+      </c>
+      <c r="M4">
         <f>'Oil Prospective'!Q15</f>
-        <v>1.2972972972972974</v>
-      </c>
-      <c r="L4">
+        <v>1.3730631704410012</v>
+      </c>
+      <c r="N4">
         <f>'Oil Prospective'!R15</f>
-        <v>1.3319819819819791</v>
-      </c>
-      <c r="M4">
+        <v>1.4097735399284832</v>
+      </c>
+      <c r="O4">
         <f>'Oil Prospective'!S15</f>
-        <v>1.3687387387387373</v>
-      </c>
-      <c r="N4">
+        <v>1.4486769964243129</v>
+      </c>
+      <c r="P4">
         <f>'Oil Prospective'!T15</f>
-        <v>1.4052387387387315</v>
-      </c>
-      <c r="O4">
+        <v>1.4873087008343187</v>
+      </c>
+      <c r="Q4">
         <f>'Oil Prospective'!U15</f>
-        <v>1.4411729729729748</v>
-      </c>
-      <c r="P4">
+        <v>1.5253415971394535</v>
+      </c>
+      <c r="R4">
         <f>'Oil Prospective'!V15</f>
-        <v>1.4771883783783688</v>
-      </c>
-      <c r="Q4">
+        <v>1.5634604052443282</v>
+      </c>
+      <c r="S4">
         <f>'Oil Prospective'!W15</f>
-        <v>1.5137182702702676</v>
-      </c>
-      <c r="R4">
+        <v>1.6021237473182328</v>
+      </c>
+      <c r="T4">
         <f>'Oil Prospective'!X15</f>
-        <v>1.5497840306306283</v>
-      </c>
-      <c r="S4">
+        <v>1.6402958512514874</v>
+      </c>
+      <c r="U4">
         <f>'Oil Prospective'!Y15</f>
-        <v>1.585911242522515</v>
-      </c>
-      <c r="T4">
+        <v>1.6785329956614938</v>
+      </c>
+      <c r="V4">
         <f>'Oil Prospective'!Z15</f>
-        <v>1.6221766363603489</v>
-      </c>
-      <c r="U4">
+        <v>1.7169163922383666</v>
+      </c>
+      <c r="W4">
         <f>'Oil Prospective'!AA15</f>
-        <v>1.6584065580972849</v>
-      </c>
-      <c r="V4">
+        <v>1.7552622450421798</v>
+      </c>
+      <c r="X4">
         <f>'Oil Prospective'!AB15</f>
-        <v>1.6945301019913346</v>
-      </c>
-      <c r="W4">
+        <v>1.7934955072327829</v>
+      </c>
+      <c r="Y4">
         <f>'Oil Prospective'!AC15</f>
-        <v>1.7307579514092779</v>
-      </c>
-      <c r="X4">
+        <v>1.8318391666882463</v>
+      </c>
+      <c r="Z4">
         <f>'Oil Prospective'!AD15</f>
-        <v>1.7669705630974966</v>
-      </c>
-      <c r="Y4">
+        <v>1.8701666984869807</v>
+      </c>
+      <c r="AA4">
         <f>'Oil Prospective'!AE15</f>
-        <v>1.8031501362270319</v>
-      </c>
-      <c r="Z4">
+        <v>1.9084592621806964</v>
+      </c>
+      <c r="AB4">
         <f>'Oil Prospective'!AF15</f>
-        <v>1.839341347374178</v>
-      </c>
-      <c r="AA4">
+        <v>1.9467641435855421</v>
+      </c>
+      <c r="AC4">
         <f>'Oil Prospective'!AG15</f>
-        <v>1.8755544226949061</v>
-      </c>
-      <c r="AB4">
+        <v>1.9850921660942509</v>
+      </c>
+      <c r="AD4">
         <f>'Oil Prospective'!AH15</f>
-        <v>1.9117440022149585</v>
-      </c>
-      <c r="AC4">
+        <v>2.0233953205803132</v>
+      </c>
+      <c r="AE4">
         <f>'Oil Prospective'!AI15</f>
-        <v>1.9479374437325638</v>
-      </c>
-      <c r="AD4">
+        <v>2.0617025626156336</v>
+      </c>
+      <c r="AF4">
         <f>'Oil Prospective'!AJ15</f>
-        <v>1.984138651404278</v>
-      </c>
-      <c r="AE4" s="5">
-        <f t="shared" si="0"/>
-        <v>2.0203363544397273</v>
-      </c>
-      <c r="AF4" s="5">
-        <f t="shared" si="0"/>
-        <v>2.0565353558528372</v>
+        <v>2.1000180243706779</v>
       </c>
       <c r="AG4" s="5">
         <f t="shared" si="0"/>
-        <v>2.0927315424844233</v>
+        <v>2.138329776808674</v>
       </c>
       <c r="AH4" s="5">
         <f t="shared" si="0"/>
-        <v>2.128929050538316</v>
+        <v>2.1766429034533004</v>
       </c>
       <c r="AI4" s="5">
         <f t="shared" si="0"/>
-        <v>2.1651273718994664</v>
+        <v>2.2149530509251103</v>
       </c>
       <c r="AJ4" s="5">
         <f t="shared" si="0"/>
-        <v>2.2013251159985039</v>
+        <v>2.2532645969940699</v>
       </c>
       <c r="AK4" s="5">
         <f t="shared" si="0"/>
-        <v>2.237522868310259</v>
+        <v>2.2915770038697572</v>
       </c>
       <c r="AL4" s="5">
         <f t="shared" si="0"/>
-        <v>2.2737203708017435</v>
+        <v>2.3298887997695732</v>
       </c>
       <c r="AM4" s="5">
         <f t="shared" si="0"/>
-        <v>2.3099181364652077</v>
+        <v>2.3682006043617529</v>
       </c>
       <c r="AN4" s="5">
         <f t="shared" si="0"/>
-        <v>2.3461159536505862</v>
+        <v>2.4065121445434436</v>
       </c>
       <c r="AO4" s="5">
-        <f t="shared" si="1"/>
-        <v>2.3823136700008103</v>
+        <f t="shared" si="0"/>
+        <v>2.4448239632671105</v>
       </c>
       <c r="AP4" s="5">
-        <f t="shared" si="1"/>
-        <v>2.4185113808012715</v>
+        <f t="shared" si="0"/>
+        <v>2.4831358365217184</v>
       </c>
       <c r="AQ4" s="5">
         <f t="shared" si="1"/>
-        <v>2.4547090832994738</v>
+        <v>2.5214476030521107</v>
       </c>
       <c r="AR4" s="5">
         <f t="shared" si="1"/>
-        <v>2.4909068257990197</v>
+        <v>2.559759363708618</v>
       </c>
       <c r="AS4" s="5">
         <f t="shared" si="1"/>
-        <v>2.5271045636657821</v>
+        <v>2.5980711155779912</v>
       </c>
       <c r="AT4" s="5">
         <f t="shared" si="1"/>
-        <v>2.5633022856688212</v>
+        <v>2.6363829097849005</v>
       </c>
       <c r="AU4" s="5">
         <f t="shared" si="1"/>
-        <v>2.5995000088024236</v>
+        <v>2.6746946990884584</v>
       </c>
       <c r="AV4" s="5">
         <f t="shared" si="1"/>
-        <v>2.6356977344026542</v>
+        <v>2.7130064716018065</v>
       </c>
       <c r="AW4" s="5">
         <f t="shared" si="1"/>
-        <v>2.6718954646232902</v>
+        <v>2.7513182453117455</v>
       </c>
       <c r="AX4" s="5">
         <f t="shared" si="1"/>
-        <v>2.7080931923881444</v>
+        <v>2.7896300216323708</v>
+      </c>
+      <c r="AY4" s="5">
+        <f t="shared" si="1"/>
+        <v>2.8279418028432466</v>
+      </c>
+      <c r="AZ4" s="5">
+        <f t="shared" si="1"/>
+        <v>2.8662535814549157</v>
       </c>
     </row>
-    <row r="5" spans="1:50">
+    <row r="5" spans="1:52">
       <c r="A5" t="s">
         <v>78</v>
       </c>
       <c r="B5">
+        <f>'Oil Prospective'!F16</f>
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <f>'Oil Prospective'!G16</f>
+        <v>1.0335570469798658</v>
+      </c>
+      <c r="D5">
         <f>'Oil Prospective'!H16</f>
-        <v>1</v>
-      </c>
-      <c r="C5">
+        <v>1.0671140939597314</v>
+      </c>
+      <c r="E5">
         <f>'Oil Prospective'!I16</f>
-        <v>1.0314465408805031</v>
-      </c>
-      <c r="D5">
+        <v>1.1006711409395973</v>
+      </c>
+      <c r="F5">
         <f>'Oil Prospective'!J16</f>
-        <v>1.0628930817610063</v>
-      </c>
-      <c r="E5">
+        <v>1.1342281879194629</v>
+      </c>
+      <c r="G5">
         <f>'Oil Prospective'!K16</f>
-        <v>1.0943396226415094</v>
-      </c>
-      <c r="F5">
+        <v>1.1677852348993287</v>
+      </c>
+      <c r="H5">
         <f>'Oil Prospective'!L16</f>
-        <v>1.1257861635220126</v>
-      </c>
-      <c r="G5">
+        <v>1.2013422818791946</v>
+      </c>
+      <c r="I5">
         <f>'Oil Prospective'!M16</f>
-        <v>1.1635220125786163</v>
-      </c>
-      <c r="H5">
+        <v>1.2416107382550334</v>
+      </c>
+      <c r="J5">
         <f>'Oil Prospective'!N16</f>
-        <v>1.1949685534591195</v>
-      </c>
-      <c r="I5">
+        <v>1.2751677852348993</v>
+      </c>
+      <c r="K5">
         <f>'Oil Prospective'!O16</f>
-        <v>1.2327044025157234</v>
-      </c>
-      <c r="J5">
+        <v>1.3154362416107384</v>
+      </c>
+      <c r="L5">
         <f>'Oil Prospective'!P16</f>
-        <v>1.270440251572327</v>
-      </c>
-      <c r="K5">
+        <v>1.355704697986577</v>
+      </c>
+      <c r="M5">
         <f>'Oil Prospective'!Q16</f>
-        <v>1.3081761006289307</v>
-      </c>
-      <c r="L5">
+        <v>1.3959731543624161</v>
+      </c>
+      <c r="N5">
         <f>'Oil Prospective'!R16</f>
-        <v>1.343396226415088</v>
-      </c>
-      <c r="M5">
+        <v>1.4335570469798591</v>
+      </c>
+      <c r="O5">
         <f>'Oil Prospective'!S16</f>
-        <v>1.3816352201257909</v>
-      </c>
-      <c r="N5">
+        <v>1.4743624161073876</v>
+      </c>
+      <c r="P5">
         <f>'Oil Prospective'!T16</f>
-        <v>1.4185157232704393</v>
-      </c>
-      <c r="O5">
+        <v>1.5137181208053683</v>
+      </c>
+      <c r="Q5">
         <f>'Oil Prospective'!U16</f>
-        <v>1.455315723270437</v>
-      </c>
-      <c r="P5">
+        <v>1.5529879194630838</v>
+      </c>
+      <c r="R5">
         <f>'Oil Prospective'!V16</f>
-        <v>1.4922274213836459</v>
-      </c>
-      <c r="Q5">
+        <v>1.592376912751676</v>
+      </c>
+      <c r="S5">
         <f>'Oil Prospective'!W16</f>
-        <v>1.5296209308176061</v>
-      </c>
-      <c r="R5">
+        <v>1.6322800536912707</v>
+      </c>
+      <c r="T5">
         <f>'Oil Prospective'!X16</f>
-        <v>1.5663679396226406</v>
-      </c>
-      <c r="S5">
+        <v>1.6714933046979856</v>
+      </c>
+      <c r="U5">
         <f>'Oil Prospective'!Y16</f>
-        <v>1.6034124397484195</v>
-      </c>
-      <c r="T5">
+        <v>1.7110240128858973</v>
+      </c>
+      <c r="V5">
         <f>'Oil Prospective'!Z16</f>
-        <v>1.640489076327035</v>
-      </c>
-      <c r="U5">
+        <v>1.7505890143355607</v>
+      </c>
+      <c r="W5">
         <f>'Oil Prospective'!AA16</f>
-        <v>1.6775180072251468</v>
-      </c>
-      <c r="V5">
+        <v>1.7901031083811969</v>
+      </c>
+      <c r="X5">
         <f>'Oil Prospective'!AB16</f>
-        <v>1.7144562656039994</v>
-      </c>
-      <c r="W5">
+        <v>1.8295204445035969</v>
+      </c>
+      <c r="Y5">
         <f>'Oil Prospective'!AC16</f>
-        <v>1.7515334115372718</v>
-      </c>
-      <c r="X5">
+        <v>1.8690859894927934</v>
+      </c>
+      <c r="Z5">
         <f>'Oil Prospective'!AD16</f>
-        <v>1.7885445799447695</v>
-      </c>
-      <c r="Y5">
+        <v>1.9085811289343513</v>
+      </c>
+      <c r="AA5">
         <f>'Oil Prospective'!AE16</f>
-        <v>1.8255461915919113</v>
-      </c>
-      <c r="Z5">
+        <v>1.948066070222241</v>
+      </c>
+      <c r="AB5">
         <f>'Oil Prospective'!AF16</f>
-        <v>1.8625630961028981</v>
-      </c>
-      <c r="AA5">
+        <v>1.9875673307406765</v>
+      </c>
+      <c r="AC5">
         <f>'Oil Prospective'!AG16</f>
-        <v>1.8995966412718996</v>
-      </c>
-      <c r="AB5">
+        <v>2.0270863487398123</v>
+      </c>
+      <c r="AD5">
         <f>'Oil Prospective'!AH16</f>
-        <v>1.9366002767779609</v>
-      </c>
-      <c r="AC5">
+        <v>2.066573449716079</v>
+      </c>
+      <c r="AE5">
         <f>'Oil Prospective'!AI16</f>
-        <v>1.973618710141805</v>
-      </c>
-      <c r="AD5">
+        <v>2.1060763416949464</v>
+      </c>
+      <c r="AF5">
         <f>'Oil Prospective'!AJ16</f>
-        <v>2.0106396485097457</v>
-      </c>
-      <c r="AE5" s="5">
-        <f t="shared" si="0"/>
-        <v>2.0476583398933128</v>
-      </c>
-      <c r="AF5" s="5">
-        <f t="shared" si="0"/>
-        <v>2.0846773886513956</v>
+        <v>2.1455819067989905</v>
       </c>
       <c r="AG5" s="5">
         <f t="shared" si="0"/>
-        <v>2.1216935381272948</v>
+        <v>2.1850850741143404</v>
       </c>
       <c r="AH5" s="5">
         <f t="shared" si="0"/>
-        <v>2.1587121903971616</v>
+        <v>2.224588622789073</v>
       </c>
       <c r="AI5" s="5">
         <f t="shared" si="0"/>
-        <v>2.1957308864482328</v>
+        <v>2.2640890775989253</v>
       </c>
       <c r="AJ5" s="5">
         <f t="shared" si="0"/>
-        <v>2.23274913403593</v>
+        <v>2.3035922031754947</v>
       </c>
       <c r="AK5" s="5">
         <f t="shared" si="0"/>
-        <v>2.2697672928644534</v>
+        <v>2.3430953754716044</v>
       </c>
       <c r="AL5" s="5">
         <f t="shared" si="0"/>
-        <v>2.3067852737070651</v>
+        <v>2.3825980692061273</v>
       </c>
       <c r="AM5" s="5">
         <f t="shared" si="0"/>
-        <v>2.3438036208230191</v>
+        <v>2.4221006682244846</v>
       </c>
       <c r="AN5" s="5">
         <f t="shared" si="0"/>
-        <v>2.3808219069081904</v>
+        <v>2.4616030773115667</v>
       </c>
       <c r="AO5" s="5">
-        <f t="shared" si="1"/>
-        <v>2.4178401110001819</v>
+        <f t="shared" si="0"/>
+        <v>2.5011058772540951</v>
       </c>
       <c r="AP5" s="5">
-        <f t="shared" si="1"/>
-        <v>2.4548583063930325</v>
+        <f t="shared" si="0"/>
+        <v>2.540608612069815</v>
       </c>
       <c r="AQ5" s="5">
         <f t="shared" si="1"/>
-        <v>2.4918765090987485</v>
+        <v>2.5801112593894571</v>
       </c>
       <c r="AR5" s="5">
         <f t="shared" si="1"/>
-        <v>2.5288947561770851</v>
+        <v>2.6196138974261229</v>
       </c>
       <c r="AS5" s="5">
         <f t="shared" si="1"/>
-        <v>2.5659129832478982</v>
+        <v>2.6591165432664505</v>
       </c>
       <c r="AT5" s="5">
         <f t="shared" si="1"/>
-        <v>2.6029311985158397</v>
+        <v>2.6986192364574273</v>
       </c>
       <c r="AU5" s="5">
         <f t="shared" si="1"/>
-        <v>2.6399494160189714</v>
+        <v>2.7381219082980937</v>
       </c>
       <c r="AV5" s="5">
         <f t="shared" si="1"/>
-        <v>2.6769676379441592</v>
+        <v>2.7776245675437492</v>
       </c>
       <c r="AW5" s="5">
         <f t="shared" si="1"/>
-        <v>2.7139858637132415</v>
+        <v>2.8171272291746075</v>
       </c>
       <c r="AX5" s="5">
         <f t="shared" si="1"/>
-        <v>2.7510040852204729</v>
+        <v>2.8566298955243044</v>
+      </c>
+      <c r="AY5" s="5">
+        <f t="shared" si="1"/>
+        <v>2.8961325659758752</v>
+      </c>
+      <c r="AZ5" s="5">
+        <f t="shared" si="1"/>
+        <v>2.9356352318795649</v>
       </c>
     </row>
-    <row r="6" spans="1:50">
+    <row r="6" spans="1:52">
       <c r="A6" t="s">
         <v>79</v>
       </c>
       <c r="B6">
+        <f>'Oil Prospective'!F17</f>
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <f>'Oil Prospective'!G17</f>
+        <v>1</v>
+      </c>
+      <c r="D6">
         <f>'Oil Prospective'!H17</f>
         <v>1</v>
       </c>
-      <c r="C6">
+      <c r="E6">
         <f>'Oil Prospective'!I17</f>
         <v>1.0075187969924813</v>
       </c>
-      <c r="D6">
+      <c r="F6">
         <f>'Oil Prospective'!J17</f>
         <v>1.0150375939849623</v>
       </c>
-      <c r="E6">
+      <c r="G6">
         <f>'Oil Prospective'!K17</f>
         <v>1.0150375939849623</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <f>'Oil Prospective'!L17</f>
         <v>1.0225563909774436</v>
       </c>
-      <c r="G6">
+      <c r="I6">
         <f>'Oil Prospective'!M17</f>
         <v>1.0300751879699248</v>
       </c>
-      <c r="H6">
+      <c r="J6">
         <f>'Oil Prospective'!N17</f>
         <v>1.0375939849624061</v>
       </c>
-      <c r="I6">
+      <c r="K6">
         <f>'Oil Prospective'!O17</f>
         <v>1.0451127819548871</v>
       </c>
-      <c r="J6">
+      <c r="L6">
         <f>'Oil Prospective'!P17</f>
         <v>1.0526315789473684</v>
       </c>
-      <c r="K6">
+      <c r="M6">
         <f>'Oil Prospective'!Q17</f>
         <v>1.0601503759398496</v>
       </c>
-      <c r="L6">
+      <c r="N6">
         <f>'Oil Prospective'!R17</f>
         <v>1.067669172932332</v>
       </c>
-      <c r="M6">
+      <c r="O6">
         <f>'Oil Prospective'!S17</f>
         <v>1.0751879699248128</v>
       </c>
-      <c r="N6">
+      <c r="P6">
         <f>'Oil Prospective'!T17</f>
         <v>1.0827067669172936</v>
       </c>
-      <c r="O6">
+      <c r="Q6">
         <f>'Oil Prospective'!U17</f>
         <v>1.0902255639097744</v>
       </c>
-      <c r="P6">
+      <c r="R6">
         <f>'Oil Prospective'!V17</f>
         <v>1.0977443609022552</v>
       </c>
-      <c r="Q6">
+      <c r="S6">
         <f>'Oil Prospective'!W17</f>
         <v>1.1052631578947358</v>
       </c>
-      <c r="R6">
+      <c r="T6">
         <f>'Oil Prospective'!X17</f>
         <v>1.1127819548872167</v>
       </c>
-      <c r="S6">
+      <c r="U6">
         <f>'Oil Prospective'!Y17</f>
         <v>1.1203007518796975</v>
       </c>
-      <c r="T6">
+      <c r="V6">
         <f>'Oil Prospective'!Z17</f>
         <v>1.1278195488721783</v>
       </c>
-      <c r="U6">
+      <c r="W6">
         <f>'Oil Prospective'!AA17</f>
         <v>1.1353383458646591</v>
       </c>
-      <c r="V6">
+      <c r="X6">
         <f>'Oil Prospective'!AB17</f>
         <v>1.1428571428571399</v>
       </c>
-      <c r="W6">
+      <c r="Y6">
         <f>'Oil Prospective'!AC17</f>
         <v>1.1503759398496205</v>
       </c>
-      <c r="X6">
+      <c r="Z6">
         <f>'Oil Prospective'!AD17</f>
         <v>1.1578947368421013</v>
       </c>
-      <c r="Y6">
+      <c r="AA6">
         <f>'Oil Prospective'!AE17</f>
         <v>1.1654135338345821</v>
       </c>
-      <c r="Z6">
+      <c r="AB6">
         <f>'Oil Prospective'!AF17</f>
         <v>1.1729323308270629</v>
       </c>
-      <c r="AA6">
+      <c r="AC6">
         <f>'Oil Prospective'!AG17</f>
         <v>1.1804511278195438</v>
       </c>
-      <c r="AB6">
+      <c r="AD6">
         <f>'Oil Prospective'!AH17</f>
         <v>1.1879699248120243</v>
       </c>
-      <c r="AC6">
+      <c r="AE6">
         <f>'Oil Prospective'!AI17</f>
         <v>1.1954887218045052</v>
       </c>
-      <c r="AD6">
+      <c r="AF6">
         <f>'Oil Prospective'!AJ17</f>
         <v>1.203007518796986</v>
       </c>
-      <c r="AE6" s="5">
+      <c r="AG6" s="5">
         <f t="shared" si="0"/>
         <v>1.2105263157894668</v>
       </c>
-      <c r="AF6" s="5">
+      <c r="AH6" s="5">
         <f t="shared" si="0"/>
         <v>1.2180451127819476</v>
       </c>
-      <c r="AG6" s="5">
+      <c r="AI6" s="5">
         <f t="shared" si="0"/>
         <v>1.2255639097744284</v>
       </c>
-      <c r="AH6" s="5">
+      <c r="AJ6" s="5">
         <f t="shared" si="0"/>
         <v>1.2330827067669092</v>
       </c>
-      <c r="AI6" s="5">
+      <c r="AK6" s="5">
         <f t="shared" si="0"/>
         <v>1.24060150375939</v>
       </c>
-      <c r="AJ6" s="5">
+      <c r="AL6" s="5">
         <f t="shared" si="0"/>
         <v>1.2481203007518709</v>
       </c>
-      <c r="AK6" s="5">
+      <c r="AM6" s="5">
         <f t="shared" si="0"/>
         <v>1.2556390977443517</v>
       </c>
-      <c r="AL6" s="5">
+      <c r="AN6" s="5">
         <f t="shared" si="0"/>
         <v>1.2631578947368325</v>
       </c>
-      <c r="AM6" s="5">
+      <c r="AO6" s="5">
         <f t="shared" si="0"/>
         <v>1.2706766917293133</v>
       </c>
-      <c r="AN6" s="5">
+      <c r="AP6" s="5">
         <f t="shared" si="0"/>
         <v>1.2781954887217941</v>
       </c>
-      <c r="AO6" s="5">
+      <c r="AQ6" s="5">
         <f t="shared" si="1"/>
         <v>1.2857142857142749</v>
       </c>
-      <c r="AP6" s="5">
+      <c r="AR6" s="5">
         <f t="shared" si="1"/>
         <v>1.2932330827067557</v>
       </c>
-      <c r="AQ6" s="5">
+      <c r="AS6" s="5">
         <f t="shared" si="1"/>
         <v>1.3007518796992366</v>
       </c>
-      <c r="AR6" s="5">
+      <c r="AT6" s="5">
         <f t="shared" si="1"/>
         <v>1.3082706766917174</v>
       </c>
-      <c r="AS6" s="5">
+      <c r="AU6" s="5">
         <f t="shared" si="1"/>
         <v>1.3157894736841982</v>
       </c>
-      <c r="AT6" s="5">
+      <c r="AV6" s="5">
         <f t="shared" si="1"/>
         <v>1.323308270676679</v>
       </c>
-      <c r="AU6" s="5">
+      <c r="AW6" s="5">
         <f t="shared" si="1"/>
         <v>1.3308270676691598</v>
       </c>
-      <c r="AV6" s="5">
+      <c r="AX6" s="5">
         <f t="shared" si="1"/>
         <v>1.3383458646616406</v>
       </c>
-      <c r="AW6" s="5">
+      <c r="AY6" s="5">
         <f t="shared" si="1"/>
         <v>1.3458646616541214</v>
       </c>
-      <c r="AX6" s="5">
+      <c r="AZ6" s="5">
         <f t="shared" si="1"/>
         <v>1.3533834586466023</v>
       </c>
     </row>
-    <row r="7" spans="1:50">
+    <row r="7" spans="1:52">
       <c r="A7" t="s">
         <v>80</v>
       </c>
@@ -19831,195 +20062,203 @@
       </c>
       <c r="C7">
         <f>'Motorcycles INEGI'!G4</f>
-        <v>1.0590871647245823</v>
+        <v>1.0670054940538001</v>
       </c>
       <c r="D7">
         <f>'Motorcycles INEGI'!H4</f>
-        <v>1.1181743294491644</v>
+        <v>1.1340109881076001</v>
       </c>
       <c r="E7">
         <f>'Motorcycles INEGI'!I4</f>
-        <v>1.1772614941737467</v>
+        <v>1.2010164821614002</v>
       </c>
       <c r="F7">
         <f>'Motorcycles INEGI'!J4</f>
-        <v>1.236348658898329</v>
+        <v>1.2680219762152003</v>
       </c>
       <c r="G7">
         <f>'Motorcycles INEGI'!K4</f>
-        <v>1.2954358236229113</v>
+        <v>1.3350274702690004</v>
       </c>
       <c r="H7">
         <f>'Motorcycles INEGI'!L4</f>
-        <v>1.3545229883474934</v>
+        <v>1.4020329643228002</v>
       </c>
       <c r="I7">
         <f>'Motorcycles INEGI'!M4</f>
-        <v>1.4136101530720757</v>
+        <v>1.4690384583766003</v>
       </c>
       <c r="J7">
         <f>'Motorcycles INEGI'!N4</f>
-        <v>1.472697317796658</v>
+        <v>1.5360439524304004</v>
       </c>
       <c r="K7">
         <f>'Motorcycles INEGI'!O4</f>
-        <v>1.5317844825212403</v>
+        <v>1.6030494464842004</v>
       </c>
       <c r="L7">
         <f>'Motorcycles INEGI'!P4</f>
-        <v>1.5908716472458224</v>
+        <v>1.6700549405380005</v>
       </c>
       <c r="M7">
         <f>'Motorcycles INEGI'!Q4</f>
-        <v>1.6499588119704047</v>
+        <v>1.7370604345918006</v>
       </c>
       <c r="N7">
         <f>'Motorcycles INEGI'!R4</f>
-        <v>1.709045976694987</v>
+        <v>1.8040659286456007</v>
       </c>
       <c r="O7">
         <f>'Motorcycles INEGI'!S4</f>
-        <v>1.7681331414195693</v>
+        <v>1.8710714226994007</v>
       </c>
       <c r="P7">
         <f>'Motorcycles INEGI'!T4</f>
-        <v>1.8272203061441514</v>
+        <v>1.9380769167532008</v>
       </c>
       <c r="Q7">
         <f>'Motorcycles INEGI'!U4</f>
-        <v>1.8863074708687337</v>
+        <v>2.0050824108070007</v>
       </c>
       <c r="R7">
         <f>'Motorcycles INEGI'!V4</f>
-        <v>1.945394635593316</v>
+        <v>2.0720879048608007</v>
       </c>
       <c r="S7">
         <f>'Motorcycles INEGI'!W4</f>
-        <v>2.0044818003178984</v>
+        <v>2.1390933989146008</v>
       </c>
       <c r="T7">
         <f>'Motorcycles INEGI'!X4</f>
-        <v>2.0635689650424807</v>
+        <v>2.2060988929684009</v>
       </c>
       <c r="U7">
         <f>'Motorcycles INEGI'!Y4</f>
-        <v>2.122656129767063</v>
+        <v>2.273104387022201</v>
       </c>
       <c r="V7">
         <f>'Motorcycles INEGI'!Z4</f>
-        <v>2.1817432944916448</v>
+        <v>2.340109881076001</v>
       </c>
       <c r="W7">
         <f>'Motorcycles INEGI'!AA4</f>
-        <v>2.2408304592162271</v>
+        <v>2.4071153751298011</v>
       </c>
       <c r="X7">
         <f>'Motorcycles INEGI'!AB4</f>
-        <v>2.2999176239408095</v>
+        <v>2.4741208691836012</v>
       </c>
       <c r="Y7">
         <f>'Motorcycles INEGI'!AC4</f>
-        <v>2.3590047886653918</v>
+        <v>2.5411263632374013</v>
       </c>
       <c r="Z7">
         <f>'Motorcycles INEGI'!AD4</f>
-        <v>2.4180919533899741</v>
+        <v>2.6081318572912013</v>
       </c>
       <c r="AA7">
         <f>'Motorcycles INEGI'!AE4</f>
-        <v>2.4771791181145564</v>
+        <v>2.6751373513450014</v>
       </c>
       <c r="AB7">
         <f>'Motorcycles INEGI'!AF4</f>
-        <v>2.5362662828391387</v>
+        <v>2.7421428453988015</v>
       </c>
       <c r="AC7">
         <f>'Motorcycles INEGI'!AG4</f>
-        <v>2.595353447563721</v>
+        <v>2.8091483394526016</v>
       </c>
       <c r="AD7">
         <f>'Motorcycles INEGI'!AH4</f>
-        <v>2.6544406122883029</v>
-      </c>
-      <c r="AE7" s="5">
-        <f t="shared" si="0"/>
-        <v>2.7135277770128852</v>
-      </c>
-      <c r="AF7" s="5">
-        <f t="shared" si="0"/>
-        <v>2.7726149417374675</v>
+        <v>2.8761538335064016</v>
+      </c>
+      <c r="AE7">
+        <f>'Motorcycles INEGI'!AI4</f>
+        <v>2.9431593275602017</v>
+      </c>
+      <c r="AF7">
+        <f>'Motorcycles INEGI'!AJ4</f>
+        <v>3.0101648216140018</v>
       </c>
       <c r="AG7" s="5">
         <f t="shared" si="0"/>
-        <v>2.8317021064620498</v>
+        <v>3.0771703156678019</v>
       </c>
       <c r="AH7" s="5">
         <f t="shared" si="0"/>
-        <v>2.8907892711866321</v>
+        <v>3.1441758097216019</v>
       </c>
       <c r="AI7" s="5">
         <f t="shared" si="0"/>
-        <v>2.9498764359112144</v>
+        <v>3.211181303775402</v>
       </c>
       <c r="AJ7" s="5">
         <f t="shared" si="0"/>
-        <v>3.0089636006357967</v>
+        <v>3.2781867978292021</v>
       </c>
       <c r="AK7" s="5">
         <f t="shared" si="0"/>
-        <v>3.068050765360379</v>
+        <v>3.3451922918830022</v>
       </c>
       <c r="AL7" s="5">
         <f t="shared" si="0"/>
-        <v>3.1271379300849613</v>
+        <v>3.4121977859368022</v>
       </c>
       <c r="AM7" s="5">
         <f t="shared" si="0"/>
-        <v>3.1862250948095436</v>
+        <v>3.4792032799906023</v>
       </c>
       <c r="AN7" s="5">
         <f t="shared" si="0"/>
-        <v>3.2453122595341259</v>
+        <v>3.5462087740444024</v>
       </c>
       <c r="AO7" s="5">
-        <f t="shared" si="1"/>
-        <v>3.3043994242587083</v>
+        <f t="shared" si="0"/>
+        <v>3.6132142680982025</v>
       </c>
       <c r="AP7" s="5">
-        <f t="shared" si="1"/>
-        <v>3.3634865889832906</v>
+        <f t="shared" si="0"/>
+        <v>3.6802197621520025</v>
       </c>
       <c r="AQ7" s="5">
         <f t="shared" si="1"/>
-        <v>3.4225737537078729</v>
+        <v>3.7472252562058026</v>
       </c>
       <c r="AR7" s="5">
         <f t="shared" si="1"/>
-        <v>3.4816609184324552</v>
+        <v>3.8142307502596027</v>
       </c>
       <c r="AS7" s="5">
         <f t="shared" si="1"/>
-        <v>3.5407480831570375</v>
+        <v>3.8812362443134028</v>
       </c>
       <c r="AT7" s="5">
         <f t="shared" si="1"/>
-        <v>3.5998352478816198</v>
+        <v>3.9482417383672028</v>
       </c>
       <c r="AU7" s="5">
         <f t="shared" si="1"/>
-        <v>3.6589224126062021</v>
+        <v>4.0152472324210029</v>
       </c>
       <c r="AV7" s="5">
         <f t="shared" si="1"/>
-        <v>3.7180095773307844</v>
+        <v>4.0822527264748025</v>
       </c>
       <c r="AW7" s="5">
         <f t="shared" si="1"/>
-        <v>3.7770967420553667</v>
+        <v>4.1492582205286022</v>
       </c>
       <c r="AX7" s="5">
         <f t="shared" si="1"/>
-        <v>3.836183906779949</v>
+        <v>4.2162637145824018</v>
+      </c>
+      <c r="AY7" s="5">
+        <f t="shared" si="1"/>
+        <v>4.2832692086362014</v>
+      </c>
+      <c r="AZ7" s="5">
+        <f t="shared" si="1"/>
+        <v>4.350274702690001</v>
       </c>
     </row>
   </sheetData>
@@ -20032,1170 +20271,1217 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AX7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="2" max="3" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" ht="80.099999999999994">
+    <row r="1" spans="1:52" ht="75">
       <c r="A1" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B1">
+      <c r="B1" s="4">
+        <v>2020</v>
+      </c>
+      <c r="C1" s="4">
+        <v>2021</v>
+      </c>
+      <c r="D1">
         <v>2022</v>
       </c>
-      <c r="C1">
+      <c r="E1">
         <v>2023</v>
       </c>
-      <c r="D1">
+      <c r="F1">
         <v>2024</v>
       </c>
-      <c r="E1">
+      <c r="G1">
         <v>2025</v>
       </c>
-      <c r="F1">
+      <c r="H1">
         <v>2026</v>
       </c>
-      <c r="G1">
+      <c r="I1">
         <v>2027</v>
       </c>
-      <c r="H1">
+      <c r="J1">
         <v>2028</v>
       </c>
-      <c r="I1">
+      <c r="K1">
         <v>2029</v>
       </c>
-      <c r="J1">
+      <c r="L1">
         <v>2030</v>
       </c>
-      <c r="K1">
+      <c r="M1">
         <v>2031</v>
       </c>
-      <c r="L1">
+      <c r="N1">
         <v>2032</v>
       </c>
-      <c r="M1">
+      <c r="O1">
         <v>2033</v>
       </c>
-      <c r="N1">
+      <c r="P1">
         <v>2034</v>
       </c>
-      <c r="O1">
+      <c r="Q1">
         <v>2035</v>
       </c>
-      <c r="P1">
+      <c r="R1">
         <v>2036</v>
       </c>
-      <c r="Q1">
+      <c r="S1">
         <v>2037</v>
       </c>
-      <c r="R1">
+      <c r="T1">
         <v>2038</v>
       </c>
-      <c r="S1">
+      <c r="U1">
         <v>2039</v>
       </c>
-      <c r="T1">
+      <c r="V1">
         <v>2040</v>
       </c>
-      <c r="U1">
+      <c r="W1">
         <v>2041</v>
       </c>
-      <c r="V1">
+      <c r="X1">
         <v>2042</v>
       </c>
-      <c r="W1">
+      <c r="Y1">
         <v>2043</v>
       </c>
-      <c r="X1">
+      <c r="Z1">
         <v>2044</v>
       </c>
-      <c r="Y1">
+      <c r="AA1">
         <v>2045</v>
       </c>
-      <c r="Z1">
+      <c r="AB1">
         <v>2046</v>
       </c>
-      <c r="AA1">
+      <c r="AC1">
         <v>2047</v>
       </c>
-      <c r="AB1">
+      <c r="AD1">
         <v>2048</v>
       </c>
-      <c r="AC1">
+      <c r="AE1">
         <v>2049</v>
       </c>
-      <c r="AD1">
+      <c r="AF1">
         <v>2050</v>
       </c>
-      <c r="AE1">
+      <c r="AG1">
         <v>2051</v>
       </c>
-      <c r="AF1">
+      <c r="AH1">
         <v>2052</v>
       </c>
-      <c r="AG1">
+      <c r="AI1">
         <v>2053</v>
       </c>
-      <c r="AH1">
+      <c r="AJ1">
         <v>2054</v>
       </c>
-      <c r="AI1">
+      <c r="AK1">
         <v>2055</v>
       </c>
-      <c r="AJ1">
+      <c r="AL1">
         <v>2056</v>
       </c>
-      <c r="AK1">
+      <c r="AM1">
         <v>2057</v>
       </c>
-      <c r="AL1">
+      <c r="AN1">
         <v>2058</v>
       </c>
-      <c r="AM1">
+      <c r="AO1">
         <v>2059</v>
       </c>
-      <c r="AN1">
+      <c r="AP1">
         <v>2060</v>
       </c>
-      <c r="AO1">
+      <c r="AQ1">
         <v>2061</v>
       </c>
-      <c r="AP1">
+      <c r="AR1">
         <v>2062</v>
       </c>
-      <c r="AQ1">
+      <c r="AS1">
         <v>2063</v>
       </c>
-      <c r="AR1">
+      <c r="AT1">
         <v>2064</v>
       </c>
-      <c r="AS1">
+      <c r="AU1">
         <v>2065</v>
       </c>
-      <c r="AT1">
+      <c r="AV1">
         <v>2066</v>
       </c>
-      <c r="AU1">
+      <c r="AW1">
         <v>2067</v>
       </c>
-      <c r="AV1">
+      <c r="AX1">
         <v>2068</v>
       </c>
-      <c r="AW1">
+      <c r="AY1">
         <v>2069</v>
       </c>
-      <c r="AX1">
+      <c r="AZ1">
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:50">
+    <row r="2" spans="1:52">
       <c r="A2" t="s">
         <v>75</v>
       </c>
       <c r="B2">
+        <f>'Mexico-Christopher'!BY51</f>
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <f>'Mexico-Christopher'!BZ51</f>
+        <v>1.0385932627131045</v>
+      </c>
+      <c r="D2">
         <f>'Mexico-Christopher'!CA51</f>
-        <v>1</v>
-      </c>
-      <c r="C2">
+        <v>1.0784414487732614</v>
+      </c>
+      <c r="E2">
         <f>'Mexico-Christopher'!CB51</f>
-        <v>1.0387392462524345</v>
-      </c>
-      <c r="D2">
+        <v>1.1202194576261209</v>
+      </c>
+      <c r="F2">
         <f>'Mexico-Christopher'!CC51</f>
-        <v>1.0790492895406165</v>
-      </c>
-      <c r="E2">
+        <v>1.1636914791099409</v>
+      </c>
+      <c r="G2">
         <f>'Mexico-Christopher'!CD51</f>
-        <v>1.1205053065006412</v>
-      </c>
-      <c r="F2">
+        <v>1.2083993661006789</v>
+      </c>
+      <c r="H2">
         <f>'Mexico-Christopher'!CE51</f>
-        <v>1.1630675066617655</v>
-      </c>
-      <c r="G2">
+        <v>1.254300206905419</v>
+      </c>
+      <c r="I2">
         <f>'Mexico-Christopher'!CF51</f>
-        <v>1.2071588757340246</v>
-      </c>
-      <c r="H2">
+        <v>1.3018501668461027</v>
+      </c>
+      <c r="J2">
         <f>'Mexico-Christopher'!CG51</f>
-        <v>1.2525224703363345</v>
-      </c>
-      <c r="I2">
+        <v>1.3507721475305807</v>
+      </c>
+      <c r="K2">
         <f>'Mexico-Christopher'!CH51</f>
-        <v>1.2992423825058057</v>
-      </c>
-      <c r="J2">
+        <v>1.401156837297185</v>
+      </c>
+      <c r="L2">
         <f>'Mexico-Christopher'!CI51</f>
-        <v>1.3472606532030782</v>
-      </c>
-      <c r="K2">
+        <v>1.4529417307155381</v>
+      </c>
+      <c r="M2">
         <f>'Mexico-Christopher'!CJ51</f>
-        <v>1.3963475688467002</v>
-      </c>
-      <c r="L2">
+        <v>1.5058790951380567</v>
+      </c>
+      <c r="N2">
         <f>'Mexico-Christopher'!CK51</f>
-        <v>1.4464209892284916</v>
-      </c>
-      <c r="M2">
+        <v>1.5598803471596283</v>
+      </c>
+      <c r="O2">
         <f>'Mexico-Christopher'!CL51</f>
-        <v>1.4973369430490049</v>
-      </c>
-      <c r="N2">
+        <v>1.6147902221634951</v>
+      </c>
+      <c r="P2">
         <f>'Mexico-Christopher'!CM51</f>
-        <v>1.5491442146359522</v>
-      </c>
-      <c r="O2">
+        <v>1.6706613311907124</v>
+      </c>
+      <c r="Q2">
         <f>'Mexico-Christopher'!CN51</f>
-        <v>1.5737401650449261</v>
-      </c>
-      <c r="P2">
+        <v>1.6971866235837214</v>
+      </c>
+      <c r="R2">
         <f>'Mexico-Christopher'!CO51</f>
-        <v>1.5987589600531527</v>
-      </c>
-      <c r="Q2">
+        <v>1.7241679291189547</v>
+      </c>
+      <c r="S2">
         <f>'Mexico-Christopher'!CP51</f>
-        <v>1.6242081999237592</v>
-      </c>
-      <c r="R2">
+        <v>1.7516134442351898</v>
+      </c>
+      <c r="T2">
         <f>'Mexico-Christopher'!CQ51</f>
-        <v>1.650095624867453</v>
-      </c>
-      <c r="S2">
+        <v>1.779531516296476</v>
+      </c>
+      <c r="U2">
         <f>'Mexico-Christopher'!CR51</f>
-        <v>1.6764291176522408</v>
-      </c>
-      <c r="T2">
+        <v>1.8079306464065628</v>
+      </c>
+      <c r="V2">
         <f>'Mexico-Christopher'!CS51</f>
-        <v>1.7032167062621333</v>
-      </c>
-      <c r="U2">
+        <v>1.8368194922761574</v>
+      </c>
+      <c r="W2">
         <f>'Mexico-Christopher'!CT51</f>
-        <v>1.730466566605751</v>
-      </c>
-      <c r="V2">
+        <v>1.8662068711439974</v>
+      </c>
+      <c r="X2">
         <f>'Mexico-Christopher'!CU51</f>
-        <v>1.7581870252757765</v>
-      </c>
-      <c r="W2">
+        <v>1.8961017627527592</v>
+      </c>
+      <c r="Y2">
         <f>'Mexico-Christopher'!CV51</f>
-        <v>1.7863865623602082</v>
-      </c>
-      <c r="X2">
+        <v>1.9265133123808289</v>
+      </c>
+      <c r="Z2">
         <f>'Mexico-Christopher'!CW51</f>
-        <v>1.81507381430639</v>
-      </c>
-      <c r="Y2">
+        <v>1.9574508339309926</v>
+      </c>
+      <c r="AA2">
         <f>'Mexico-Christopher'!CX51</f>
-        <v>1.844257576838815</v>
-      </c>
-      <c r="Z2">
+        <v>1.9889238130771161</v>
+      </c>
+      <c r="AB2">
         <f>'Mexico-Christopher'!CY51</f>
-        <v>1.8739468079317096</v>
-      </c>
-      <c r="AA2">
+        <v>2.0209419104699013</v>
+      </c>
+      <c r="AC2">
         <f>'Mexico-Christopher'!CZ51</f>
-        <v>1.9041506308374387</v>
-      </c>
-      <c r="AB2">
+        <v>2.0535149650028468</v>
+      </c>
+      <c r="AD2">
         <f>'Mexico-Christopher'!DA51</f>
-        <v>1.934878337171771</v>
-      </c>
-      <c r="AC2">
+        <v>2.0866529971395233</v>
+      </c>
+      <c r="AE2">
         <f>'Mexico-Christopher'!DB51</f>
-        <v>1.9661393900570896</v>
-      </c>
-      <c r="AD2">
+        <v>2.120366212303344</v>
+      </c>
+      <c r="AF2">
         <f>'Mexico-Christopher'!DC51</f>
-        <v>1.9979434273246284</v>
-      </c>
-      <c r="AE2" s="5">
-        <f t="shared" ref="AE2:AX7" si="0">AD2+(AD2-Y2)/5</f>
-        <v>2.0286805974217912</v>
-      </c>
-      <c r="AF2" s="5">
-        <f t="shared" si="0"/>
-        <v>2.0596273553198077</v>
+        <v>2.1546650043309876</v>
       </c>
       <c r="AG2" s="5">
-        <f t="shared" si="0"/>
-        <v>2.0907227002162814</v>
+        <f t="shared" ref="AG2:AZ7" si="0">AF2+(AF2-AA2)/5</f>
+        <v>2.187813242581762</v>
       </c>
       <c r="AH2" s="5">
         <f t="shared" si="0"/>
-        <v>2.1218915728251835</v>
+        <v>2.221187509004134</v>
       </c>
       <c r="AI2" s="5">
         <f t="shared" si="0"/>
-        <v>2.1530420093788023</v>
+        <v>2.2547220178043914</v>
       </c>
       <c r="AJ2" s="5">
         <f t="shared" si="0"/>
-        <v>2.1840617257896371</v>
+        <v>2.2883358219373648</v>
       </c>
       <c r="AK2" s="5">
         <f t="shared" si="0"/>
-        <v>2.2151379514632064</v>
+        <v>2.3219297438641688</v>
       </c>
       <c r="AL2" s="5">
         <f t="shared" si="0"/>
-        <v>2.2462400706918859</v>
+        <v>2.3553826917708052</v>
       </c>
       <c r="AM2" s="5">
         <f t="shared" si="0"/>
-        <v>2.2773435447870067</v>
+        <v>2.3888965816086136</v>
       </c>
       <c r="AN2" s="5">
         <f t="shared" si="0"/>
-        <v>2.3084339391793716</v>
+        <v>2.4224383961295097</v>
       </c>
       <c r="AO2" s="5">
         <f t="shared" si="0"/>
-        <v>2.3395123251394856</v>
+        <v>2.4559816717945333</v>
       </c>
       <c r="AP2" s="5">
         <f t="shared" si="0"/>
-        <v>2.3706024450094554</v>
+        <v>2.4895108417659668</v>
       </c>
       <c r="AQ2" s="5">
         <f t="shared" si="0"/>
-        <v>2.4016953437187052</v>
+        <v>2.5230270613463266</v>
       </c>
       <c r="AR2" s="5">
         <f t="shared" si="0"/>
-        <v>2.432786398324069</v>
+        <v>2.5565559352614309</v>
       </c>
       <c r="AS2" s="5">
         <f t="shared" si="0"/>
-        <v>2.4638749690314814</v>
+        <v>2.5900878059919945</v>
       </c>
       <c r="AT2" s="5">
         <f t="shared" si="0"/>
-        <v>2.4949631750019035</v>
+        <v>2.6236176879644915</v>
       </c>
       <c r="AU2" s="5">
         <f t="shared" si="0"/>
-        <v>2.5260533449743869</v>
+        <v>2.6571448911984832</v>
       </c>
       <c r="AV2" s="5">
         <f t="shared" si="0"/>
-        <v>2.5571435249673731</v>
+        <v>2.6906717010849865</v>
       </c>
       <c r="AW2" s="5">
         <f t="shared" si="0"/>
-        <v>2.5882331612171066</v>
+        <v>2.7242006290327185</v>
       </c>
       <c r="AX2" s="5">
         <f t="shared" si="0"/>
-        <v>2.6193225137957139</v>
+        <v>2.757729567786976</v>
+      </c>
+      <c r="AY2" s="5">
+        <f t="shared" si="0"/>
+        <v>2.7912579201459722</v>
+      </c>
+      <c r="AZ2" s="5">
+        <f t="shared" si="0"/>
+        <v>2.8247859665822683</v>
       </c>
     </row>
-    <row r="3" spans="1:50">
+    <row r="3" spans="1:52">
       <c r="A3" t="s">
         <v>76</v>
       </c>
       <c r="B3">
+        <f>'Mexico-Christopher'!BY52</f>
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <f>'Mexico-Christopher'!BZ52</f>
+        <v>1.0385304103583184</v>
+      </c>
+      <c r="D3">
         <f>'Mexico-Christopher'!CA52</f>
-        <v>1</v>
-      </c>
-      <c r="C3">
+        <v>1.0767815246643786</v>
+      </c>
+      <c r="E3">
         <f>'Mexico-Christopher'!CB52</f>
-        <v>1.0366928505573572</v>
-      </c>
-      <c r="D3">
+        <v>1.116291708231812</v>
+      </c>
+      <c r="F3">
         <f>'Mexico-Christopher'!CC52</f>
-        <v>1.0747457226603214</v>
-      </c>
-      <c r="E3">
+        <v>1.1572663378727004</v>
+      </c>
+      <c r="G3">
         <f>'Mexico-Christopher'!CD52</f>
-        <v>1.1129713773465184</v>
-      </c>
-      <c r="F3">
+        <v>1.1984270166069975</v>
+      </c>
+      <c r="H3">
         <f>'Mexico-Christopher'!CE52</f>
-        <v>1.1508897605862682</v>
-      </c>
-      <c r="G3">
+        <v>1.2392568311247036</v>
+      </c>
+      <c r="I3">
         <f>'Mexico-Christopher'!CF52</f>
-        <v>1.1896502082696867</v>
-      </c>
-      <c r="H3">
+        <v>1.280993365077929</v>
+      </c>
+      <c r="J3">
         <f>'Mexico-Christopher'!CG52</f>
-        <v>1.2289208288140567</v>
-      </c>
-      <c r="I3">
+        <v>1.3232792437422118</v>
+      </c>
+      <c r="K3">
         <f>'Mexico-Christopher'!CH52</f>
-        <v>1.2685780737967898</v>
-      </c>
-      <c r="J3">
+        <v>1.3659814324587078</v>
+      </c>
+      <c r="L3">
         <f>'Mexico-Christopher'!CI52</f>
-        <v>1.308431797012628</v>
-      </c>
-      <c r="K3">
+        <v>1.4088951853066105</v>
+      </c>
+      <c r="M3">
         <f>'Mexico-Christopher'!CJ52</f>
-        <v>1.3476040478621698</v>
-      </c>
-      <c r="L3">
+        <v>1.4510751413009155</v>
+      </c>
+      <c r="N3">
         <f>'Mexico-Christopher'!CK52</f>
-        <v>1.3857333624672377</v>
-      </c>
-      <c r="M3">
+        <v>1.4921320828157683</v>
+      </c>
+      <c r="O3">
         <f>'Mexico-Christopher'!CL52</f>
-        <v>1.4234019521852281</v>
-      </c>
-      <c r="N3">
+        <v>1.5326929242842628</v>
+      </c>
+      <c r="P3">
         <f>'Mexico-Christopher'!CM52</f>
-        <v>1.4613884740306986</v>
-      </c>
-      <c r="O3">
+        <v>1.5735961091937254</v>
+      </c>
+      <c r="Q3">
         <f>'Mexico-Christopher'!CN52</f>
-        <v>1.4779253094881875</v>
-      </c>
-      <c r="P3">
+        <v>1.5914026680907642</v>
+      </c>
+      <c r="R3">
         <f>'Mexico-Christopher'!CO52</f>
-        <v>1.4946509724334369</v>
-      </c>
-      <c r="Q3">
+        <v>1.6094125529379724</v>
+      </c>
+      <c r="S3">
         <f>'Mexico-Christopher'!CP52</f>
-        <v>1.5115676386059371</v>
-      </c>
-      <c r="R3">
+        <v>1.6276281065314355</v>
+      </c>
+      <c r="T3">
         <f>'Mexico-Christopher'!CQ52</f>
-        <v>1.5286775090439715</v>
-      </c>
-      <c r="S3">
+        <v>1.6460516989085121</v>
+      </c>
+      <c r="U3">
         <f>'Mexico-Christopher'!CR52</f>
-        <v>1.5459828103814854</v>
-      </c>
-      <c r="T3">
+        <v>1.6646857276674969</v>
+      </c>
+      <c r="V3">
         <f>'Mexico-Christopher'!CS52</f>
-        <v>1.5634857951484729</v>
-      </c>
-      <c r="U3">
+        <v>1.683532618291071</v>
+      </c>
+      <c r="W3">
         <f>'Mexico-Christopher'!CT52</f>
-        <v>1.58118874207492</v>
-      </c>
-      <c r="V3">
+        <v>1.7025948244735833</v>
+      </c>
+      <c r="X3">
         <f>'Mexico-Christopher'!CU52</f>
-        <v>1.5990939563983482</v>
-      </c>
-      <c r="W3">
+        <v>1.7218748284522067</v>
+      </c>
+      <c r="Y3">
         <f>'Mexico-Christopher'!CV52</f>
-        <v>1.6172037701750008</v>
-      </c>
-      <c r="X3">
+        <v>1.7413751413420189</v>
+      </c>
+      <c r="Z3">
         <f>'Mexico-Christopher'!CW52</f>
-        <v>1.635520542594719</v>
-      </c>
-      <c r="Y3">
+        <v>1.7610983034750534</v>
+      </c>
+      <c r="AA3">
         <f>'Mexico-Christopher'!CX52</f>
-        <v>1.6540466602995441</v>
-      </c>
-      <c r="Z3">
+        <v>1.7810468847433665</v>
+      </c>
+      <c r="AB3">
         <f>'Mexico-Christopher'!CY52</f>
-        <v>1.672784537706099</v>
-      </c>
-      <c r="AA3">
+        <v>1.8012234849461712</v>
+      </c>
+      <c r="AC3">
         <f>'Mexico-Christopher'!CZ52</f>
-        <v>1.6917366173317909</v>
-      </c>
-      <c r="AB3">
+        <v>1.8216307341410845</v>
+      </c>
+      <c r="AD3">
         <f>'Mexico-Christopher'!DA52</f>
-        <v>1.7109053701248744</v>
-      </c>
-      <c r="AC3">
+        <v>1.8422712929995353</v>
+      </c>
+      <c r="AE3">
         <f>'Mexico-Christopher'!DB52</f>
-        <v>1.7302932957984352</v>
-      </c>
-      <c r="AD3">
+        <v>1.8631478531663916</v>
+      </c>
+      <c r="AF3">
         <f>'Mexico-Christopher'!DC52</f>
-        <v>1.7499029231683283</v>
-      </c>
-      <c r="AE3" s="5">
-        <f t="shared" si="0"/>
-        <v>1.7690741757420851</v>
-      </c>
-      <c r="AF3" s="5">
-        <f t="shared" si="0"/>
-        <v>1.7883321033492823</v>
+        <v>1.8842631376238455</v>
       </c>
       <c r="AG3" s="5">
         <f t="shared" si="0"/>
-        <v>1.8076512005527805</v>
+        <v>1.9049063881999413</v>
       </c>
       <c r="AH3" s="5">
         <f t="shared" si="0"/>
-        <v>1.8270003666383616</v>
+        <v>1.9256429688506953</v>
       </c>
       <c r="AI3" s="5">
         <f t="shared" si="0"/>
-        <v>1.8463417808063469</v>
+        <v>1.9464454157926174</v>
       </c>
       <c r="AJ3" s="5">
         <f t="shared" si="0"/>
-        <v>1.8656295523339506</v>
+        <v>1.9672802403512339</v>
       </c>
       <c r="AK3" s="5">
         <f t="shared" si="0"/>
-        <v>1.8849406276523237</v>
+        <v>1.9881067177882024</v>
       </c>
       <c r="AL3" s="5">
         <f t="shared" si="0"/>
-        <v>1.904262332512932</v>
+        <v>2.0088754338210739</v>
       </c>
       <c r="AM3" s="5">
         <f t="shared" si="0"/>
-        <v>1.9235845589049623</v>
+        <v>2.0296692429453005</v>
       </c>
       <c r="AN3" s="5">
         <f t="shared" si="0"/>
-        <v>1.9429013973582825</v>
+        <v>2.0504744977642213</v>
       </c>
       <c r="AO3" s="5">
         <f t="shared" si="0"/>
-        <v>1.9622133206686696</v>
+        <v>2.0712803141585421</v>
       </c>
       <c r="AP3" s="5">
         <f t="shared" si="0"/>
-        <v>1.9815300743356135</v>
+        <v>2.0920803289200038</v>
       </c>
       <c r="AQ3" s="5">
         <f t="shared" si="0"/>
-        <v>2.0008479636722716</v>
+        <v>2.1128750511463643</v>
       </c>
       <c r="AR3" s="5">
         <f t="shared" si="0"/>
-        <v>2.0201650899041397</v>
+        <v>2.1336749746114223</v>
       </c>
       <c r="AS3" s="5">
         <f t="shared" si="0"/>
-        <v>2.0394811961039752</v>
+        <v>2.1544761209446466</v>
       </c>
       <c r="AT3" s="5">
         <f t="shared" si="0"/>
-        <v>2.0587971558531137</v>
+        <v>2.1752764455807316</v>
       </c>
       <c r="AU3" s="5">
         <f t="shared" si="0"/>
-        <v>2.0781139228900027</v>
+        <v>2.1960756718651697</v>
       </c>
       <c r="AV3" s="5">
         <f t="shared" si="0"/>
-        <v>2.0974306926008808</v>
+        <v>2.2168747404542031</v>
       </c>
       <c r="AW3" s="5">
         <f t="shared" si="0"/>
-        <v>2.1167472383866026</v>
+        <v>2.2376746783157708</v>
       </c>
       <c r="AX3" s="5">
         <f t="shared" si="0"/>
-        <v>2.1360636680830951</v>
+        <v>2.2584746190566407</v>
+      </c>
+      <c r="AY3" s="5">
+        <f t="shared" si="0"/>
+        <v>2.2792743186790396</v>
+      </c>
+      <c r="AZ3" s="5">
+        <f t="shared" si="0"/>
+        <v>2.300073893298701</v>
       </c>
     </row>
-    <row r="4" spans="1:50">
+    <row r="4" spans="1:52">
       <c r="A4" t="s">
         <v>77</v>
       </c>
       <c r="B4">
+        <f>'Oil Prospective'!F15</f>
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <f>'Oil Prospective'!G15</f>
+        <v>1.0286054827175208</v>
+      </c>
+      <c r="D4">
         <f>'Oil Prospective'!H15</f>
-        <v>1</v>
-      </c>
-      <c r="C4" s="7">
+        <v>1.0584028605482716</v>
+      </c>
+      <c r="E4" s="7">
         <f>'Oil Prospective'!I15</f>
-        <v>1.0292792792792793</v>
-      </c>
-      <c r="D4" s="7">
+        <v>1.0893921334922527</v>
+      </c>
+      <c r="F4" s="7">
         <f>'Oil Prospective'!J15</f>
-        <v>1.0585585585585586</v>
-      </c>
-      <c r="E4" s="7">
+        <v>1.1203814064362336</v>
+      </c>
+      <c r="G4" s="7">
         <f>'Oil Prospective'!K15</f>
-        <v>1.0889639639639641</v>
-      </c>
-      <c r="F4" s="7">
+        <v>1.1525625744934445</v>
+      </c>
+      <c r="H4" s="7">
         <f>'Oil Prospective'!L15</f>
-        <v>1.1204954954954955</v>
-      </c>
-      <c r="G4" s="7">
+        <v>1.1859356376638854</v>
+      </c>
+      <c r="I4" s="7">
         <f>'Oil Prospective'!M15</f>
-        <v>1.1542792792792793</v>
-      </c>
-      <c r="H4" s="7">
+        <v>1.2216924910607865</v>
+      </c>
+      <c r="J4" s="7">
         <f>'Oil Prospective'!N15</f>
-        <v>1.1880630630630631</v>
-      </c>
-      <c r="I4" s="7">
+        <v>1.2574493444576877</v>
+      </c>
+      <c r="K4" s="7">
         <f>'Oil Prospective'!O15</f>
-        <v>1.222972972972973</v>
-      </c>
-      <c r="J4" s="7">
+        <v>1.2943980929678187</v>
+      </c>
+      <c r="L4" s="7">
         <f>'Oil Prospective'!P15</f>
-        <v>1.2601351351351353</v>
-      </c>
-      <c r="K4" s="7">
+        <v>1.33373063170441</v>
+      </c>
+      <c r="M4" s="7">
         <f>'Oil Prospective'!Q15</f>
-        <v>1.2972972972972974</v>
-      </c>
-      <c r="L4" s="7">
+        <v>1.3730631704410012</v>
+      </c>
+      <c r="N4" s="7">
         <f>'Oil Prospective'!R15</f>
-        <v>1.3319819819819791</v>
-      </c>
-      <c r="M4" s="7">
+        <v>1.4097735399284832</v>
+      </c>
+      <c r="O4" s="7">
         <f>'Oil Prospective'!S15</f>
-        <v>1.3687387387387373</v>
-      </c>
-      <c r="N4" s="7">
+        <v>1.4486769964243129</v>
+      </c>
+      <c r="P4" s="7">
         <f>'Oil Prospective'!T15</f>
-        <v>1.4052387387387315</v>
-      </c>
-      <c r="O4" s="7">
+        <v>1.4873087008343187</v>
+      </c>
+      <c r="Q4" s="7">
         <f>'Oil Prospective'!U15</f>
-        <v>1.4411729729729748</v>
-      </c>
-      <c r="P4" s="7">
+        <v>1.5253415971394535</v>
+      </c>
+      <c r="R4" s="7">
         <f>'Oil Prospective'!V15</f>
-        <v>1.4771883783783688</v>
-      </c>
-      <c r="Q4" s="7">
+        <v>1.5634604052443282</v>
+      </c>
+      <c r="S4" s="7">
         <f>'Oil Prospective'!W15</f>
-        <v>1.5137182702702676</v>
-      </c>
-      <c r="R4" s="7">
+        <v>1.6021237473182328</v>
+      </c>
+      <c r="T4" s="7">
         <f>'Oil Prospective'!X15</f>
-        <v>1.5497840306306283</v>
-      </c>
-      <c r="S4" s="7">
+        <v>1.6402958512514874</v>
+      </c>
+      <c r="U4" s="7">
         <f>'Oil Prospective'!Y15</f>
-        <v>1.585911242522515</v>
-      </c>
-      <c r="T4" s="7">
+        <v>1.6785329956614938</v>
+      </c>
+      <c r="V4" s="7">
         <f>'Oil Prospective'!Z15</f>
-        <v>1.6221766363603489</v>
-      </c>
-      <c r="U4" s="7">
+        <v>1.7169163922383666</v>
+      </c>
+      <c r="W4" s="7">
         <f>'Oil Prospective'!AA15</f>
-        <v>1.6584065580972849</v>
-      </c>
-      <c r="V4" s="7">
+        <v>1.7552622450421798</v>
+      </c>
+      <c r="X4" s="7">
         <f>'Oil Prospective'!AB15</f>
-        <v>1.6945301019913346</v>
-      </c>
-      <c r="W4" s="7">
+        <v>1.7934955072327829</v>
+      </c>
+      <c r="Y4" s="7">
         <f>'Oil Prospective'!AC15</f>
-        <v>1.7307579514092779</v>
-      </c>
-      <c r="X4" s="7">
+        <v>1.8318391666882463</v>
+      </c>
+      <c r="Z4" s="7">
         <f>'Oil Prospective'!AD15</f>
-        <v>1.7669705630974966</v>
-      </c>
-      <c r="Y4" s="7">
+        <v>1.8701666984869807</v>
+      </c>
+      <c r="AA4" s="7">
         <f>'Oil Prospective'!AE15</f>
-        <v>1.8031501362270319</v>
-      </c>
-      <c r="Z4" s="7">
+        <v>1.9084592621806964</v>
+      </c>
+      <c r="AB4" s="7">
         <f>'Oil Prospective'!AF15</f>
-        <v>1.839341347374178</v>
-      </c>
-      <c r="AA4" s="7">
+        <v>1.9467641435855421</v>
+      </c>
+      <c r="AC4" s="7">
         <f>'Oil Prospective'!AG15</f>
-        <v>1.8755544226949061</v>
-      </c>
-      <c r="AB4" s="7">
+        <v>1.9850921660942509</v>
+      </c>
+      <c r="AD4" s="7">
         <f>'Oil Prospective'!AH15</f>
-        <v>1.9117440022149585</v>
-      </c>
-      <c r="AC4" s="7">
+        <v>2.0233953205803132</v>
+      </c>
+      <c r="AE4" s="7">
         <f>'Oil Prospective'!AI15</f>
-        <v>1.9479374437325638</v>
-      </c>
-      <c r="AD4" s="7">
+        <v>2.0617025626156336</v>
+      </c>
+      <c r="AF4" s="7">
         <f>'Oil Prospective'!AJ15</f>
-        <v>1.984138651404278</v>
-      </c>
-      <c r="AE4" s="5">
-        <f t="shared" si="0"/>
-        <v>2.0203363544397273</v>
-      </c>
-      <c r="AF4" s="5">
-        <f t="shared" si="0"/>
-        <v>2.0565353558528372</v>
+        <v>2.1000180243706779</v>
       </c>
       <c r="AG4" s="5">
         <f t="shared" si="0"/>
-        <v>2.0927315424844233</v>
+        <v>2.138329776808674</v>
       </c>
       <c r="AH4" s="5">
         <f t="shared" si="0"/>
-        <v>2.128929050538316</v>
+        <v>2.1766429034533004</v>
       </c>
       <c r="AI4" s="5">
         <f t="shared" si="0"/>
-        <v>2.1651273718994664</v>
+        <v>2.2149530509251103</v>
       </c>
       <c r="AJ4" s="5">
         <f t="shared" si="0"/>
-        <v>2.2013251159985039</v>
+        <v>2.2532645969940699</v>
       </c>
       <c r="AK4" s="5">
         <f t="shared" si="0"/>
-        <v>2.237522868310259</v>
+        <v>2.2915770038697572</v>
       </c>
       <c r="AL4" s="5">
         <f t="shared" si="0"/>
-        <v>2.2737203708017435</v>
+        <v>2.3298887997695732</v>
       </c>
       <c r="AM4" s="5">
         <f t="shared" si="0"/>
-        <v>2.3099181364652077</v>
+        <v>2.3682006043617529</v>
       </c>
       <c r="AN4" s="5">
         <f t="shared" si="0"/>
-        <v>2.3461159536505862</v>
+        <v>2.4065121445434436</v>
       </c>
       <c r="AO4" s="5">
         <f t="shared" si="0"/>
-        <v>2.3823136700008103</v>
+        <v>2.4448239632671105</v>
       </c>
       <c r="AP4" s="5">
         <f t="shared" si="0"/>
-        <v>2.4185113808012715</v>
+        <v>2.4831358365217184</v>
       </c>
       <c r="AQ4" s="5">
         <f t="shared" si="0"/>
-        <v>2.4547090832994738</v>
+        <v>2.5214476030521107</v>
       </c>
       <c r="AR4" s="5">
         <f t="shared" si="0"/>
-        <v>2.4909068257990197</v>
+        <v>2.559759363708618</v>
       </c>
       <c r="AS4" s="5">
         <f t="shared" si="0"/>
-        <v>2.5271045636657821</v>
+        <v>2.5980711155779912</v>
       </c>
       <c r="AT4" s="5">
         <f t="shared" si="0"/>
-        <v>2.5633022856688212</v>
+        <v>2.6363829097849005</v>
       </c>
       <c r="AU4" s="5">
         <f t="shared" si="0"/>
-        <v>2.5995000088024236</v>
+        <v>2.6746946990884584</v>
       </c>
       <c r="AV4" s="5">
         <f t="shared" si="0"/>
-        <v>2.6356977344026542</v>
+        <v>2.7130064716018065</v>
       </c>
       <c r="AW4" s="5">
         <f t="shared" si="0"/>
-        <v>2.6718954646232902</v>
+        <v>2.7513182453117455</v>
       </c>
       <c r="AX4" s="5">
         <f t="shared" si="0"/>
-        <v>2.7080931923881444</v>
+        <v>2.7896300216323708</v>
+      </c>
+      <c r="AY4" s="5">
+        <f t="shared" si="0"/>
+        <v>2.8279418028432466</v>
+      </c>
+      <c r="AZ4" s="5">
+        <f t="shared" si="0"/>
+        <v>2.8662535814549157</v>
       </c>
     </row>
-    <row r="5" spans="1:50">
+    <row r="5" spans="1:52">
       <c r="A5" t="s">
         <v>78</v>
       </c>
       <c r="B5">
+        <f>'Oil Prospective'!F16</f>
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <f>'Oil Prospective'!G16</f>
+        <v>1.0335570469798658</v>
+      </c>
+      <c r="D5">
         <f>'Oil Prospective'!H16</f>
-        <v>1</v>
-      </c>
-      <c r="C5">
+        <v>1.0671140939597314</v>
+      </c>
+      <c r="E5">
         <f>'Oil Prospective'!I16</f>
-        <v>1.0314465408805031</v>
-      </c>
-      <c r="D5">
+        <v>1.1006711409395973</v>
+      </c>
+      <c r="F5">
         <f>'Oil Prospective'!J16</f>
-        <v>1.0628930817610063</v>
-      </c>
-      <c r="E5">
+        <v>1.1342281879194629</v>
+      </c>
+      <c r="G5">
         <f>'Oil Prospective'!K16</f>
-        <v>1.0943396226415094</v>
-      </c>
-      <c r="F5">
+        <v>1.1677852348993287</v>
+      </c>
+      <c r="H5">
         <f>'Oil Prospective'!L16</f>
-        <v>1.1257861635220126</v>
-      </c>
-      <c r="G5">
+        <v>1.2013422818791946</v>
+      </c>
+      <c r="I5">
         <f>'Oil Prospective'!M16</f>
-        <v>1.1635220125786163</v>
-      </c>
-      <c r="H5">
+        <v>1.2416107382550334</v>
+      </c>
+      <c r="J5">
         <f>'Oil Prospective'!N16</f>
-        <v>1.1949685534591195</v>
-      </c>
-      <c r="I5">
+        <v>1.2751677852348993</v>
+      </c>
+      <c r="K5">
         <f>'Oil Prospective'!O16</f>
-        <v>1.2327044025157234</v>
-      </c>
-      <c r="J5">
+        <v>1.3154362416107384</v>
+      </c>
+      <c r="L5">
         <f>'Oil Prospective'!P16</f>
-        <v>1.270440251572327</v>
-      </c>
-      <c r="K5">
+        <v>1.355704697986577</v>
+      </c>
+      <c r="M5">
         <f>'Oil Prospective'!Q16</f>
-        <v>1.3081761006289307</v>
-      </c>
-      <c r="L5">
+        <v>1.3959731543624161</v>
+      </c>
+      <c r="N5">
         <f>'Oil Prospective'!R16</f>
-        <v>1.343396226415088</v>
-      </c>
-      <c r="M5">
+        <v>1.4335570469798591</v>
+      </c>
+      <c r="O5">
         <f>'Oil Prospective'!S16</f>
-        <v>1.3816352201257909</v>
-      </c>
-      <c r="N5">
+        <v>1.4743624161073876</v>
+      </c>
+      <c r="P5">
         <f>'Oil Prospective'!T16</f>
-        <v>1.4185157232704393</v>
-      </c>
-      <c r="O5">
+        <v>1.5137181208053683</v>
+      </c>
+      <c r="Q5">
         <f>'Oil Prospective'!U16</f>
-        <v>1.455315723270437</v>
-      </c>
-      <c r="P5">
+        <v>1.5529879194630838</v>
+      </c>
+      <c r="R5">
         <f>'Oil Prospective'!V16</f>
-        <v>1.4922274213836459</v>
-      </c>
-      <c r="Q5">
+        <v>1.592376912751676</v>
+      </c>
+      <c r="S5">
         <f>'Oil Prospective'!W16</f>
-        <v>1.5296209308176061</v>
-      </c>
-      <c r="R5">
+        <v>1.6322800536912707</v>
+      </c>
+      <c r="T5">
         <f>'Oil Prospective'!X16</f>
-        <v>1.5663679396226406</v>
-      </c>
-      <c r="S5">
+        <v>1.6714933046979856</v>
+      </c>
+      <c r="U5">
         <f>'Oil Prospective'!Y16</f>
-        <v>1.6034124397484195</v>
-      </c>
-      <c r="T5">
+        <v>1.7110240128858973</v>
+      </c>
+      <c r="V5">
         <f>'Oil Prospective'!Z16</f>
-        <v>1.640489076327035</v>
-      </c>
-      <c r="U5">
+        <v>1.7505890143355607</v>
+      </c>
+      <c r="W5">
         <f>'Oil Prospective'!AA16</f>
-        <v>1.6775180072251468</v>
-      </c>
-      <c r="V5">
+        <v>1.7901031083811969</v>
+      </c>
+      <c r="X5">
         <f>'Oil Prospective'!AB16</f>
-        <v>1.7144562656039994</v>
-      </c>
-      <c r="W5">
+        <v>1.8295204445035969</v>
+      </c>
+      <c r="Y5">
         <f>'Oil Prospective'!AC16</f>
-        <v>1.7515334115372718</v>
-      </c>
-      <c r="X5">
+        <v>1.8690859894927934</v>
+      </c>
+      <c r="Z5">
         <f>'Oil Prospective'!AD16</f>
-        <v>1.7885445799447695</v>
-      </c>
-      <c r="Y5">
+        <v>1.9085811289343513</v>
+      </c>
+      <c r="AA5">
         <f>'Oil Prospective'!AE16</f>
-        <v>1.8255461915919113</v>
-      </c>
-      <c r="Z5">
+        <v>1.948066070222241</v>
+      </c>
+      <c r="AB5">
         <f>'Oil Prospective'!AF16</f>
-        <v>1.8625630961028981</v>
-      </c>
-      <c r="AA5">
+        <v>1.9875673307406765</v>
+      </c>
+      <c r="AC5">
         <f>'Oil Prospective'!AG16</f>
-        <v>1.8995966412718996</v>
-      </c>
-      <c r="AB5">
+        <v>2.0270863487398123</v>
+      </c>
+      <c r="AD5">
         <f>'Oil Prospective'!AH16</f>
-        <v>1.9366002767779609</v>
-      </c>
-      <c r="AC5">
+        <v>2.066573449716079</v>
+      </c>
+      <c r="AE5">
         <f>'Oil Prospective'!AI16</f>
-        <v>1.973618710141805</v>
-      </c>
-      <c r="AD5">
+        <v>2.1060763416949464</v>
+      </c>
+      <c r="AF5">
         <f>'Oil Prospective'!AJ16</f>
-        <v>2.0106396485097457</v>
-      </c>
-      <c r="AE5" s="5">
-        <f t="shared" si="0"/>
-        <v>2.0476583398933128</v>
-      </c>
-      <c r="AF5" s="5">
-        <f t="shared" si="0"/>
-        <v>2.0846773886513956</v>
+        <v>2.1455819067989905</v>
       </c>
       <c r="AG5" s="5">
         <f t="shared" si="0"/>
-        <v>2.1216935381272948</v>
+        <v>2.1850850741143404</v>
       </c>
       <c r="AH5" s="5">
         <f t="shared" si="0"/>
-        <v>2.1587121903971616</v>
+        <v>2.224588622789073</v>
       </c>
       <c r="AI5" s="5">
         <f t="shared" si="0"/>
-        <v>2.1957308864482328</v>
+        <v>2.2640890775989253</v>
       </c>
       <c r="AJ5" s="5">
         <f t="shared" si="0"/>
-        <v>2.23274913403593</v>
+        <v>2.3035922031754947</v>
       </c>
       <c r="AK5" s="5">
         <f t="shared" si="0"/>
-        <v>2.2697672928644534</v>
+        <v>2.3430953754716044</v>
       </c>
       <c r="AL5" s="5">
         <f t="shared" si="0"/>
-        <v>2.3067852737070651</v>
+        <v>2.3825980692061273</v>
       </c>
       <c r="AM5" s="5">
         <f t="shared" si="0"/>
-        <v>2.3438036208230191</v>
+        <v>2.4221006682244846</v>
       </c>
       <c r="AN5" s="5">
         <f t="shared" si="0"/>
-        <v>2.3808219069081904</v>
+        <v>2.4616030773115667</v>
       </c>
       <c r="AO5" s="5">
         <f t="shared" si="0"/>
-        <v>2.4178401110001819</v>
+        <v>2.5011058772540951</v>
       </c>
       <c r="AP5" s="5">
         <f t="shared" si="0"/>
-        <v>2.4548583063930325</v>
+        <v>2.540608612069815</v>
       </c>
       <c r="AQ5" s="5">
         <f t="shared" si="0"/>
-        <v>2.4918765090987485</v>
+        <v>2.5801112593894571</v>
       </c>
       <c r="AR5" s="5">
         <f t="shared" si="0"/>
-        <v>2.5288947561770851</v>
+        <v>2.6196138974261229</v>
       </c>
       <c r="AS5" s="5">
         <f t="shared" si="0"/>
-        <v>2.5659129832478982</v>
+        <v>2.6591165432664505</v>
       </c>
       <c r="AT5" s="5">
         <f t="shared" si="0"/>
-        <v>2.6029311985158397</v>
+        <v>2.6986192364574273</v>
       </c>
       <c r="AU5" s="5">
         <f t="shared" si="0"/>
-        <v>2.6399494160189714</v>
+        <v>2.7381219082980937</v>
       </c>
       <c r="AV5" s="5">
         <f t="shared" si="0"/>
-        <v>2.6769676379441592</v>
+        <v>2.7776245675437492</v>
       </c>
       <c r="AW5" s="5">
         <f t="shared" si="0"/>
-        <v>2.7139858637132415</v>
+        <v>2.8171272291746075</v>
       </c>
       <c r="AX5" s="5">
         <f t="shared" si="0"/>
-        <v>2.7510040852204729</v>
+        <v>2.8566298955243044</v>
+      </c>
+      <c r="AY5" s="5">
+        <f t="shared" si="0"/>
+        <v>2.8961325659758752</v>
+      </c>
+      <c r="AZ5" s="5">
+        <f t="shared" si="0"/>
+        <v>2.9356352318795649</v>
       </c>
     </row>
-    <row r="6" spans="1:50">
+    <row r="6" spans="1:52">
       <c r="A6" t="s">
         <v>79</v>
       </c>
       <c r="B6">
+        <f>'Oil Prospective'!F17</f>
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <f>'Oil Prospective'!G17</f>
+        <v>1</v>
+      </c>
+      <c r="D6">
         <f>'Oil Prospective'!H17</f>
         <v>1</v>
       </c>
-      <c r="C6">
+      <c r="E6">
         <f>'Oil Prospective'!I17</f>
         <v>1.0075187969924813</v>
       </c>
-      <c r="D6">
+      <c r="F6">
         <f>'Oil Prospective'!J17</f>
         <v>1.0150375939849623</v>
       </c>
-      <c r="E6">
+      <c r="G6">
         <f>'Oil Prospective'!K17</f>
         <v>1.0150375939849623</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <f>'Oil Prospective'!L17</f>
         <v>1.0225563909774436</v>
       </c>
-      <c r="G6">
+      <c r="I6">
         <f>'Oil Prospective'!M17</f>
         <v>1.0300751879699248</v>
       </c>
-      <c r="H6">
+      <c r="J6">
         <f>'Oil Prospective'!N17</f>
         <v>1.0375939849624061</v>
       </c>
-      <c r="I6">
+      <c r="K6">
         <f>'Oil Prospective'!O17</f>
         <v>1.0451127819548871</v>
       </c>
-      <c r="J6">
+      <c r="L6">
         <f>'Oil Prospective'!P17</f>
         <v>1.0526315789473684</v>
       </c>
-      <c r="K6">
+      <c r="M6">
         <f>'Oil Prospective'!Q17</f>
         <v>1.0601503759398496</v>
       </c>
-      <c r="L6">
+      <c r="N6">
         <f>'Oil Prospective'!R17</f>
         <v>1.067669172932332</v>
       </c>
-      <c r="M6">
+      <c r="O6">
         <f>'Oil Prospective'!S17</f>
         <v>1.0751879699248128</v>
       </c>
-      <c r="N6">
+      <c r="P6">
         <f>'Oil Prospective'!T17</f>
         <v>1.0827067669172936</v>
       </c>
-      <c r="O6">
+      <c r="Q6">
         <f>'Oil Prospective'!U17</f>
         <v>1.0902255639097744</v>
       </c>
-      <c r="P6">
+      <c r="R6">
         <f>'Oil Prospective'!V17</f>
         <v>1.0977443609022552</v>
       </c>
-      <c r="Q6">
+      <c r="S6">
         <f>'Oil Prospective'!W17</f>
         <v>1.1052631578947358</v>
       </c>
-      <c r="R6">
+      <c r="T6">
         <f>'Oil Prospective'!X17</f>
         <v>1.1127819548872167</v>
       </c>
-      <c r="S6">
+      <c r="U6">
         <f>'Oil Prospective'!Y17</f>
         <v>1.1203007518796975</v>
       </c>
-      <c r="T6">
+      <c r="V6">
         <f>'Oil Prospective'!Z17</f>
         <v>1.1278195488721783</v>
       </c>
-      <c r="U6">
+      <c r="W6">
         <f>'Oil Prospective'!AA17</f>
         <v>1.1353383458646591</v>
       </c>
-      <c r="V6">
+      <c r="X6">
         <f>'Oil Prospective'!AB17</f>
         <v>1.1428571428571399</v>
       </c>
-      <c r="W6">
+      <c r="Y6">
         <f>'Oil Prospective'!AC17</f>
         <v>1.1503759398496205</v>
       </c>
-      <c r="X6">
+      <c r="Z6">
         <f>'Oil Prospective'!AD17</f>
         <v>1.1578947368421013</v>
       </c>
-      <c r="Y6">
+      <c r="AA6">
         <f>'Oil Prospective'!AE17</f>
         <v>1.1654135338345821</v>
       </c>
-      <c r="Z6">
+      <c r="AB6">
         <f>'Oil Prospective'!AF17</f>
         <v>1.1729323308270629</v>
       </c>
-      <c r="AA6">
+      <c r="AC6">
         <f>'Oil Prospective'!AG17</f>
         <v>1.1804511278195438</v>
       </c>
-      <c r="AB6">
+      <c r="AD6">
         <f>'Oil Prospective'!AH17</f>
         <v>1.1879699248120243</v>
       </c>
-      <c r="AC6">
+      <c r="AE6">
         <f>'Oil Prospective'!AI17</f>
         <v>1.1954887218045052</v>
       </c>
-      <c r="AD6">
+      <c r="AF6">
         <f>'Oil Prospective'!AJ17</f>
         <v>1.203007518796986</v>
       </c>
-      <c r="AE6" s="5">
+      <c r="AG6" s="5">
         <f t="shared" si="0"/>
         <v>1.2105263157894668</v>
       </c>
-      <c r="AF6" s="5">
+      <c r="AH6" s="5">
         <f t="shared" si="0"/>
         <v>1.2180451127819476</v>
       </c>
-      <c r="AG6" s="5">
+      <c r="AI6" s="5">
         <f t="shared" si="0"/>
         <v>1.2255639097744284</v>
       </c>
-      <c r="AH6" s="5">
+      <c r="AJ6" s="5">
         <f t="shared" si="0"/>
         <v>1.2330827067669092</v>
       </c>
-      <c r="AI6" s="5">
+      <c r="AK6" s="5">
         <f t="shared" si="0"/>
         <v>1.24060150375939</v>
       </c>
-      <c r="AJ6" s="5">
+      <c r="AL6" s="5">
         <f t="shared" si="0"/>
         <v>1.2481203007518709</v>
       </c>
-      <c r="AK6" s="5">
+      <c r="AM6" s="5">
         <f t="shared" si="0"/>
         <v>1.2556390977443517</v>
       </c>
-      <c r="AL6" s="5">
+      <c r="AN6" s="5">
         <f t="shared" si="0"/>
         <v>1.2631578947368325</v>
       </c>
-      <c r="AM6" s="5">
+      <c r="AO6" s="5">
         <f t="shared" si="0"/>
         <v>1.2706766917293133</v>
       </c>
-      <c r="AN6" s="5">
+      <c r="AP6" s="5">
         <f t="shared" si="0"/>
         <v>1.2781954887217941</v>
       </c>
-      <c r="AO6" s="5">
+      <c r="AQ6" s="5">
         <f t="shared" si="0"/>
         <v>1.2857142857142749</v>
       </c>
-      <c r="AP6" s="5">
+      <c r="AR6" s="5">
         <f t="shared" si="0"/>
         <v>1.2932330827067557</v>
       </c>
-      <c r="AQ6" s="5">
+      <c r="AS6" s="5">
         <f t="shared" si="0"/>
         <v>1.3007518796992366</v>
       </c>
-      <c r="AR6" s="5">
+      <c r="AT6" s="5">
         <f t="shared" si="0"/>
         <v>1.3082706766917174</v>
       </c>
-      <c r="AS6" s="5">
+      <c r="AU6" s="5">
         <f t="shared" si="0"/>
         <v>1.3157894736841982</v>
       </c>
-      <c r="AT6" s="5">
+      <c r="AV6" s="5">
         <f t="shared" si="0"/>
         <v>1.323308270676679</v>
       </c>
-      <c r="AU6" s="5">
+      <c r="AW6" s="5">
         <f t="shared" si="0"/>
         <v>1.3308270676691598</v>
       </c>
-      <c r="AV6" s="5">
+      <c r="AX6" s="5">
         <f t="shared" si="0"/>
         <v>1.3383458646616406</v>
       </c>
-      <c r="AW6" s="5">
+      <c r="AY6" s="5">
         <f t="shared" si="0"/>
         <v>1.3458646616541214</v>
       </c>
-      <c r="AX6" s="5">
+      <c r="AZ6" s="5">
         <f t="shared" si="0"/>
         <v>1.3533834586466023</v>
       </c>
     </row>
-    <row r="7" spans="1:50">
+    <row r="7" spans="1:52">
       <c r="A7" t="s">
         <v>80</v>
       </c>
@@ -21286,12 +21572,10 @@
       <c r="AD7">
         <v>0</v>
       </c>
-      <c r="AE7" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AF7" s="5">
-        <f t="shared" si="0"/>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
         <v>0</v>
       </c>
       <c r="AG7" s="5">
@@ -21363,6 +21647,14 @@
         <v>0</v>
       </c>
       <c r="AX7" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY7" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -21373,6 +21665,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
     <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
@@ -21516,15 +21817,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -21532,13 +21824,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8735FF9-3953-491F-9D62-08844ADA29C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6313B344-85D4-4D88-AA3A-B806A8982D77}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6313B344-85D4-4D88-AA3A-B806A8982D77}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8735FF9-3953-491F-9D62-08844ADA29C0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BC39C73-B2AB-45B7-8076-125344F91E0B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BC39C73-B2AB-45B7-8076-125344F91E0B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>